--- a/risk/Risk_Analysis_T3_100yrs_Future_Perfect.xlsx
+++ b/risk/Risk_Analysis_T3_100yrs_Future_Perfect.xlsx
@@ -25,18 +25,12 @@
     <sheet name="Kashmore_Exp" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="Kashmore_Vul" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="Kashmore_Dmg" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Naushahro Feroze_Exp" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Naushahro Feroze_Vul" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Naushahro Feroze_Dmg" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Qambar Shahdadkot_Exp" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Qambar Shahdadkot_Vul" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Qambar Shahdadkot_Dmg" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="Shaheed Benazirabad_Exp" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="Shaheed Benazirabad_Vul" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="Shaheed Benazirabad_Dmg" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="Shikarpur_Exp" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="Shikarpur_Vul" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="Shikarpur_Dmg" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="Qambar Shahdadkot_Exp" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Qambar Shahdadkot_Vul" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Qambar Shahdadkot_Dmg" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Shikarpur_Exp" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Shikarpur_Vul" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Shikarpur_Dmg" sheetId="24" state="visible" r:id="rId24"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -9772,7 +9766,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Naushahro Feroze | Mode: Exp</t>
+          <t>Region: Qambar Shahdadkot | Mode: Exp</t>
         </is>
       </c>
     </row>
@@ -9843,37 +9837,37 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>2059.83</v>
+        <v>28714.23</v>
       </c>
       <c r="C4" t="n">
-        <v>593208</v>
+        <v>5145336</v>
       </c>
       <c r="D4" t="n">
-        <v>466092</v>
+        <v>4042764</v>
       </c>
       <c r="E4" t="n">
-        <v>150300</v>
+        <v>1573200</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="G4" t="n">
-        <v>6660</v>
+        <v>83760</v>
       </c>
       <c r="H4" t="n">
-        <v>300</v>
+        <v>7140</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>20790</v>
+        <v>172110</v>
       </c>
     </row>
     <row r="5">
@@ -9881,37 +9875,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>3707.91</v>
+        <v>24119.01</v>
       </c>
       <c r="C5" t="n">
-        <v>666792</v>
+        <v>4257792</v>
       </c>
       <c r="D5" t="n">
-        <v>523908</v>
+        <v>3345408</v>
       </c>
       <c r="E5" t="n">
-        <v>131400</v>
+        <v>1048500</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="G5" t="n">
-        <v>8520</v>
+        <v>68280</v>
       </c>
       <c r="H5" t="n">
-        <v>30</v>
+        <v>6270</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>20520</v>
+        <v>164670</v>
       </c>
     </row>
     <row r="6">
@@ -9919,37 +9913,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>4067.01</v>
+        <v>25020.45</v>
       </c>
       <c r="C6" t="n">
-        <v>488880</v>
+        <v>3874752</v>
       </c>
       <c r="D6" t="n">
-        <v>384120</v>
+        <v>3044448</v>
       </c>
       <c r="E6" t="n">
-        <v>78300</v>
+        <v>880200</v>
       </c>
       <c r="F6" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G6" t="n">
-        <v>8160</v>
+        <v>70350</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>7710</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>22800</v>
+        <v>158730</v>
       </c>
     </row>
     <row r="7">
@@ -9957,37 +9951,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>3012.39</v>
+        <v>33500.43</v>
       </c>
       <c r="C7" t="n">
-        <v>264096</v>
+        <v>4558176</v>
       </c>
       <c r="D7" t="n">
-        <v>207504</v>
+        <v>3581424</v>
       </c>
       <c r="E7" t="n">
-        <v>38700</v>
+        <v>785700</v>
       </c>
       <c r="F7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>86340</v>
+      </c>
+      <c r="H7" t="n">
+        <v>11760</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
         <v>1</v>
       </c>
-      <c r="G7" t="n">
-        <v>5460</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>13440</v>
+        <v>202800</v>
       </c>
     </row>
     <row r="8">
@@ -9995,37 +9989,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>1587.24</v>
+        <v>27742.5</v>
       </c>
       <c r="C8" t="n">
-        <v>91224</v>
+        <v>2269512</v>
       </c>
       <c r="D8" t="n">
-        <v>71676</v>
+        <v>1783188</v>
       </c>
       <c r="E8" t="n">
-        <v>19800</v>
+        <v>245700</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2370</v>
+        <v>58710</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>2580</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>4770</v>
+        <v>124770</v>
       </c>
     </row>
     <row r="9">
@@ -10033,37 +10027,37 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>752.67</v>
+        <v>23407.47</v>
       </c>
       <c r="C9" t="n">
-        <v>37800</v>
+        <v>1675296</v>
       </c>
       <c r="D9" t="n">
-        <v>29700</v>
+        <v>1316304</v>
       </c>
       <c r="E9" t="n">
-        <v>9000</v>
+        <v>134100</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>990</v>
+        <v>36300</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>960</v>
+        <v>72870</v>
       </c>
     </row>
     <row r="10">
@@ -10071,22 +10065,22 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>425.88</v>
+        <v>12497.76</v>
       </c>
       <c r="C10" t="n">
-        <v>4536</v>
+        <v>837144</v>
       </c>
       <c r="D10" t="n">
-        <v>3564</v>
+        <v>657756</v>
       </c>
       <c r="E10" t="n">
-        <v>1800</v>
+        <v>45000</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>630</v>
+        <v>19350</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -10095,13 +10089,13 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>630</v>
+        <v>38340</v>
       </c>
     </row>
     <row r="11">
@@ -10109,25 +10103,25 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>275.31</v>
+        <v>1361.79</v>
       </c>
       <c r="C11" t="n">
-        <v>1512</v>
+        <v>106344</v>
       </c>
       <c r="D11" t="n">
-        <v>1188</v>
+        <v>83556</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>180</v>
+        <v>2460</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -10139,7 +10133,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>210</v>
+        <v>9390</v>
       </c>
     </row>
     <row r="12">
@@ -10147,22 +10141,22 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>160.83</v>
+        <v>283.23</v>
       </c>
       <c r="C12" t="n">
-        <v>2016</v>
+        <v>30744</v>
       </c>
       <c r="D12" t="n">
-        <v>1584</v>
+        <v>24156</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>120</v>
+        <v>960</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -10177,7 +10171,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>240</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="13">
@@ -10185,13 +10179,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>134.1</v>
+        <v>179.64</v>
       </c>
       <c r="C13" t="n">
-        <v>504</v>
+        <v>8568</v>
       </c>
       <c r="D13" t="n">
-        <v>396</v>
+        <v>6732</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -10200,7 +10194,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -10215,7 +10209,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>150</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="14">
@@ -10223,22 +10217,22 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>125.01</v>
+        <v>95.76000000000001</v>
       </c>
       <c r="C14" t="n">
-        <v>504</v>
+        <v>1512</v>
       </c>
       <c r="D14" t="n">
-        <v>396</v>
+        <v>1188</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>450</v>
+        <v>240</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -10253,7 +10247,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>540</v>
+        <v>840</v>
       </c>
     </row>
     <row r="15">
@@ -10261,13 +10255,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>6.48</v>
+        <v>12.15</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>3528</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>2772</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -10276,7 +10270,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -10291,7 +10285,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>480</v>
       </c>
     </row>
     <row r="16">
@@ -10299,13 +10293,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>1.08</v>
+        <v>17.55</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -10314,7 +10308,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -10329,7 +10323,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
     </row>
     <row r="17">
@@ -10337,13 +10331,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>1.26</v>
+        <v>10.35</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -10352,7 +10346,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -10367,7 +10361,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>390</v>
       </c>
     </row>
     <row r="18">
@@ -10375,13 +10369,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>1.44</v>
+        <v>4.68</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -10390,7 +10384,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -10405,7 +10399,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
     </row>
     <row r="19">
@@ -10413,7 +10407,7 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>0.18</v>
+        <v>1.44</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -10428,7 +10422,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -10443,7 +10437,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>570</v>
       </c>
     </row>
     <row r="20">
@@ -10451,13 +10445,13 @@
         <v>800</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>4536</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>3564</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -10466,7 +10460,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>3630</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -10492,10 +10486,10 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -10530,10 +10524,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -10568,10 +10562,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -10606,10 +10600,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>2520</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>1980</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -11636,7 +11630,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Naushahro Feroze | Mode: Vul</t>
+          <t>Region: Qambar Shahdadkot | Mode: Vul</t>
         </is>
       </c>
     </row>
@@ -11745,37 +11739,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>1668.56</v>
+        <v>10853.55</v>
       </c>
       <c r="C5" t="n">
-        <v>366735.6</v>
+        <v>2341785.6</v>
       </c>
       <c r="D5" t="n">
-        <v>173413.55</v>
+        <v>1107330.05</v>
       </c>
       <c r="E5" t="n">
-        <v>14493.42</v>
+        <v>115649.55</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06</v>
+        <v>0.4</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>10.8</v>
+        <v>2257.2</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>4309.2</v>
+        <v>34580.7</v>
       </c>
     </row>
     <row r="6">
@@ -11783,37 +11777,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>3253.61</v>
+        <v>20016.36</v>
       </c>
       <c r="C6" t="n">
-        <v>439992</v>
+        <v>3487276.8</v>
       </c>
       <c r="D6" t="n">
-        <v>194748.84</v>
+        <v>1543535.14</v>
       </c>
       <c r="E6" t="n">
-        <v>13232.7</v>
+        <v>148753.8</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="G6" t="n">
-        <v>408</v>
+        <v>3517.5</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>4394.7</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>8436</v>
+        <v>58730.1</v>
       </c>
     </row>
     <row r="7">
@@ -11821,37 +11815,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>2861.77</v>
+        <v>31825.41</v>
       </c>
       <c r="C7" t="n">
-        <v>264096</v>
+        <v>4558176</v>
       </c>
       <c r="D7" t="n">
-        <v>132387.55</v>
+        <v>2284948.51</v>
       </c>
       <c r="E7" t="n">
-        <v>8231.49</v>
+        <v>167118.39</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="G7" t="n">
-        <v>819</v>
+        <v>12951</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>8584.799999999999</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>8064</v>
+        <v>121680</v>
       </c>
     </row>
     <row r="8">
@@ -11859,37 +11853,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>1587.24</v>
+        <v>27742.5</v>
       </c>
       <c r="C8" t="n">
-        <v>91224</v>
+        <v>2269512</v>
       </c>
       <c r="D8" t="n">
-        <v>52753.54</v>
+        <v>1312426.37</v>
       </c>
       <c r="E8" t="n">
-        <v>4856.94</v>
+        <v>60270.21</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1540.5</v>
+        <v>38161.5</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>2193</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>3386.7</v>
+        <v>88586.7</v>
       </c>
     </row>
     <row r="9">
@@ -11897,37 +11891,37 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>752.67</v>
+        <v>23407.47</v>
       </c>
       <c r="C9" t="n">
-        <v>37800</v>
+        <v>1675296</v>
       </c>
       <c r="D9" t="n">
-        <v>23849.1</v>
+        <v>1056992.11</v>
       </c>
       <c r="E9" t="n">
-        <v>2409.3</v>
+        <v>35898.57</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>841.5</v>
+        <v>30855</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>777.6</v>
+        <v>59024.7</v>
       </c>
     </row>
     <row r="10">
@@ -11935,22 +11929,22 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>425.88</v>
+        <v>12497.76</v>
       </c>
       <c r="C10" t="n">
-        <v>4536</v>
+        <v>837144</v>
       </c>
       <c r="D10" t="n">
-        <v>3100.68</v>
+        <v>572247.72</v>
       </c>
       <c r="E10" t="n">
-        <v>522</v>
+        <v>13050</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>630</v>
+        <v>19350</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -11959,13 +11953,13 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>560.7</v>
+        <v>34122.6</v>
       </c>
     </row>
     <row r="11">
@@ -11973,25 +11967,25 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>275.31</v>
+        <v>1361.79</v>
       </c>
       <c r="C11" t="n">
-        <v>1512</v>
+        <v>106344</v>
       </c>
       <c r="D11" t="n">
-        <v>1067.42</v>
+        <v>75075.07000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>1475.28</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>180</v>
+        <v>2460</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -12003,7 +11997,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>210</v>
+        <v>9390</v>
       </c>
     </row>
     <row r="12">
@@ -12011,22 +12005,22 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>160.83</v>
+        <v>283.23</v>
       </c>
       <c r="C12" t="n">
-        <v>2016</v>
+        <v>30744</v>
       </c>
       <c r="D12" t="n">
-        <v>1468.37</v>
+        <v>22392.61</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>860.4</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>120</v>
+        <v>960</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -12041,7 +12035,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>240</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="13">
@@ -12049,13 +12043,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>134.1</v>
+        <v>179.64</v>
       </c>
       <c r="C13" t="n">
-        <v>504</v>
+        <v>8568</v>
       </c>
       <c r="D13" t="n">
-        <v>376</v>
+        <v>6392.03</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -12064,7 +12058,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -12079,7 +12073,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>150</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="14">
@@ -12087,22 +12081,22 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>125.01</v>
+        <v>95.76000000000001</v>
       </c>
       <c r="C14" t="n">
-        <v>504</v>
+        <v>1512</v>
       </c>
       <c r="D14" t="n">
-        <v>384.91</v>
+        <v>1154.74</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>512.37</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>450</v>
+        <v>240</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -12117,7 +12111,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>540</v>
+        <v>840</v>
       </c>
     </row>
     <row r="15">
@@ -12125,13 +12119,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>6.48</v>
+        <v>12.15</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>3528</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>2733.19</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -12140,7 +12134,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -12155,7 +12149,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>480</v>
       </c>
     </row>
     <row r="16">
@@ -12163,13 +12157,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>1.08</v>
+        <v>17.55</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -12178,7 +12172,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -12193,7 +12187,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
     </row>
     <row r="17">
@@ -12201,13 +12195,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>1.26</v>
+        <v>10.35</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -12216,7 +12210,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -12231,7 +12225,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>390</v>
       </c>
     </row>
     <row r="18">
@@ -12239,13 +12233,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>1.44</v>
+        <v>4.68</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -12254,7 +12248,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -12269,7 +12263,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
     </row>
     <row r="19">
@@ -12277,7 +12271,7 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>0.18</v>
+        <v>1.44</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -12292,7 +12286,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -12307,7 +12301,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>570</v>
       </c>
     </row>
     <row r="20">
@@ -12315,13 +12309,13 @@
         <v>800</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>4536</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>3564</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -12330,7 +12324,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>3630</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -12356,10 +12350,10 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -12394,10 +12388,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -12432,10 +12426,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -12470,10 +12464,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>2520</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>1980</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -12568,7 +12562,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Naushahro Feroze | Mode: Dmg</t>
+          <t>Region: Qambar Shahdadkot | Mode: Dmg</t>
         </is>
       </c>
     </row>
@@ -12677,37 +12671,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>3670830.9</v>
+        <v>23877819.9</v>
       </c>
       <c r="C5" t="n">
-        <v>20170458</v>
+        <v>128798208</v>
       </c>
       <c r="D5" t="n">
-        <v>17571994.82</v>
+        <v>112205753.76</v>
       </c>
       <c r="E5" t="n">
-        <v>2670267.7</v>
+        <v>21307273.09</v>
       </c>
       <c r="F5" t="n">
-        <v>2500.02</v>
+        <v>16666.8</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2987.82</v>
+        <v>624454.38</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>174999</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>40592.66</v>
+        <v>325750.19</v>
       </c>
     </row>
     <row r="6">
@@ -12715,37 +12709,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>7157937.6</v>
+        <v>44035992</v>
       </c>
       <c r="C6" t="n">
-        <v>24199560</v>
+        <v>191800224</v>
       </c>
       <c r="D6" t="n">
-        <v>19733899.96</v>
+        <v>156406415.33</v>
       </c>
       <c r="E6" t="n">
-        <v>2437992.65</v>
+        <v>27406400.11</v>
       </c>
       <c r="F6" t="n">
-        <v>29166.9</v>
+        <v>58333.8</v>
       </c>
       <c r="G6" t="n">
-        <v>7548</v>
+        <v>65073.75</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1215793.75</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>174999</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>79467.12</v>
+        <v>553237.54</v>
       </c>
     </row>
     <row r="7">
@@ -12753,37 +12747,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>6295895.1</v>
+        <v>70015898.7</v>
       </c>
       <c r="C7" t="n">
-        <v>14525280</v>
+        <v>250699680</v>
       </c>
       <c r="D7" t="n">
-        <v>13414830.64</v>
+        <v>231533832.72</v>
       </c>
       <c r="E7" t="n">
-        <v>1516569.72</v>
+        <v>30789892.17</v>
       </c>
       <c r="F7" t="n">
-        <v>25000.2</v>
+        <v>50000.4</v>
       </c>
       <c r="G7" t="n">
-        <v>15151.5</v>
+        <v>239593.5</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2374984.92</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>40833.1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>75962.88</v>
+        <v>1146225.6</v>
       </c>
     </row>
     <row r="8">
@@ -12791,37 +12785,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>3491928</v>
+        <v>61033500</v>
       </c>
       <c r="C8" t="n">
-        <v>5017320</v>
+        <v>124823160</v>
       </c>
       <c r="D8" t="n">
-        <v>5345515.8</v>
+        <v>132988163.87</v>
       </c>
       <c r="E8" t="n">
-        <v>894842.63</v>
+        <v>11104183.49</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>28499.25</v>
+        <v>705987.75</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>606693.45</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>99166.10000000001</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>31902.71</v>
+        <v>834486.71</v>
       </c>
     </row>
     <row r="9">
@@ -12829,37 +12823,37 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>1655874</v>
+        <v>51496434</v>
       </c>
       <c r="C9" t="n">
-        <v>2079000</v>
+        <v>92141280</v>
       </c>
       <c r="D9" t="n">
-        <v>2416629.3</v>
+        <v>107105010.71</v>
       </c>
       <c r="E9" t="n">
-        <v>443889.43</v>
+        <v>6613952.54</v>
       </c>
       <c r="F9" t="n">
-        <v>41667</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>15567.75</v>
+        <v>570817.5</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>74695.5</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>110832.7</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>7324.99</v>
+        <v>556012.67</v>
       </c>
     </row>
     <row r="10">
@@ -12867,22 +12861,22 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>936936</v>
+        <v>27495072</v>
       </c>
       <c r="C10" t="n">
-        <v>249480</v>
+        <v>46042920</v>
       </c>
       <c r="D10" t="n">
-        <v>314191.9</v>
+        <v>57985861.47</v>
       </c>
       <c r="E10" t="n">
-        <v>96173.28</v>
+        <v>2404332</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>11655</v>
+        <v>357975</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -12891,13 +12885,13 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>58333</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>5281.79</v>
+        <v>321434.89</v>
       </c>
     </row>
     <row r="11">
@@ -12905,25 +12899,25 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>605682</v>
+        <v>2995938</v>
       </c>
       <c r="C11" t="n">
-        <v>83160</v>
+        <v>5848920</v>
       </c>
       <c r="D11" t="n">
-        <v>108161.47</v>
+        <v>7607356.44</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>271805.59</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>3330</v>
+        <v>45510</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>8299.5</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -12935,7 +12929,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1978.2</v>
+        <v>88453.8</v>
       </c>
     </row>
     <row r="12">
@@ -12943,22 +12937,22 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>353826</v>
+        <v>623106</v>
       </c>
       <c r="C12" t="n">
-        <v>110880</v>
+        <v>1690920</v>
       </c>
       <c r="D12" t="n">
-        <v>148789.73</v>
+        <v>2269043.37</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>158520.1</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>2220</v>
+        <v>17760</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -12973,7 +12967,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>2260.8</v>
+        <v>42390</v>
       </c>
     </row>
     <row r="13">
@@ -12981,13 +12975,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>295020</v>
+        <v>395208</v>
       </c>
       <c r="C13" t="n">
-        <v>27720</v>
+        <v>471240</v>
       </c>
       <c r="D13" t="n">
-        <v>38100.28</v>
+        <v>647704.8100000001</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -12996,7 +12990,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>2220</v>
+        <v>2775</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -13011,7 +13005,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1413</v>
+        <v>26847</v>
       </c>
     </row>
     <row r="14">
@@ -13019,22 +13013,22 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>275022</v>
+        <v>210672</v>
       </c>
       <c r="C14" t="n">
-        <v>27720</v>
+        <v>83160</v>
       </c>
       <c r="D14" t="n">
-        <v>39003.13</v>
+        <v>117009.4</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>94399.05</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>8325</v>
+        <v>4440</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -13049,7 +13043,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>5086.8</v>
+        <v>7912.8</v>
       </c>
     </row>
     <row r="15">
@@ -13057,13 +13051,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>14256</v>
+        <v>26730</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>194040</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>276954.35</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -13072,7 +13066,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1665</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -13087,7 +13081,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>4521.6</v>
       </c>
     </row>
     <row r="16">
@@ -13095,13 +13089,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>2376</v>
+        <v>38610</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>55440</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>80253.36</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -13110,7 +13104,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>2775</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -13125,7 +13119,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2543.4</v>
       </c>
     </row>
     <row r="17">
@@ -13133,13 +13127,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>2772</v>
+        <v>22770</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>55440</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>80253.36</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -13148,7 +13142,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1665</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -13163,7 +13157,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>3673.8</v>
       </c>
     </row>
     <row r="18">
@@ -13171,13 +13165,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>3168</v>
+        <v>10296</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>55440</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>80253.36</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -13186,7 +13180,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>3885</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -13201,7 +13195,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>3391.2</v>
       </c>
     </row>
     <row r="19">
@@ -13209,7 +13203,7 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>396</v>
+        <v>3168</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -13224,7 +13218,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>3330</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -13239,7 +13233,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>5369.4</v>
       </c>
     </row>
     <row r="20">
@@ -13247,13 +13241,13 @@
         <v>800</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>198</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>249480</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>361140.12</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -13262,7 +13256,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>67155</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -13288,10 +13282,10 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>55440</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>80253.36</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -13326,10 +13320,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>55440</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>80253.36</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -13364,10 +13358,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>27720</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>40126.68</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -13402,10 +13396,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>138600</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>200633.4</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -13500,7 +13494,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Qambar Shahdadkot | Mode: Exp</t>
+          <t>Region: Shikarpur | Mode: Exp</t>
         </is>
       </c>
     </row>
@@ -13571,37 +13565,37 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>28714.23</v>
+        <v>35635.14</v>
       </c>
       <c r="C4" t="n">
-        <v>5145336</v>
+        <v>3646440</v>
       </c>
       <c r="D4" t="n">
-        <v>4042764</v>
+        <v>2865060</v>
       </c>
       <c r="E4" t="n">
-        <v>1573200</v>
+        <v>1043100</v>
       </c>
       <c r="F4" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="G4" t="n">
-        <v>83760</v>
+        <v>107160</v>
       </c>
       <c r="H4" t="n">
-        <v>7140</v>
+        <v>13650</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>172110</v>
+        <v>343050</v>
       </c>
     </row>
     <row r="5">
@@ -13609,37 +13603,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>24119.01</v>
+        <v>11607.3</v>
       </c>
       <c r="C5" t="n">
-        <v>4257792</v>
+        <v>782712</v>
       </c>
       <c r="D5" t="n">
-        <v>3345408</v>
+        <v>614988</v>
       </c>
       <c r="E5" t="n">
-        <v>1048500</v>
+        <v>241200</v>
       </c>
       <c r="F5" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="G5" t="n">
-        <v>68280</v>
+        <v>30300</v>
       </c>
       <c r="H5" t="n">
-        <v>6270</v>
+        <v>2910</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>164670</v>
+        <v>110880</v>
       </c>
     </row>
     <row r="6">
@@ -13647,37 +13641,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>25020.45</v>
+        <v>1142.55</v>
       </c>
       <c r="C6" t="n">
-        <v>3874752</v>
+        <v>109368</v>
       </c>
       <c r="D6" t="n">
-        <v>3044448</v>
+        <v>85932</v>
       </c>
       <c r="E6" t="n">
-        <v>880200</v>
+        <v>31500</v>
       </c>
       <c r="F6" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>70350</v>
+        <v>4110</v>
       </c>
       <c r="H6" t="n">
-        <v>7710</v>
+        <v>330</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>158730</v>
+        <v>18780</v>
       </c>
     </row>
     <row r="7">
@@ -13685,37 +13679,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>33500.43</v>
+        <v>150.12</v>
       </c>
       <c r="C7" t="n">
-        <v>4558176</v>
+        <v>26712</v>
       </c>
       <c r="D7" t="n">
-        <v>3581424</v>
+        <v>20988</v>
       </c>
       <c r="E7" t="n">
-        <v>785700</v>
+        <v>3600</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>86340</v>
+        <v>780</v>
       </c>
       <c r="H7" t="n">
-        <v>11760</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>202800</v>
+        <v>2940</v>
       </c>
     </row>
     <row r="8">
@@ -13723,37 +13717,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>27742.5</v>
+        <v>12.33</v>
       </c>
       <c r="C8" t="n">
-        <v>2269512</v>
+        <v>1008</v>
       </c>
       <c r="D8" t="n">
-        <v>1783188</v>
+        <v>792</v>
       </c>
       <c r="E8" t="n">
-        <v>245700</v>
+        <v>900</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>58710</v>
+        <v>270</v>
       </c>
       <c r="H8" t="n">
-        <v>2580</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>124770</v>
+        <v>480</v>
       </c>
     </row>
     <row r="9">
@@ -13761,37 +13755,37 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>23407.47</v>
+        <v>0.09</v>
       </c>
       <c r="C9" t="n">
-        <v>1675296</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>1316304</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>134100</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>36300</v>
+        <v>30</v>
       </c>
       <c r="H9" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>72870</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10">
@@ -13799,22 +13793,22 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>12497.76</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>837144</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>657756</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>45000</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>19350</v>
+        <v>30</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -13823,13 +13817,13 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>38340</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11">
@@ -13837,25 +13831,25 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>1361.79</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>106344</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>83556</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>3600</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>2460</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -13867,7 +13861,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>9390</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12">
@@ -13875,22 +13869,22 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>283.23</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>30744</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>24156</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>960</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -13905,7 +13899,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>4500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -13913,13 +13907,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>179.64</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>8568</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>6732</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -13928,7 +13922,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -13943,7 +13937,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>2850</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -13951,22 +13945,22 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>95.76000000000001</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>1512</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>1188</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -13981,7 +13975,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>840</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -13989,13 +13983,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>12.15</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>3528</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>2772</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -14004,7 +13998,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -14019,7 +14013,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>480</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -14027,13 +14021,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>17.55</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -14042,7 +14036,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -14057,7 +14051,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -14065,13 +14059,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>10.35</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -14080,7 +14074,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -14095,7 +14089,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>390</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -14103,13 +14097,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -14118,7 +14112,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -14133,7 +14127,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>360</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -14141,7 +14135,7 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -14156,7 +14150,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -14171,7 +14165,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>570</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -14179,13 +14173,13 @@
         <v>800</v>
       </c>
       <c r="B20" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>4536</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>3564</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -14194,7 +14188,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>3630</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -14220,10 +14214,10 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -14258,10 +14252,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -14296,10 +14290,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -14334,10 +14328,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>2520</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>1980</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -14432,7 +14426,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Qambar Shahdadkot | Mode: Vul</t>
+          <t>Region: Shikarpur | Mode: Vul</t>
         </is>
       </c>
     </row>
@@ -14541,37 +14535,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>10853.55</v>
+        <v>5223.28</v>
       </c>
       <c r="C5" t="n">
-        <v>2341785.6</v>
+        <v>430491.6</v>
       </c>
       <c r="D5" t="n">
-        <v>1107330.05</v>
+        <v>203561.03</v>
       </c>
       <c r="E5" t="n">
-        <v>115649.55</v>
+        <v>26604.36</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4</v>
+        <v>0.18</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2257.2</v>
+        <v>1047.6</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>34580.7</v>
+        <v>23284.8</v>
       </c>
     </row>
     <row r="6">
@@ -14579,37 +14573,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>20016.36</v>
+        <v>914.04</v>
       </c>
       <c r="C6" t="n">
-        <v>3487276.8</v>
+        <v>98431.2</v>
       </c>
       <c r="D6" t="n">
-        <v>1543535.14</v>
+        <v>43567.52</v>
       </c>
       <c r="E6" t="n">
-        <v>148753.8</v>
+        <v>5323.5</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>3517.5</v>
+        <v>205.5</v>
       </c>
       <c r="H6" t="n">
-        <v>4394.7</v>
+        <v>188.1</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>58730.1</v>
+        <v>6948.6</v>
       </c>
     </row>
     <row r="7">
@@ -14617,37 +14611,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>31825.41</v>
+        <v>142.61</v>
       </c>
       <c r="C7" t="n">
-        <v>4558176</v>
+        <v>26712</v>
       </c>
       <c r="D7" t="n">
-        <v>2284948.51</v>
+        <v>13390.34</v>
       </c>
       <c r="E7" t="n">
-        <v>167118.39</v>
+        <v>765.72</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>12951</v>
+        <v>117</v>
       </c>
       <c r="H7" t="n">
-        <v>8584.799999999999</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>121680</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="8">
@@ -14655,37 +14649,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>27742.5</v>
+        <v>12.33</v>
       </c>
       <c r="C8" t="n">
-        <v>2269512</v>
+        <v>1008</v>
       </c>
       <c r="D8" t="n">
-        <v>1312426.37</v>
+        <v>582.91</v>
       </c>
       <c r="E8" t="n">
-        <v>60270.21</v>
+        <v>220.77</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>38161.5</v>
+        <v>175.5</v>
       </c>
       <c r="H8" t="n">
-        <v>2193</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>88586.7</v>
+        <v>340.8</v>
       </c>
     </row>
     <row r="9">
@@ -14693,37 +14687,37 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>23407.47</v>
+        <v>0.09</v>
       </c>
       <c r="C9" t="n">
-        <v>1675296</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>1056992.11</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>35898.57</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>30855</v>
+        <v>25.5</v>
       </c>
       <c r="H9" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>59024.7</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="10">
@@ -14731,22 +14725,22 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>12497.76</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>837144</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>572247.72</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>13050</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>19350</v>
+        <v>30</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -14755,13 +14749,13 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>34122.6</v>
+        <v>160.2</v>
       </c>
     </row>
     <row r="11">
@@ -14769,25 +14763,25 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>1361.79</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>106344</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>75075.07000000001</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>1475.28</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>2460</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -14799,7 +14793,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>9390</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12">
@@ -14807,22 +14801,22 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>283.23</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>30744</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>22392.61</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>860.4</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>960</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -14837,7 +14831,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>4500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -14845,13 +14839,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>179.64</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>8568</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>6392.03</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -14860,7 +14854,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -14875,7 +14869,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>2850</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -14883,22 +14877,22 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>95.76000000000001</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>1512</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>1154.74</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>512.37</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -14913,7 +14907,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>840</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -14921,13 +14915,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>12.15</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>3528</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>2733.19</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -14936,7 +14930,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -14951,7 +14945,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>480</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -14959,13 +14953,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>17.55</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -14974,7 +14968,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -14989,7 +14983,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -14997,13 +14991,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>10.35</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -15012,7 +15006,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -15027,7 +15021,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>390</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -15035,13 +15029,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -15050,7 +15044,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -15065,7 +15059,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>360</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -15073,7 +15067,7 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -15088,7 +15082,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -15103,7 +15097,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>570</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -15111,13 +15105,13 @@
         <v>800</v>
       </c>
       <c r="B20" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>4536</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>3564</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -15126,7 +15120,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>3630</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -15152,10 +15146,10 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -15190,10 +15184,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -15228,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -15266,10 +15260,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>2520</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>1980</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -15364,7 +15358,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Qambar Shahdadkot | Mode: Dmg</t>
+          <t>Region: Shikarpur | Mode: Dmg</t>
         </is>
       </c>
     </row>
@@ -15473,37 +15467,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>23877819.9</v>
+        <v>11491227</v>
       </c>
       <c r="C5" t="n">
-        <v>128798208</v>
+        <v>23677038</v>
       </c>
       <c r="D5" t="n">
-        <v>112205753.76</v>
+        <v>20626838.97</v>
       </c>
       <c r="E5" t="n">
-        <v>21307273.09</v>
+        <v>4901587.29</v>
       </c>
       <c r="F5" t="n">
-        <v>16666.8</v>
+        <v>7500.06</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>624454.38</v>
+        <v>289818.54</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>174999</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>325750.19</v>
+        <v>219342.82</v>
       </c>
     </row>
     <row r="6">
@@ -15511,37 +15505,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>44035992</v>
+        <v>2010888</v>
       </c>
       <c r="C6" t="n">
-        <v>191800224</v>
+        <v>5413716</v>
       </c>
       <c r="D6" t="n">
-        <v>156406415.33</v>
+        <v>4414697.21</v>
       </c>
       <c r="E6" t="n">
-        <v>27406400.11</v>
+        <v>980801.64</v>
       </c>
       <c r="F6" t="n">
-        <v>58333.8</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>65073.75</v>
+        <v>3801.75</v>
       </c>
       <c r="H6" t="n">
-        <v>1215793.75</v>
+        <v>52037.86</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>174999</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>553237.54</v>
+        <v>65455.81</v>
       </c>
     </row>
     <row r="7">
@@ -15549,37 +15543,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>70015898.7</v>
+        <v>313750.8</v>
       </c>
       <c r="C7" t="n">
-        <v>250699680</v>
+        <v>1469160</v>
       </c>
       <c r="D7" t="n">
-        <v>231533832.72</v>
+        <v>1356843.56</v>
       </c>
       <c r="E7" t="n">
-        <v>30789892.17</v>
+        <v>141076.25</v>
       </c>
       <c r="F7" t="n">
-        <v>50000.4</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>239593.5</v>
+        <v>2164.5</v>
       </c>
       <c r="H7" t="n">
-        <v>2374984.92</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>40833.1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1146225.6</v>
+        <v>16616.88</v>
       </c>
     </row>
     <row r="8">
@@ -15587,37 +15581,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>61033500</v>
+        <v>27126</v>
       </c>
       <c r="C8" t="n">
-        <v>124823160</v>
+        <v>55440</v>
       </c>
       <c r="D8" t="n">
-        <v>132988163.87</v>
+        <v>59066.47</v>
       </c>
       <c r="E8" t="n">
-        <v>11104183.49</v>
+        <v>40674.66</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>705987.75</v>
+        <v>3246.75</v>
       </c>
       <c r="H8" t="n">
-        <v>606693.45</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>99166.10000000001</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>834486.71</v>
+        <v>3210.34</v>
       </c>
     </row>
     <row r="9">
@@ -15625,37 +15619,37 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>51496434</v>
+        <v>198</v>
       </c>
       <c r="C9" t="n">
-        <v>92141280</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>107105010.71</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>6613952.54</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>570817.5</v>
+        <v>471.75</v>
       </c>
       <c r="H9" t="n">
-        <v>74695.5</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>110832.7</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>556012.67</v>
+        <v>457.81</v>
       </c>
     </row>
     <row r="10">
@@ -15663,22 +15657,22 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>27495072</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>46042920</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>57985861.47</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>2404332</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>357975</v>
+        <v>555</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -15687,13 +15681,13 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>58333</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>321434.89</v>
+        <v>1509.08</v>
       </c>
     </row>
     <row r="11">
@@ -15701,25 +15695,25 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>2995938</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>5848920</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>7607356.44</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>271805.59</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>45510</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>8299.5</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -15731,4667 +15725,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>88453.8</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>623106</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1690920</v>
-      </c>
-      <c r="D12" t="n">
-        <v>2269043.37</v>
-      </c>
-      <c r="E12" t="n">
-        <v>158520.1</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>17760</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>42390</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>395208</v>
-      </c>
-      <c r="C13" t="n">
-        <v>471240</v>
-      </c>
-      <c r="D13" t="n">
-        <v>647704.8100000001</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>2775</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>26847</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>210672</v>
-      </c>
-      <c r="C14" t="n">
-        <v>83160</v>
-      </c>
-      <c r="D14" t="n">
-        <v>117009.4</v>
-      </c>
-      <c r="E14" t="n">
-        <v>94399.05</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>4440</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>7912.8</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>26730</v>
-      </c>
-      <c r="C15" t="n">
-        <v>194040</v>
-      </c>
-      <c r="D15" t="n">
-        <v>276954.35</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1665</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>4521.6</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>38610</v>
-      </c>
-      <c r="C16" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D16" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>2775</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>2543.4</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>22770</v>
-      </c>
-      <c r="C17" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D17" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1665</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>3673.8</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>10296</v>
-      </c>
-      <c r="C18" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D18" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>3885</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>3391.2</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>3168</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>3330</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>5369.4</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>198</v>
-      </c>
-      <c r="C20" t="n">
-        <v>249480</v>
-      </c>
-      <c r="D20" t="n">
-        <v>361140.12</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>67155</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D21" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D22" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>27720</v>
-      </c>
-      <c r="D23" t="n">
-        <v>40126.68</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>138600</v>
-      </c>
-      <c r="D24" t="n">
-        <v>200633.4</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shaheed Benazirabad | Mode: Exp</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>3766.32</v>
-      </c>
-      <c r="C4" t="n">
-        <v>1108800</v>
-      </c>
-      <c r="D4" t="n">
-        <v>871200</v>
-      </c>
-      <c r="E4" t="n">
-        <v>364500</v>
-      </c>
-      <c r="F4" t="n">
-        <v>10</v>
-      </c>
-      <c r="G4" t="n">
-        <v>13350</v>
-      </c>
-      <c r="H4" t="n">
-        <v>3330</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>34890</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>4836.69</v>
-      </c>
-      <c r="C5" t="n">
-        <v>928368</v>
-      </c>
-      <c r="D5" t="n">
-        <v>729432</v>
-      </c>
-      <c r="E5" t="n">
-        <v>216000</v>
-      </c>
-      <c r="F5" t="n">
-        <v>8</v>
-      </c>
-      <c r="G5" t="n">
-        <v>16200</v>
-      </c>
-      <c r="H5" t="n">
-        <v>3000</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>35280</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>4413.51</v>
-      </c>
-      <c r="C6" t="n">
-        <v>537768</v>
-      </c>
-      <c r="D6" t="n">
-        <v>422532</v>
-      </c>
-      <c r="E6" t="n">
-        <v>105300</v>
-      </c>
-      <c r="F6" t="n">
-        <v>6</v>
-      </c>
-      <c r="G6" t="n">
-        <v>11670</v>
-      </c>
-      <c r="H6" t="n">
-        <v>930</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>22590</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>4003.65</v>
-      </c>
-      <c r="C7" t="n">
-        <v>346752</v>
-      </c>
-      <c r="D7" t="n">
-        <v>272448</v>
-      </c>
-      <c r="E7" t="n">
-        <v>69300</v>
-      </c>
-      <c r="F7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G7" t="n">
-        <v>5040</v>
-      </c>
-      <c r="H7" t="n">
-        <v>390</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>4268.25</v>
-      </c>
-      <c r="C8" t="n">
-        <v>233856</v>
-      </c>
-      <c r="D8" t="n">
-        <v>183744</v>
-      </c>
-      <c r="E8" t="n">
-        <v>39600</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>3030</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>10500</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>4117.05</v>
-      </c>
-      <c r="C9" t="n">
-        <v>204624</v>
-      </c>
-      <c r="D9" t="n">
-        <v>160776</v>
-      </c>
-      <c r="E9" t="n">
-        <v>27000</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>4290</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>12090</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>2748.96</v>
-      </c>
-      <c r="C10" t="n">
-        <v>93240</v>
-      </c>
-      <c r="D10" t="n">
-        <v>73260</v>
-      </c>
-      <c r="E10" t="n">
-        <v>5400</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" t="n">
-        <v>2790</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>5730</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>1942.56</v>
-      </c>
-      <c r="C11" t="n">
-        <v>35280</v>
-      </c>
-      <c r="D11" t="n">
-        <v>27720</v>
-      </c>
-      <c r="E11" t="n">
-        <v>900</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>450</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1170</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>1069.02</v>
-      </c>
-      <c r="C12" t="n">
-        <v>8568</v>
-      </c>
-      <c r="D12" t="n">
-        <v>6732</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>300</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>647.8200000000001</v>
-      </c>
-      <c r="C13" t="n">
-        <v>4536</v>
-      </c>
-      <c r="D13" t="n">
-        <v>3564</v>
-      </c>
-      <c r="E13" t="n">
-        <v>900</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>447.84</v>
-      </c>
-      <c r="C14" t="n">
-        <v>2520</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1980</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>295.65</v>
-      </c>
-      <c r="C15" t="n">
-        <v>2016</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1584</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>348.12</v>
-      </c>
-      <c r="C16" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D16" t="n">
-        <v>792</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>355.77</v>
-      </c>
-      <c r="C17" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D17" t="n">
-        <v>792</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>131.67</v>
-      </c>
-      <c r="C18" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D18" t="n">
-        <v>792</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>36.72</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>13.41</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shaheed Benazirabad | Mode: Vul</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>2176.51</v>
-      </c>
-      <c r="C5" t="n">
-        <v>510602.4</v>
-      </c>
-      <c r="D5" t="n">
-        <v>241441.99</v>
-      </c>
-      <c r="E5" t="n">
-        <v>23824.8</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1080</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>7408.8</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>3530.81</v>
-      </c>
-      <c r="C6" t="n">
-        <v>483991.2</v>
-      </c>
-      <c r="D6" t="n">
-        <v>214223.72</v>
-      </c>
-      <c r="E6" t="n">
-        <v>17795.7</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G6" t="n">
-        <v>583.5</v>
-      </c>
-      <c r="H6" t="n">
-        <v>530.1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>8358.299999999999</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>3803.47</v>
-      </c>
-      <c r="C7" t="n">
-        <v>346752</v>
-      </c>
-      <c r="D7" t="n">
-        <v>173821.82</v>
-      </c>
-      <c r="E7" t="n">
-        <v>14740.11</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="G7" t="n">
-        <v>756</v>
-      </c>
-      <c r="H7" t="n">
-        <v>284.7</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>9000</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>4268.25</v>
-      </c>
-      <c r="C8" t="n">
-        <v>233856</v>
-      </c>
-      <c r="D8" t="n">
-        <v>135235.58</v>
-      </c>
-      <c r="E8" t="n">
-        <v>9713.879999999999</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1969.5</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>7455</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>4117.05</v>
-      </c>
-      <c r="C9" t="n">
-        <v>204624</v>
-      </c>
-      <c r="D9" t="n">
-        <v>129103.13</v>
-      </c>
-      <c r="E9" t="n">
-        <v>7227.9</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>3646.5</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>9792.9</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>2748.96</v>
-      </c>
-      <c r="C10" t="n">
-        <v>93240</v>
-      </c>
-      <c r="D10" t="n">
-        <v>63736.2</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1566</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" t="n">
-        <v>2790</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>5099.7</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>1942.56</v>
-      </c>
-      <c r="C11" t="n">
-        <v>35280</v>
-      </c>
-      <c r="D11" t="n">
-        <v>24906.42</v>
-      </c>
-      <c r="E11" t="n">
-        <v>368.82</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>450</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1170</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>1069.02</v>
-      </c>
-      <c r="C12" t="n">
-        <v>8568</v>
-      </c>
-      <c r="D12" t="n">
-        <v>6240.56</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>300</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>647.8200000000001</v>
-      </c>
-      <c r="C13" t="n">
-        <v>4536</v>
-      </c>
-      <c r="D13" t="n">
-        <v>3384.02</v>
-      </c>
-      <c r="E13" t="n">
-        <v>476.28</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>447.84</v>
-      </c>
-      <c r="C14" t="n">
-        <v>2520</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1924.56</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>295.65</v>
-      </c>
-      <c r="C15" t="n">
-        <v>2016</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1561.82</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>348.12</v>
-      </c>
-      <c r="C16" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D16" t="n">
-        <v>792</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>355.77</v>
-      </c>
-      <c r="C17" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D17" t="n">
-        <v>792</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>131.67</v>
-      </c>
-      <c r="C18" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D18" t="n">
-        <v>792</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>36.72</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>13.41</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shaheed Benazirabad | Mode: Dmg</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>4788323.1</v>
-      </c>
-      <c r="C5" t="n">
-        <v>28083132</v>
-      </c>
-      <c r="D5" t="n">
-        <v>24465317.05</v>
-      </c>
-      <c r="E5" t="n">
-        <v>4389481.15</v>
-      </c>
-      <c r="F5" t="n">
-        <v>6666.72</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>298782</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>17499.9</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>69790.89999999999</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>7767777.6</v>
-      </c>
-      <c r="C6" t="n">
-        <v>26619516</v>
-      </c>
-      <c r="D6" t="n">
-        <v>21707289.95</v>
-      </c>
-      <c r="E6" t="n">
-        <v>3278679.77</v>
-      </c>
-      <c r="F6" t="n">
-        <v>25000.2</v>
-      </c>
-      <c r="G6" t="n">
-        <v>10794.75</v>
-      </c>
-      <c r="H6" t="n">
-        <v>146652.16</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>78735.19</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>8367628.5</v>
-      </c>
-      <c r="C7" t="n">
-        <v>19071360</v>
-      </c>
-      <c r="D7" t="n">
-        <v>17613365.43</v>
-      </c>
-      <c r="E7" t="n">
-        <v>2715717.87</v>
-      </c>
-      <c r="F7" t="n">
-        <v>50000.4</v>
-      </c>
-      <c r="G7" t="n">
-        <v>13986</v>
-      </c>
-      <c r="H7" t="n">
-        <v>78762.25</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>84780</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>9390150</v>
-      </c>
-      <c r="C8" t="n">
-        <v>12862080</v>
-      </c>
-      <c r="D8" t="n">
-        <v>13703421.73</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1789685.25</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>36435.75</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>70226.10000000001</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>9057510</v>
-      </c>
-      <c r="C9" t="n">
-        <v>11254320</v>
-      </c>
-      <c r="D9" t="n">
-        <v>13082019.96</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1331668.3</v>
-      </c>
-      <c r="F9" t="n">
-        <v>41667</v>
-      </c>
-      <c r="G9" t="n">
-        <v>67460.25</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>92249.12</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>6047712</v>
-      </c>
-      <c r="C10" t="n">
-        <v>5128200</v>
-      </c>
-      <c r="D10" t="n">
-        <v>6458389.15</v>
-      </c>
-      <c r="E10" t="n">
-        <v>288519.84</v>
-      </c>
-      <c r="F10" t="n">
-        <v>41667</v>
-      </c>
-      <c r="G10" t="n">
-        <v>51615</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>48039.17</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>4273632</v>
-      </c>
-      <c r="C11" t="n">
-        <v>1940400</v>
-      </c>
-      <c r="D11" t="n">
-        <v>2523767.54</v>
-      </c>
-      <c r="E11" t="n">
-        <v>67951.39999999999</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>8325</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>11021.4</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>2351844</v>
-      </c>
-      <c r="C12" t="n">
-        <v>471240</v>
-      </c>
-      <c r="D12" t="n">
-        <v>632356.35</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>5550</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>3391.2</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>1425204</v>
-      </c>
-      <c r="C13" t="n">
-        <v>249480</v>
-      </c>
-      <c r="D13" t="n">
-        <v>342902.54</v>
-      </c>
-      <c r="E13" t="n">
-        <v>87749.83</v>
-      </c>
-      <c r="F13" t="n">
-        <v>41667</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>985248</v>
-      </c>
-      <c r="C14" t="n">
-        <v>138600</v>
-      </c>
-      <c r="D14" t="n">
-        <v>195015.66</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>650430</v>
-      </c>
-      <c r="C15" t="n">
-        <v>110880</v>
-      </c>
-      <c r="D15" t="n">
-        <v>158259.63</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>41667</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>765864</v>
-      </c>
-      <c r="C16" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D16" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>782694</v>
-      </c>
-      <c r="C17" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D17" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>289674</v>
-      </c>
-      <c r="C18" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D18" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>80784</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>29502</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shikarpur | Mode: Exp</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>35635.14</v>
-      </c>
-      <c r="C4" t="n">
-        <v>3646440</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2865060</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1043100</v>
-      </c>
-      <c r="F4" t="n">
-        <v>35</v>
-      </c>
-      <c r="G4" t="n">
-        <v>107160</v>
-      </c>
-      <c r="H4" t="n">
-        <v>13650</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>4</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>343050</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>11607.3</v>
-      </c>
-      <c r="C5" t="n">
-        <v>782712</v>
-      </c>
-      <c r="D5" t="n">
-        <v>614988</v>
-      </c>
-      <c r="E5" t="n">
-        <v>241200</v>
-      </c>
-      <c r="F5" t="n">
-        <v>9</v>
-      </c>
-      <c r="G5" t="n">
-        <v>30300</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2910</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>110880</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>1142.55</v>
-      </c>
-      <c r="C6" t="n">
-        <v>109368</v>
-      </c>
-      <c r="D6" t="n">
-        <v>85932</v>
-      </c>
-      <c r="E6" t="n">
-        <v>31500</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>4110</v>
-      </c>
-      <c r="H6" t="n">
-        <v>330</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>18780</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>150.12</v>
-      </c>
-      <c r="C7" t="n">
-        <v>26712</v>
-      </c>
-      <c r="D7" t="n">
-        <v>20988</v>
-      </c>
-      <c r="E7" t="n">
-        <v>3600</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>780</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>2940</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>12.33</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D8" t="n">
-        <v>792</v>
-      </c>
-      <c r="E8" t="n">
-        <v>900</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>270</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>30</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>30</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shikarpur | Mode: Vul</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>5223.28</v>
-      </c>
-      <c r="C5" t="n">
-        <v>430491.6</v>
-      </c>
-      <c r="D5" t="n">
-        <v>203561.03</v>
-      </c>
-      <c r="E5" t="n">
-        <v>26604.36</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1047.6</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>23284.8</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>914.04</v>
-      </c>
-      <c r="C6" t="n">
-        <v>98431.2</v>
-      </c>
-      <c r="D6" t="n">
-        <v>43567.52</v>
-      </c>
-      <c r="E6" t="n">
-        <v>5323.5</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>205.5</v>
-      </c>
-      <c r="H6" t="n">
-        <v>188.1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>6948.6</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>142.61</v>
-      </c>
-      <c r="C7" t="n">
-        <v>26712</v>
-      </c>
-      <c r="D7" t="n">
-        <v>13390.34</v>
-      </c>
-      <c r="E7" t="n">
-        <v>765.72</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>117</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1764</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>12.33</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D8" t="n">
-        <v>582.91</v>
-      </c>
-      <c r="E8" t="n">
-        <v>220.77</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>175.5</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>340.8</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>48.6</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>30</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>160.2</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>90</v>
+        <v>847.8</v>
       </c>
     </row>
     <row r="12">
@@ -21876,938 +17210,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shikarpur | Mode: Dmg</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>11491227</v>
-      </c>
-      <c r="C5" t="n">
-        <v>23677038</v>
-      </c>
-      <c r="D5" t="n">
-        <v>20626838.97</v>
-      </c>
-      <c r="E5" t="n">
-        <v>4901587.29</v>
-      </c>
-      <c r="F5" t="n">
-        <v>7500.06</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>289818.54</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>219342.82</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>2010888</v>
-      </c>
-      <c r="C6" t="n">
-        <v>5413716</v>
-      </c>
-      <c r="D6" t="n">
-        <v>4414697.21</v>
-      </c>
-      <c r="E6" t="n">
-        <v>980801.64</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>3801.75</v>
-      </c>
-      <c r="H6" t="n">
-        <v>52037.86</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>65455.81</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>313750.8</v>
-      </c>
-      <c r="C7" t="n">
-        <v>1469160</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1356843.56</v>
-      </c>
-      <c r="E7" t="n">
-        <v>141076.25</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>2164.5</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>16616.88</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>27126</v>
-      </c>
-      <c r="C8" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D8" t="n">
-        <v>59066.47</v>
-      </c>
-      <c r="E8" t="n">
-        <v>40674.66</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>3246.75</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>3210.34</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>198</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>471.75</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>457.81</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>555</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1509.08</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>847.8</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/risk/Risk_Analysis_T3_100yrs_Future_Perfect.xlsx
+++ b/risk/Risk_Analysis_T3_100yrs_Future_Perfect.xlsx
@@ -538,7 +538,7 @@
         <v>59910</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J4" t="n">
         <v>40</v>
@@ -576,7 +576,7 @@
         <v>54420</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J5" t="n">
         <v>24</v>
@@ -614,7 +614,7 @@
         <v>45720</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>14</v>
@@ -652,7 +652,7 @@
         <v>43470</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
         <v>12</v>
@@ -690,7 +690,7 @@
         <v>26700</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J8" t="n">
         <v>8</v>
@@ -728,7 +728,7 @@
         <v>8040</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>5</v>
@@ -804,7 +804,7 @@
         <v>4800</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J11" t="n">
         <v>3</v>
@@ -918,7 +918,7 @@
         <v>810</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1660,7 +1660,7 @@
         <v>3510</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1736,7 +1736,7 @@
         <v>4440</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1850,7 +1850,7 @@
         <v>810</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -2592,7 +2592,7 @@
         <v>3510</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -2668,7 +2668,7 @@
         <v>4440</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -2782,7 +2782,7 @@
         <v>810</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -3524,7 +3524,7 @@
         <v>971041.5</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>337330.4</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
         <v>1228326</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>766660</v>
       </c>
       <c r="J11" t="n">
         <v>58333</v>
@@ -3714,7 +3714,7 @@
         <v>224086.5</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>383330</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -9858,7 +9858,7 @@
         <v>7140</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J4" t="n">
         <v>9</v>
@@ -9896,7 +9896,7 @@
         <v>6270</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J5" t="n">
         <v>10</v>
@@ -9934,7 +9934,7 @@
         <v>7710</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>6</v>
@@ -9972,7 +9972,7 @@
         <v>11760</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
@@ -10010,7 +10010,7 @@
         <v>2580</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J8" t="n">
         <v>2</v>
@@ -10124,7 +10124,7 @@
         <v>30</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -10828,7 +10828,7 @@
         <v>19591.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="J5" t="n">
         <v>7.2</v>
@@ -10866,7 +10866,7 @@
         <v>26060.4</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="J6" t="n">
         <v>7</v>
@@ -10904,7 +10904,7 @@
         <v>31733.1</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="J7" t="n">
         <v>8.4</v>
@@ -10942,7 +10942,7 @@
         <v>22695</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="J8" t="n">
         <v>6.8</v>
@@ -10980,7 +10980,7 @@
         <v>8040</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="J9" t="n">
         <v>4.75</v>
@@ -11056,7 +11056,7 @@
         <v>4800</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J11" t="n">
         <v>3</v>
@@ -11170,7 +11170,7 @@
         <v>810</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -11760,7 +11760,7 @@
         <v>2257.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="J5" t="n">
         <v>3</v>
@@ -11798,7 +11798,7 @@
         <v>4394.7</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="J6" t="n">
         <v>3</v>
@@ -11836,7 +11836,7 @@
         <v>8584.799999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="J7" t="n">
         <v>0.7</v>
@@ -11874,7 +11874,7 @@
         <v>2193</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="J8" t="n">
         <v>1.7</v>
@@ -11988,7 +11988,7 @@
         <v>30</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -12692,7 +12692,7 @@
         <v>624454.38</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>229998</v>
       </c>
       <c r="J5" t="n">
         <v>174999</v>
@@ -12730,7 +12730,7 @@
         <v>1215793.75</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>134165.5</v>
       </c>
       <c r="J6" t="n">
         <v>174999</v>
@@ -12768,7 +12768,7 @@
         <v>2374984.92</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>421663</v>
       </c>
       <c r="J7" t="n">
         <v>40833.1</v>
@@ -12806,7 +12806,7 @@
         <v>606693.45</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>551995.2</v>
       </c>
       <c r="J8" t="n">
         <v>99166.10000000001</v>
@@ -12920,7 +12920,7 @@
         <v>8299.5</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>383330</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -13586,7 +13586,7 @@
         <v>13650</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>4</v>
@@ -16420,7 +16420,7 @@
         <v>5419905.48</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>287497.5</v>
       </c>
       <c r="J5" t="n">
         <v>419997.6</v>
@@ -16458,7 +16458,7 @@
         <v>7209609.66</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>134165.5</v>
       </c>
       <c r="J6" t="n">
         <v>408331</v>
@@ -16496,7 +16496,7 @@
         <v>8778962.109999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>421663</v>
       </c>
       <c r="J7" t="n">
         <v>489997.2</v>
@@ -16534,7 +16534,7 @@
         <v>6278571.75</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>827992.8</v>
       </c>
       <c r="J8" t="n">
         <v>396664.4</v>
@@ -16572,7 +16572,7 @@
         <v>2224266</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>337330.4</v>
       </c>
       <c r="J9" t="n">
         <v>277081.75</v>
@@ -16648,7 +16648,7 @@
         <v>1327920</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1149990</v>
       </c>
       <c r="J11" t="n">
         <v>174999</v>
@@ -16762,7 +16762,7 @@
         <v>224086.5</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>383330</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -17314,7 +17314,7 @@
         <v>3120</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -17466,7 +17466,7 @@
         <v>19320</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>5</v>
@@ -18398,7 +18398,7 @@
         <v>16422</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="J8" t="n">
         <v>4.25</v>
@@ -19330,7 +19330,7 @@
         <v>4543146.3</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>275997.6</v>
       </c>
       <c r="J8" t="n">
         <v>247915.25</v>
@@ -20110,7 +20110,7 @@
         <v>17520</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>14</v>
@@ -20148,7 +20148,7 @@
         <v>22560</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>7</v>
@@ -21080,7 +21080,7 @@
         <v>8121.6</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="J5" t="n">
         <v>2.1</v>
@@ -22012,7 +22012,7 @@
         <v>2246840.64</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>57499.5</v>
       </c>
       <c r="J5" t="n">
         <v>122499.3</v>

--- a/risk/Risk_Analysis_T3_100yrs_Future_Perfect.xlsx
+++ b/risk/Risk_Analysis_T3_100yrs_Future_Perfect.xlsx
@@ -544,7 +544,7 @@
         <v>40</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1133</v>
       </c>
       <c r="L4" t="n">
         <v>1421940</v>
@@ -582,7 +582,7 @@
         <v>24</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>617</v>
       </c>
       <c r="L5" t="n">
         <v>892830</v>
@@ -620,7 +620,7 @@
         <v>14</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>432</v>
       </c>
       <c r="L6" t="n">
         <v>586080</v>
@@ -658,7 +658,7 @@
         <v>12</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>459</v>
       </c>
       <c r="L7" t="n">
         <v>540510</v>
@@ -696,7 +696,7 @@
         <v>8</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>357</v>
       </c>
       <c r="L8" t="n">
         <v>444000</v>
@@ -734,7 +734,7 @@
         <v>5</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>334</v>
       </c>
       <c r="L9" t="n">
         <v>377790</v>
@@ -772,7 +772,7 @@
         <v>11</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>257</v>
       </c>
       <c r="L10" t="n">
         <v>288450</v>
@@ -810,7 +810,7 @@
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>167</v>
       </c>
       <c r="L11" t="n">
         <v>181290</v>
@@ -848,7 +848,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="L12" t="n">
         <v>149640</v>
@@ -886,7 +886,7 @@
         <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="L13" t="n">
         <v>95400</v>
@@ -924,7 +924,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="L14" t="n">
         <v>41310</v>
@@ -962,7 +962,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L15" t="n">
         <v>16170</v>
@@ -1000,7 +1000,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L16" t="n">
         <v>7050</v>
@@ -1038,7 +1038,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>2280</v>
@@ -1476,7 +1476,7 @@
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L4" t="n">
         <v>16950</v>
@@ -1514,7 +1514,7 @@
         <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L5" t="n">
         <v>21270</v>
@@ -1552,7 +1552,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="L6" t="n">
         <v>22680</v>
@@ -1590,7 +1590,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L7" t="n">
         <v>27840</v>
@@ -1628,7 +1628,7 @@
         <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="L8" t="n">
         <v>37590</v>
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L9" t="n">
         <v>46890</v>
@@ -1704,7 +1704,7 @@
         <v>5</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="L10" t="n">
         <v>44040</v>
@@ -1742,7 +1742,7 @@
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="L11" t="n">
         <v>57720</v>
@@ -1780,7 +1780,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="L12" t="n">
         <v>92490</v>
@@ -1818,7 +1818,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="L13" t="n">
         <v>67470</v>
@@ -1856,7 +1856,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="L14" t="n">
         <v>32280</v>
@@ -1894,7 +1894,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L15" t="n">
         <v>13140</v>
@@ -1932,7 +1932,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L16" t="n">
         <v>5820</v>
@@ -2446,7 +2446,7 @@
         <v>0.6</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="L5" t="n">
         <v>4466.7</v>
@@ -2484,7 +2484,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>13.65</v>
       </c>
       <c r="L6" t="n">
         <v>8391.6</v>
@@ -2522,7 +2522,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>16.4</v>
       </c>
       <c r="L7" t="n">
         <v>16704</v>
@@ -2560,7 +2560,7 @@
         <v>0.85</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>18.9</v>
       </c>
       <c r="L8" t="n">
         <v>26688.9</v>
@@ -2598,7 +2598,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L9" t="n">
         <v>37980.9</v>
@@ -2636,7 +2636,7 @@
         <v>5</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="L10" t="n">
         <v>39195.6</v>
@@ -2674,7 +2674,7 @@
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="L11" t="n">
         <v>57720</v>
@@ -2712,7 +2712,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="L12" t="n">
         <v>92490</v>
@@ -2750,7 +2750,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="L13" t="n">
         <v>67470</v>
@@ -2788,7 +2788,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="L14" t="n">
         <v>32280</v>
@@ -2826,7 +2826,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L15" t="n">
         <v>13140</v>
@@ -2864,7 +2864,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L16" t="n">
         <v>5820</v>
@@ -3378,7 +3378,7 @@
         <v>34999.8</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>62721.96</v>
       </c>
       <c r="L5" t="n">
         <v>42076.31</v>
@@ -3416,7 +3416,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>291209.1</v>
       </c>
       <c r="L6" t="n">
         <v>79048.87</v>
@@ -3454,7 +3454,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>349877.6</v>
       </c>
       <c r="L7" t="n">
         <v>157351.68</v>
@@ -3492,7 +3492,7 @@
         <v>49583.05</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>403212.6</v>
       </c>
       <c r="L8" t="n">
         <v>251409.44</v>
@@ -3530,7 +3530,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>533350</v>
       </c>
       <c r="L9" t="n">
         <v>357780.08</v>
@@ -3568,7 +3568,7 @@
         <v>291665</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>405346</v>
       </c>
       <c r="L10" t="n">
         <v>369222.55</v>
@@ -3606,7 +3606,7 @@
         <v>58333</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>704022</v>
       </c>
       <c r="L11" t="n">
         <v>543722.4</v>
@@ -3644,7 +3644,7 @@
         <v>58333</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>768024</v>
       </c>
       <c r="L12" t="n">
         <v>871255.8</v>
@@ -3682,7 +3682,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>704022</v>
       </c>
       <c r="L13" t="n">
         <v>635567.4</v>
@@ -3720,7 +3720,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>405346</v>
       </c>
       <c r="L14" t="n">
         <v>304077.6</v>
@@ -3758,7 +3758,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>213340</v>
       </c>
       <c r="L15" t="n">
         <v>123778.8</v>
@@ -3796,7 +3796,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>64002</v>
       </c>
       <c r="L16" t="n">
         <v>54824.4</v>
@@ -4272,7 +4272,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="L4" t="n">
         <v>144780</v>
@@ -4310,7 +4310,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="L5" t="n">
         <v>57810</v>
@@ -4348,7 +4348,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>11280</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
         <v>3090</v>
@@ -5242,7 +5242,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>12.18</v>
       </c>
       <c r="L5" t="n">
         <v>12140.1</v>
@@ -5280,7 +5280,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="L6" t="n">
         <v>4173.6</v>
@@ -5318,7 +5318,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="L7" t="n">
         <v>1854</v>
@@ -6174,7 +6174,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>259848.12</v>
       </c>
       <c r="L5" t="n">
         <v>114359.74</v>
@@ -6212,7 +6212,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>13867.1</v>
       </c>
       <c r="L6" t="n">
         <v>39315.31</v>
@@ -6250,7 +6250,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>17493.88</v>
       </c>
       <c r="L7" t="n">
         <v>17464.68</v>
@@ -7068,7 +7068,7 @@
         <v>10</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="L4" t="n">
         <v>138090</v>
@@ -7106,7 +7106,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="L5" t="n">
         <v>48090</v>
@@ -7144,7 +7144,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L6" t="n">
         <v>13800</v>
@@ -7182,7 +7182,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L7" t="n">
         <v>3780</v>
@@ -7220,7 +7220,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L8" t="n">
         <v>2040</v>
@@ -8038,7 +8038,7 @@
         <v>0.3</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>20.16</v>
       </c>
       <c r="L5" t="n">
         <v>10098.9</v>
@@ -8076,7 +8076,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="L6" t="n">
         <v>5106</v>
@@ -8114,7 +8114,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="L7" t="n">
         <v>2268</v>
@@ -8152,7 +8152,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="L8" t="n">
         <v>1448.4</v>
@@ -8970,7 +8970,7 @@
         <v>17499.9</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>430093.44</v>
       </c>
       <c r="L5" t="n">
         <v>95131.64</v>
@@ -9008,7 +9008,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>124803.9</v>
       </c>
       <c r="L6" t="n">
         <v>48098.52</v>
@@ -9046,7 +9046,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>34987.76</v>
       </c>
       <c r="L7" t="n">
         <v>21364.56</v>
@@ -9084,7 +9084,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>38401.2</v>
       </c>
       <c r="L8" t="n">
         <v>13643.93</v>
@@ -9864,7 +9864,7 @@
         <v>9</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>232</v>
       </c>
       <c r="L4" t="n">
         <v>172110</v>
@@ -9902,7 +9902,7 @@
         <v>10</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>157</v>
       </c>
       <c r="L5" t="n">
         <v>164670</v>
@@ -9940,7 +9940,7 @@
         <v>6</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="L6" t="n">
         <v>158730</v>
@@ -9978,7 +9978,7 @@
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>208</v>
       </c>
       <c r="L7" t="n">
         <v>202800</v>
@@ -10016,7 +10016,7 @@
         <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="L8" t="n">
         <v>124770</v>
@@ -10054,7 +10054,7 @@
         <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L9" t="n">
         <v>72870</v>
@@ -10092,7 +10092,7 @@
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L10" t="n">
         <v>38340</v>
@@ -10130,7 +10130,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L11" t="n">
         <v>9390</v>
@@ -10168,7 +10168,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L12" t="n">
         <v>4500</v>
@@ -10834,7 +10834,7 @@
         <v>7.2</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>259.14</v>
       </c>
       <c r="L5" t="n">
         <v>187494.3</v>
@@ -10872,7 +10872,7 @@
         <v>7</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>280.8</v>
       </c>
       <c r="L6" t="n">
         <v>216849.6</v>
@@ -10910,7 +10910,7 @@
         <v>8.4</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>376.38</v>
       </c>
       <c r="L7" t="n">
         <v>324306</v>
@@ -10948,7 +10948,7 @@
         <v>6.8</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>321.3</v>
       </c>
       <c r="L8" t="n">
         <v>315240</v>
@@ -10986,7 +10986,7 @@
         <v>4.75</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>334</v>
       </c>
       <c r="L9" t="n">
         <v>306009.9</v>
@@ -11024,7 +11024,7 @@
         <v>11</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>257</v>
       </c>
       <c r="L10" t="n">
         <v>256720.5</v>
@@ -11062,7 +11062,7 @@
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>167</v>
       </c>
       <c r="L11" t="n">
         <v>181290</v>
@@ -11100,7 +11100,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="L12" t="n">
         <v>149640</v>
@@ -11138,7 +11138,7 @@
         <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="L13" t="n">
         <v>95400</v>
@@ -11176,7 +11176,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="L14" t="n">
         <v>41310</v>
@@ -11214,7 +11214,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L15" t="n">
         <v>16170</v>
@@ -11252,7 +11252,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L16" t="n">
         <v>7050</v>
@@ -11290,7 +11290,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>2280</v>
@@ -11766,7 +11766,7 @@
         <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>65.94</v>
       </c>
       <c r="L5" t="n">
         <v>34580.7</v>
@@ -11804,7 +11804,7 @@
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>98.15000000000001</v>
       </c>
       <c r="L6" t="n">
         <v>58730.1</v>
@@ -11842,7 +11842,7 @@
         <v>0.7</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>170.56</v>
       </c>
       <c r="L7" t="n">
         <v>121680</v>
@@ -11880,7 +11880,7 @@
         <v>1.7</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>109.8</v>
       </c>
       <c r="L8" t="n">
         <v>88586.7</v>
@@ -11918,7 +11918,7 @@
         <v>1.9</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L9" t="n">
         <v>59024.7</v>
@@ -11956,7 +11956,7 @@
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L10" t="n">
         <v>34122.6</v>
@@ -11994,7 +11994,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L11" t="n">
         <v>9390</v>
@@ -12032,7 +12032,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L12" t="n">
         <v>4500</v>
@@ -12698,7 +12698,7 @@
         <v>174999</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1406763.96</v>
       </c>
       <c r="L5" t="n">
         <v>325750.19</v>
@@ -12736,7 +12736,7 @@
         <v>174999</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>2093932.1</v>
       </c>
       <c r="L6" t="n">
         <v>553237.54</v>
@@ -12774,7 +12774,7 @@
         <v>40833.1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>3638727.04</v>
       </c>
       <c r="L7" t="n">
         <v>1146225.6</v>
@@ -12812,7 +12812,7 @@
         <v>99166.10000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>2342473.2</v>
       </c>
       <c r="L8" t="n">
         <v>834486.71</v>
@@ -12850,7 +12850,7 @@
         <v>110832.7</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1920060</v>
       </c>
       <c r="L9" t="n">
         <v>556012.67</v>
@@ -12888,7 +12888,7 @@
         <v>58333</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>938696</v>
       </c>
       <c r="L10" t="n">
         <v>321434.89</v>
@@ -12926,7 +12926,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>106670</v>
       </c>
       <c r="L11" t="n">
         <v>88453.8</v>
@@ -12964,7 +12964,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>42668</v>
       </c>
       <c r="L12" t="n">
         <v>42390</v>
@@ -13592,7 +13592,7 @@
         <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="L4" t="n">
         <v>343050</v>
@@ -13630,7 +13630,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="L5" t="n">
         <v>110880</v>
@@ -14562,7 +14562,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>13.44</v>
       </c>
       <c r="L5" t="n">
         <v>23284.8</v>
@@ -15494,7 +15494,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>286728.96</v>
       </c>
       <c r="L5" t="n">
         <v>219342.82</v>
@@ -16426,7 +16426,7 @@
         <v>419997.6</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>5528492.76</v>
       </c>
       <c r="L5" t="n">
         <v>1766196.31</v>
@@ -16464,7 +16464,7 @@
         <v>408331</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>5990587.2</v>
       </c>
       <c r="L6" t="n">
         <v>2042723.23</v>
@@ -16502,7 +16502,7 @@
         <v>489997.2</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>8029690.92</v>
       </c>
       <c r="L7" t="n">
         <v>3054962.52</v>
@@ -16540,7 +16540,7 @@
         <v>396664.4</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>6854614.2</v>
       </c>
       <c r="L8" t="n">
         <v>2969560.8</v>
@@ -16578,7 +16578,7 @@
         <v>277081.75</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>7125556</v>
       </c>
       <c r="L9" t="n">
         <v>2882613.26</v>
@@ -16616,7 +16616,7 @@
         <v>641663</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>5482838</v>
       </c>
       <c r="L10" t="n">
         <v>2418307.11</v>
@@ -16654,7 +16654,7 @@
         <v>174999</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>3562778</v>
       </c>
       <c r="L11" t="n">
         <v>1707751.8</v>
@@ -16692,7 +16692,7 @@
         <v>58333</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>2197402</v>
       </c>
       <c r="L12" t="n">
         <v>1409608.8</v>
@@ -16730,7 +16730,7 @@
         <v>174999</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1194704</v>
       </c>
       <c r="L13" t="n">
         <v>898668</v>
@@ -16768,7 +16768,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>576018</v>
       </c>
       <c r="L14" t="n">
         <v>389140.2</v>
@@ -16806,7 +16806,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>213340</v>
       </c>
       <c r="L15" t="n">
         <v>152321.4</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>85336</v>
       </c>
       <c r="L16" t="n">
         <v>66411</v>
@@ -16882,7 +16882,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L17" t="n">
         <v>21477.6</v>
@@ -17320,7 +17320,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="L4" t="n">
         <v>140160</v>
@@ -17358,7 +17358,7 @@
         <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="L5" t="n">
         <v>166890</v>
@@ -17396,7 +17396,7 @@
         <v>5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="L6" t="n">
         <v>173760</v>
@@ -17434,7 +17434,7 @@
         <v>8</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="L7" t="n">
         <v>185340</v>
@@ -17472,7 +17472,7 @@
         <v>5</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>203</v>
       </c>
       <c r="L8" t="n">
         <v>240090</v>
@@ -17510,7 +17510,7 @@
         <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="L9" t="n">
         <v>240450</v>
@@ -17548,7 +17548,7 @@
         <v>5</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>193</v>
       </c>
       <c r="L10" t="n">
         <v>198150</v>
@@ -17586,7 +17586,7 @@
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="L11" t="n">
         <v>111960</v>
@@ -17624,7 +17624,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="L12" t="n">
         <v>51810</v>
@@ -17662,7 +17662,7 @@
         <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="L13" t="n">
         <v>24930</v>
@@ -17700,7 +17700,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L14" t="n">
         <v>7650</v>
@@ -17776,7 +17776,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
         <v>960</v>
@@ -17814,7 +17814,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>120</v>
@@ -18290,7 +18290,7 @@
         <v>0.6</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>64.26000000000001</v>
       </c>
       <c r="L5" t="n">
         <v>35046.9</v>
@@ -18328,7 +18328,7 @@
         <v>2.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>91.65000000000001</v>
       </c>
       <c r="L6" t="n">
         <v>64291.2</v>
@@ -18366,7 +18366,7 @@
         <v>5.6</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>124.64</v>
       </c>
       <c r="L7" t="n">
         <v>111204</v>
@@ -18404,7 +18404,7 @@
         <v>4.25</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>182.7</v>
       </c>
       <c r="L8" t="n">
         <v>170463.9</v>
@@ -18442,7 +18442,7 @@
         <v>2.85</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="L9" t="n">
         <v>194764.5</v>
@@ -18480,7 +18480,7 @@
         <v>5</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>193</v>
       </c>
       <c r="L10" t="n">
         <v>176353.5</v>
@@ -18518,7 +18518,7 @@
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="L11" t="n">
         <v>111960</v>
@@ -18556,7 +18556,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="L12" t="n">
         <v>51810</v>
@@ -18594,7 +18594,7 @@
         <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="L13" t="n">
         <v>24930</v>
@@ -18632,7 +18632,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L14" t="n">
         <v>7650</v>
@@ -18708,7 +18708,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
         <v>960</v>
@@ -18746,7 +18746,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>120</v>
@@ -19222,7 +19222,7 @@
         <v>34999.8</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1370922.84</v>
       </c>
       <c r="L5" t="n">
         <v>330141.8</v>
@@ -19260,7 +19260,7 @@
         <v>145832.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1955261.1</v>
       </c>
       <c r="L6" t="n">
         <v>605623.1</v>
@@ -19298,7 +19298,7 @@
         <v>326664.8</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>2659069.76</v>
       </c>
       <c r="L7" t="n">
         <v>1047541.68</v>
@@ -19336,7 +19336,7 @@
         <v>247915.25</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>3897721.8</v>
       </c>
       <c r="L8" t="n">
         <v>1605769.94</v>
@@ -19374,7 +19374,7 @@
         <v>166249.05</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>4608144</v>
       </c>
       <c r="L9" t="n">
         <v>1834681.59</v>
@@ -19412,7 +19412,7 @@
         <v>291665</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>4117462</v>
       </c>
       <c r="L10" t="n">
         <v>1661249.97</v>
@@ -19450,7 +19450,7 @@
         <v>116666</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>2752086</v>
       </c>
       <c r="L11" t="n">
         <v>1054663.2</v>
@@ -19488,7 +19488,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1386710</v>
       </c>
       <c r="L12" t="n">
         <v>488050.2</v>
@@ -19526,7 +19526,7 @@
         <v>174999</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>469348</v>
       </c>
       <c r="L13" t="n">
         <v>234840.6</v>
@@ -19564,7 +19564,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>170672</v>
       </c>
       <c r="L14" t="n">
         <v>72063</v>
@@ -19640,7 +19640,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L16" t="n">
         <v>9043.200000000001</v>
@@ -19678,7 +19678,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L17" t="n">
         <v>1130.4</v>
@@ -20116,7 +20116,7 @@
         <v>14</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>387</v>
       </c>
       <c r="L4" t="n">
         <v>408240</v>
@@ -20154,7 +20154,7 @@
         <v>7</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="L5" t="n">
         <v>261990</v>
@@ -20192,7 +20192,7 @@
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="L6" t="n">
         <v>134700</v>
@@ -20230,7 +20230,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="L7" t="n">
         <v>79020</v>
@@ -20268,7 +20268,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L8" t="n">
         <v>21780</v>
@@ -21086,7 +21086,7 @@
         <v>2.1</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>79.8</v>
       </c>
       <c r="L5" t="n">
         <v>55017.9</v>
@@ -21124,7 +21124,7 @@
         <v>1.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>70.2</v>
       </c>
       <c r="L6" t="n">
         <v>49839</v>
@@ -21162,7 +21162,7 @@
         <v>2.1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>60.68</v>
       </c>
       <c r="L7" t="n">
         <v>47412</v>
@@ -21200,7 +21200,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="L8" t="n">
         <v>15463.8</v>
@@ -22018,7 +22018,7 @@
         <v>122499.3</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1702453.2</v>
       </c>
       <c r="L5" t="n">
         <v>518268.62</v>
@@ -22056,7 +22056,7 @@
         <v>87499.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1497646.8</v>
       </c>
       <c r="L6" t="n">
         <v>469483.38</v>
@@ -22094,7 +22094,7 @@
         <v>122499.3</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1294547.12</v>
       </c>
       <c r="L7" t="n">
         <v>446621.04</v>
@@ -22132,7 +22132,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>172805.4</v>
       </c>
       <c r="L8" t="n">
         <v>145669</v>

--- a/risk/Risk_Analysis_T3_100yrs_Future_Perfect.xlsx
+++ b/risk/Risk_Analysis_T3_100yrs_Future_Perfect.xlsx
@@ -549,7 +549,7 @@
         <v>40</v>
       </c>
       <c r="K4" t="n">
-        <v>1114</v>
+        <v>436</v>
       </c>
       <c r="L4" t="n">
         <v>1418850</v>
@@ -590,7 +590,7 @@
         <v>24</v>
       </c>
       <c r="K5" t="n">
-        <v>604</v>
+        <v>256</v>
       </c>
       <c r="L5" t="n">
         <v>890880</v>
@@ -631,7 +631,7 @@
         <v>14</v>
       </c>
       <c r="K6" t="n">
-        <v>427</v>
+        <v>165</v>
       </c>
       <c r="L6" t="n">
         <v>584340</v>
@@ -672,7 +672,7 @@
         <v>12</v>
       </c>
       <c r="K7" t="n">
-        <v>458</v>
+        <v>155</v>
       </c>
       <c r="L7" t="n">
         <v>539460</v>
@@ -713,7 +713,7 @@
         <v>8</v>
       </c>
       <c r="K8" t="n">
-        <v>357</v>
+        <v>101</v>
       </c>
       <c r="L8" t="n">
         <v>443280</v>
@@ -754,7 +754,7 @@
         <v>5</v>
       </c>
       <c r="K9" t="n">
-        <v>334</v>
+        <v>110</v>
       </c>
       <c r="L9" t="n">
         <v>377430</v>
@@ -795,7 +795,7 @@
         <v>11</v>
       </c>
       <c r="K10" t="n">
-        <v>257</v>
+        <v>57</v>
       </c>
       <c r="L10" t="n">
         <v>288360</v>
@@ -836,7 +836,7 @@
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>167</v>
+        <v>34</v>
       </c>
       <c r="L11" t="n">
         <v>181020</v>
@@ -877,7 +877,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>103</v>
+        <v>12</v>
       </c>
       <c r="L12" t="n">
         <v>149430</v>
@@ -918,7 +918,7 @@
         <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>56</v>
+        <v>6</v>
       </c>
       <c r="L13" t="n">
         <v>95400</v>
@@ -959,7 +959,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
         <v>41310</v>
@@ -1000,7 +1000,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>16170</v>
@@ -1041,7 +1041,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>7050</v>
@@ -1082,7 +1082,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>2280</v>
@@ -1553,7 +1553,7 @@
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L4" t="n">
         <v>17100</v>
@@ -1594,7 +1594,7 @@
         <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L5" t="n">
         <v>21240</v>
@@ -1635,7 +1635,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="L6" t="n">
         <v>22740</v>
@@ -1676,7 +1676,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="L7" t="n">
         <v>27960</v>
@@ -1717,7 +1717,7 @@
         <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="L8" t="n">
         <v>37800</v>
@@ -1758,7 +1758,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="L9" t="n">
         <v>47010</v>
@@ -1799,7 +1799,7 @@
         <v>5</v>
       </c>
       <c r="K10" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="L10" t="n">
         <v>44070</v>
@@ -1840,7 +1840,7 @@
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="L11" t="n">
         <v>57960</v>
@@ -1881,7 +1881,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="L12" t="n">
         <v>92610</v>
@@ -1922,7 +1922,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="L13" t="n">
         <v>67530</v>
@@ -1963,7 +1963,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
         <v>32340</v>
@@ -2004,7 +2004,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>13170</v>
@@ -2045,7 +2045,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>5820</v>
@@ -2598,7 +2598,7 @@
         <v>0.6</v>
       </c>
       <c r="K5" t="n">
-        <v>1.99</v>
+        <v>0.99</v>
       </c>
       <c r="L5" t="n">
         <v>4460.4</v>
@@ -2639,7 +2639,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>10.65</v>
+        <v>4.56</v>
       </c>
       <c r="L6" t="n">
         <v>8413.799999999999</v>
@@ -2680,7 +2680,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>12.76</v>
+        <v>6.38</v>
       </c>
       <c r="L7" t="n">
         <v>16776</v>
@@ -2721,7 +2721,7 @@
         <v>0.85</v>
       </c>
       <c r="K8" t="n">
-        <v>15.46</v>
+        <v>8.83</v>
       </c>
       <c r="L8" t="n">
         <v>26838</v>
@@ -2762,7 +2762,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>20.08</v>
+        <v>7.23</v>
       </c>
       <c r="L9" t="n">
         <v>38078.1</v>
@@ -2803,7 +2803,7 @@
         <v>5</v>
       </c>
       <c r="K10" t="n">
-        <v>16.53</v>
+        <v>2.61</v>
       </c>
       <c r="L10" t="n">
         <v>39222.3</v>
@@ -2844,7 +2844,7 @@
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>29.65</v>
+        <v>3.59</v>
       </c>
       <c r="L11" t="n">
         <v>57960</v>
@@ -2885,7 +2885,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>33.37</v>
+        <v>3.71</v>
       </c>
       <c r="L12" t="n">
         <v>92610</v>
@@ -2926,7 +2926,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>31.33</v>
+        <v>4.75</v>
       </c>
       <c r="L13" t="n">
         <v>67530</v>
@@ -2967,7 +2967,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>18.47</v>
+        <v>0.97</v>
       </c>
       <c r="L14" t="n">
         <v>32340</v>
@@ -3008,7 +3008,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>9.859999999999999</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>13170</v>
@@ -3049,7 +3049,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>5820</v>
@@ -3602,7 +3602,7 @@
         <v>14566.8</v>
       </c>
       <c r="K5" t="n">
-        <v>96432.22</v>
+        <v>48216.11</v>
       </c>
       <c r="L5" t="n">
         <v>802872</v>
@@ -3643,7 +3643,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>516975.73</v>
+        <v>221561.03</v>
       </c>
       <c r="L6" t="n">
         <v>1514484</v>
@@ -3684,7 +3684,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>619574.5600000001</v>
+        <v>309787.28</v>
       </c>
       <c r="L7" t="n">
         <v>3019680</v>
@@ -3725,7 +3725,7 @@
         <v>20636.3</v>
       </c>
       <c r="K8" t="n">
-        <v>750481.54</v>
+        <v>428846.59</v>
       </c>
       <c r="L8" t="n">
         <v>4830840</v>
@@ -3766,7 +3766,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>974761.7</v>
+        <v>350914.21</v>
       </c>
       <c r="L9" t="n">
         <v>6854058</v>
@@ -3807,7 +3807,7 @@
         <v>121390</v>
       </c>
       <c r="K10" t="n">
-        <v>802630.6800000001</v>
+        <v>126731.16</v>
       </c>
       <c r="L10" t="n">
         <v>7060014</v>
@@ -3848,7 +3848,7 @@
         <v>24278</v>
       </c>
       <c r="K11" t="n">
-        <v>1439709.68</v>
+        <v>174510.26</v>
       </c>
       <c r="L11" t="n">
         <v>10432800</v>
@@ -3889,7 +3889,7 @@
         <v>24278</v>
       </c>
       <c r="K12" t="n">
-        <v>1620410.83</v>
+        <v>180045.65</v>
       </c>
       <c r="L12" t="n">
         <v>16669800</v>
@@ -3930,7 +3930,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>1521429.43</v>
+        <v>230519.61</v>
       </c>
       <c r="L13" t="n">
         <v>12155400</v>
@@ -3971,7 +3971,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>896732.21</v>
+        <v>47196.43</v>
       </c>
       <c r="L14" t="n">
         <v>5821200</v>
@@ -4012,7 +4012,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>478762.16</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>2370600</v>
@@ -4053,7 +4053,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>145668</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>1047600</v>
@@ -4565,7 +4565,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="L4" t="n">
         <v>144660</v>
@@ -4606,7 +4606,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="L5" t="n">
         <v>58500</v>
@@ -4647,7 +4647,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>11220</v>
@@ -5610,7 +5610,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>9.6</v>
+        <v>4.96</v>
       </c>
       <c r="L5" t="n">
         <v>12285</v>
@@ -5651,7 +5651,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.51</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>4151.4</v>
@@ -6614,7 +6614,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>466089.04</v>
+        <v>241080.54</v>
       </c>
       <c r="L5" t="n">
         <v>2211300</v>
@@ -6655,7 +6655,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>24617.89</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>747252</v>
@@ -7577,7 +7577,7 @@
         <v>10</v>
       </c>
       <c r="K4" t="n">
-        <v>175</v>
+        <v>37</v>
       </c>
       <c r="L4" t="n">
         <v>138300</v>
@@ -7618,7 +7618,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="L5" t="n">
         <v>48660</v>
@@ -7659,7 +7659,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>13890</v>
@@ -7700,7 +7700,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>3780</v>
@@ -7741,7 +7741,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>2040</v>
@@ -8622,7 +8622,7 @@
         <v>0.3</v>
       </c>
       <c r="K5" t="n">
-        <v>15.89</v>
+        <v>3.64</v>
       </c>
       <c r="L5" t="n">
         <v>10218.6</v>
@@ -8663,7 +8663,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>5139.3</v>
@@ -8704,7 +8704,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>2268</v>
@@ -8745,7 +8745,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>1448.4</v>
@@ -9626,7 +9626,7 @@
         <v>7283.4</v>
       </c>
       <c r="K5" t="n">
-        <v>771457.73</v>
+        <v>176792.4</v>
       </c>
       <c r="L5" t="n">
         <v>1839348</v>
@@ -9667,7 +9667,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>221561.03</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>925074</v>
@@ -9708,7 +9708,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>61957.46</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>408240</v>
@@ -9749,7 +9749,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>71474.42999999999</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>260712</v>
@@ -10589,7 +10589,7 @@
         <v>9</v>
       </c>
       <c r="K4" t="n">
-        <v>232</v>
+        <v>134</v>
       </c>
       <c r="L4" t="n">
         <v>172500</v>
@@ -10630,7 +10630,7 @@
         <v>10</v>
       </c>
       <c r="K5" t="n">
-        <v>157</v>
+        <v>84</v>
       </c>
       <c r="L5" t="n">
         <v>164760</v>
@@ -10671,7 +10671,7 @@
         <v>6</v>
       </c>
       <c r="K6" t="n">
-        <v>151</v>
+        <v>75</v>
       </c>
       <c r="L6" t="n">
         <v>158820</v>
@@ -10712,7 +10712,7 @@
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>208</v>
+        <v>73</v>
       </c>
       <c r="L7" t="n">
         <v>202890</v>
@@ -10753,7 +10753,7 @@
         <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>122</v>
+        <v>40</v>
       </c>
       <c r="L8" t="n">
         <v>124800</v>
@@ -10794,7 +10794,7 @@
         <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>90</v>
+        <v>34</v>
       </c>
       <c r="L9" t="n">
         <v>72930</v>
@@ -10835,7 +10835,7 @@
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="L10" t="n">
         <v>38340</v>
@@ -10876,7 +10876,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L11" t="n">
         <v>9390</v>
@@ -11634,7 +11634,7 @@
         <v>7.2</v>
       </c>
       <c r="K5" t="n">
-        <v>199.92</v>
+        <v>84.73999999999999</v>
       </c>
       <c r="L5" t="n">
         <v>187084.8</v>
@@ -11675,7 +11675,7 @@
         <v>7</v>
       </c>
       <c r="K6" t="n">
-        <v>216.49</v>
+        <v>83.66</v>
       </c>
       <c r="L6" t="n">
         <v>216205.8</v>
@@ -11716,7 +11716,7 @@
         <v>8.4</v>
       </c>
       <c r="K7" t="n">
-        <v>292.2</v>
+        <v>98.89</v>
       </c>
       <c r="L7" t="n">
         <v>323676</v>
@@ -11757,7 +11757,7 @@
         <v>6.8</v>
       </c>
       <c r="K8" t="n">
-        <v>262.75</v>
+        <v>74.34</v>
       </c>
       <c r="L8" t="n">
         <v>314728.8</v>
@@ -11798,7 +11798,7 @@
         <v>4.75</v>
       </c>
       <c r="K9" t="n">
-        <v>268.2</v>
+        <v>88.33</v>
       </c>
       <c r="L9" t="n">
         <v>305718.3</v>
@@ -11839,7 +11839,7 @@
         <v>11</v>
       </c>
       <c r="K10" t="n">
-        <v>223.59</v>
+        <v>49.59</v>
       </c>
       <c r="L10" t="n">
         <v>256640.4</v>
@@ -11880,7 +11880,7 @@
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>150.05</v>
+        <v>30.55</v>
       </c>
       <c r="L11" t="n">
         <v>181020</v>
@@ -11921,7 +11921,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>95.48</v>
+        <v>11.12</v>
       </c>
       <c r="L12" t="n">
         <v>149430</v>
@@ -11962,7 +11962,7 @@
         <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>53.17</v>
+        <v>5.7</v>
       </c>
       <c r="L13" t="n">
         <v>95400</v>
@@ -12003,7 +12003,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>26.24</v>
+        <v>0.97</v>
       </c>
       <c r="L14" t="n">
         <v>41310</v>
@@ -12044,7 +12044,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>9.859999999999999</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>16170</v>
@@ -12085,7 +12085,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>7050</v>
@@ -12126,7 +12126,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>2280</v>
@@ -12638,7 +12638,7 @@
         <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>51.97</v>
+        <v>27.8</v>
       </c>
       <c r="L5" t="n">
         <v>34599.6</v>
@@ -12679,7 +12679,7 @@
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>76.56</v>
+        <v>38.02</v>
       </c>
       <c r="L6" t="n">
         <v>58763.4</v>
@@ -12720,7 +12720,7 @@
         <v>0.7</v>
       </c>
       <c r="K7" t="n">
-        <v>132.7</v>
+        <v>46.57</v>
       </c>
       <c r="L7" t="n">
         <v>121734</v>
@@ -12761,7 +12761,7 @@
         <v>1.7</v>
       </c>
       <c r="K8" t="n">
-        <v>89.79000000000001</v>
+        <v>29.44</v>
       </c>
       <c r="L8" t="n">
         <v>88608</v>
@@ -12802,7 +12802,7 @@
         <v>1.9</v>
       </c>
       <c r="K9" t="n">
-        <v>72.27</v>
+        <v>27.3</v>
       </c>
       <c r="L9" t="n">
         <v>59073.3</v>
@@ -12843,7 +12843,7 @@
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>39.15</v>
+        <v>4.35</v>
       </c>
       <c r="L10" t="n">
         <v>34122.6</v>
@@ -12884,7 +12884,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>4.49</v>
+        <v>1.8</v>
       </c>
       <c r="L11" t="n">
         <v>9390</v>
@@ -13642,7 +13642,7 @@
         <v>72834</v>
       </c>
       <c r="K5" t="n">
-        <v>2523309.65</v>
+        <v>1350051.02</v>
       </c>
       <c r="L5" t="n">
         <v>6227928</v>
@@ -13683,7 +13683,7 @@
         <v>72834</v>
       </c>
       <c r="K6" t="n">
-        <v>3717301.69</v>
+        <v>1846341.9</v>
       </c>
       <c r="L6" t="n">
         <v>10577412</v>
@@ -13724,7 +13724,7 @@
         <v>16994.6</v>
       </c>
       <c r="K7" t="n">
-        <v>6443575.42</v>
+        <v>2261447.14</v>
       </c>
       <c r="L7" t="n">
         <v>21912120</v>
@@ -13765,7 +13765,7 @@
         <v>41272.6</v>
       </c>
       <c r="K8" t="n">
-        <v>4359940.35</v>
+        <v>1429488.64</v>
       </c>
       <c r="L8" t="n">
         <v>15949440</v>
@@ -13806,7 +13806,7 @@
         <v>46128.2</v>
       </c>
       <c r="K9" t="n">
-        <v>3509142.12</v>
+        <v>1325675.91</v>
       </c>
       <c r="L9" t="n">
         <v>10633194</v>
@@ -13847,7 +13847,7 @@
         <v>24278</v>
       </c>
       <c r="K10" t="n">
-        <v>1900967.4</v>
+        <v>211218.6</v>
       </c>
       <c r="L10" t="n">
         <v>6142068</v>
@@ -13888,7 +13888,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>218137.83</v>
+        <v>87255.13</v>
       </c>
       <c r="L11" t="n">
         <v>1690200</v>
@@ -14605,7 +14605,7 @@
         <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>118</v>
+        <v>48</v>
       </c>
       <c r="L4" t="n">
         <v>345540</v>
@@ -14646,7 +14646,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="L5" t="n">
         <v>111990</v>
@@ -15650,7 +15650,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>10.59</v>
+        <v>4.96</v>
       </c>
       <c r="L5" t="n">
         <v>23517.9</v>
@@ -16654,7 +16654,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>514305.15</v>
+        <v>241080.54</v>
       </c>
       <c r="L5" t="n">
         <v>4233222</v>
@@ -17658,7 +17658,7 @@
         <v>174801.6</v>
       </c>
       <c r="K5" t="n">
-        <v>9707509.74</v>
+        <v>4114441.22</v>
       </c>
       <c r="L5" t="n">
         <v>33675264</v>
@@ -17699,7 +17699,7 @@
         <v>169946</v>
       </c>
       <c r="K6" t="n">
-        <v>10511839.88</v>
+        <v>4061952.18</v>
       </c>
       <c r="L6" t="n">
         <v>38917044</v>
@@ -17740,7 +17740,7 @@
         <v>203935.2</v>
       </c>
       <c r="K7" t="n">
-        <v>14188257.42</v>
+        <v>4801702.84</v>
       </c>
       <c r="L7" t="n">
         <v>58261680</v>
@@ -17781,7 +17781,7 @@
         <v>165090.4</v>
       </c>
       <c r="K8" t="n">
-        <v>12758186.11</v>
+        <v>3609458.82</v>
       </c>
       <c r="L8" t="n">
         <v>56651184</v>
@@ -17822,7 +17822,7 @@
         <v>115320.5</v>
       </c>
       <c r="K9" t="n">
-        <v>13022816.31</v>
+        <v>4288951.48</v>
       </c>
       <c r="L9" t="n">
         <v>55029294</v>
@@ -17863,7 +17863,7 @@
         <v>267058</v>
       </c>
       <c r="K10" t="n">
-        <v>10856636.04</v>
+        <v>2407892.04</v>
       </c>
       <c r="L10" t="n">
         <v>46195272</v>
@@ -17904,7 +17904,7 @@
         <v>72834</v>
       </c>
       <c r="K11" t="n">
-        <v>7285803.52</v>
+        <v>1483337.24</v>
       </c>
       <c r="L11" t="n">
         <v>32583600</v>
@@ -17945,7 +17945,7 @@
         <v>24278</v>
       </c>
       <c r="K12" t="n">
-        <v>4636175.44</v>
+        <v>540136.9399999999</v>
       </c>
       <c r="L12" t="n">
         <v>26897400</v>
@@ -17986,7 +17986,7 @@
         <v>72834</v>
       </c>
       <c r="K13" t="n">
-        <v>2581819.63</v>
+        <v>276623.53</v>
       </c>
       <c r="L13" t="n">
         <v>17172000</v>
@@ -18027,7 +18027,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>1274303.66</v>
+        <v>47196.43</v>
       </c>
       <c r="L14" t="n">
         <v>7435800</v>
@@ -18068,7 +18068,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>478762.16</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>2910600</v>
@@ -18109,7 +18109,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>194224</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>1269000</v>
@@ -18150,7 +18150,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>48556</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>410400</v>
@@ -18621,7 +18621,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>126</v>
+        <v>73</v>
       </c>
       <c r="L4" t="n">
         <v>137190</v>
@@ -18662,7 +18662,7 @@
         <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>141</v>
+        <v>68</v>
       </c>
       <c r="L5" t="n">
         <v>165390</v>
@@ -18703,7 +18703,7 @@
         <v>5</v>
       </c>
       <c r="K6" t="n">
-        <v>136</v>
+        <v>54</v>
       </c>
       <c r="L6" t="n">
         <v>173100</v>
@@ -18744,7 +18744,7 @@
         <v>8</v>
       </c>
       <c r="K7" t="n">
-        <v>151</v>
+        <v>59</v>
       </c>
       <c r="L7" t="n">
         <v>184590</v>
@@ -18785,7 +18785,7 @@
         <v>5</v>
       </c>
       <c r="K8" t="n">
-        <v>203</v>
+        <v>48</v>
       </c>
       <c r="L8" t="n">
         <v>239370</v>
@@ -18826,7 +18826,7 @@
         <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>216</v>
+        <v>66</v>
       </c>
       <c r="L9" t="n">
         <v>240120</v>
@@ -18867,7 +18867,7 @@
         <v>5</v>
       </c>
       <c r="K10" t="n">
-        <v>193</v>
+        <v>49</v>
       </c>
       <c r="L10" t="n">
         <v>198120</v>
@@ -18908,7 +18908,7 @@
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>129</v>
+        <v>28</v>
       </c>
       <c r="L11" t="n">
         <v>111750</v>
@@ -18949,7 +18949,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>65</v>
+        <v>6</v>
       </c>
       <c r="L12" t="n">
         <v>51630</v>
@@ -18990,7 +18990,7 @@
         <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>25020</v>
@@ -19031,7 +19031,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>7650</v>
@@ -19113,7 +19113,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>960</v>
@@ -19154,7 +19154,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>120</v>
@@ -19666,7 +19666,7 @@
         <v>0.6</v>
       </c>
       <c r="K5" t="n">
-        <v>46.67</v>
+        <v>22.51</v>
       </c>
       <c r="L5" t="n">
         <v>34731.9</v>
@@ -19707,7 +19707,7 @@
         <v>2.5</v>
       </c>
       <c r="K6" t="n">
-        <v>68.95</v>
+        <v>27.38</v>
       </c>
       <c r="L6" t="n">
         <v>64047</v>
@@ -19748,7 +19748,7 @@
         <v>5.6</v>
       </c>
       <c r="K7" t="n">
-        <v>96.34</v>
+        <v>37.64</v>
       </c>
       <c r="L7" t="n">
         <v>110754</v>
@@ -19789,7 +19789,7 @@
         <v>4.25</v>
       </c>
       <c r="K8" t="n">
-        <v>149.41</v>
+        <v>35.33</v>
       </c>
       <c r="L8" t="n">
         <v>169952.7</v>
@@ -19830,7 +19830,7 @@
         <v>2.85</v>
       </c>
       <c r="K9" t="n">
-        <v>173.45</v>
+        <v>53</v>
       </c>
       <c r="L9" t="n">
         <v>194497.2</v>
@@ -19871,7 +19871,7 @@
         <v>5</v>
       </c>
       <c r="K10" t="n">
-        <v>167.91</v>
+        <v>42.63</v>
       </c>
       <c r="L10" t="n">
         <v>176326.8</v>
@@ -19912,7 +19912,7 @@
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>115.91</v>
+        <v>25.16</v>
       </c>
       <c r="L11" t="n">
         <v>111750</v>
@@ -19953,7 +19953,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>60.26</v>
+        <v>5.56</v>
       </c>
       <c r="L12" t="n">
         <v>51630</v>
@@ -19994,7 +19994,7 @@
         <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>21.84</v>
+        <v>0.95</v>
       </c>
       <c r="L13" t="n">
         <v>25020</v>
@@ -20035,7 +20035,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>7.78</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>7650</v>
@@ -20117,7 +20117,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>960</v>
@@ -20158,7 +20158,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>120</v>
@@ -20670,7 +20670,7 @@
         <v>14566.8</v>
       </c>
       <c r="K5" t="n">
-        <v>2266157.08</v>
+        <v>1092898.45</v>
       </c>
       <c r="L5" t="n">
         <v>6251742</v>
@@ -20711,7 +20711,7 @@
         <v>60695</v>
       </c>
       <c r="K6" t="n">
-        <v>3348033.31</v>
+        <v>1329366.17</v>
       </c>
       <c r="L6" t="n">
         <v>11528460</v>
@@ -20752,7 +20752,7 @@
         <v>135956.8</v>
       </c>
       <c r="K7" t="n">
-        <v>4677787.93</v>
+        <v>1827744.95</v>
       </c>
       <c r="L7" t="n">
         <v>19935720</v>
@@ -20793,7 +20793,7 @@
         <v>103181.5</v>
       </c>
       <c r="K8" t="n">
-        <v>7254654.85</v>
+        <v>1715386.37</v>
       </c>
       <c r="L8" t="n">
         <v>30591486</v>
@@ -20834,7 +20834,7 @@
         <v>69192.3</v>
       </c>
       <c r="K9" t="n">
-        <v>8421941.09</v>
+        <v>2573370.89</v>
       </c>
       <c r="L9" t="n">
         <v>35009496</v>
@@ -20875,7 +20875,7 @@
         <v>121390</v>
       </c>
       <c r="K10" t="n">
-        <v>8153037.96</v>
+        <v>2069942.28</v>
       </c>
       <c r="L10" t="n">
         <v>31738824</v>
@@ -20916,7 +20916,7 @@
         <v>48556</v>
       </c>
       <c r="K11" t="n">
-        <v>5627956.01</v>
+        <v>1221571.85</v>
       </c>
       <c r="L11" t="n">
         <v>20115000</v>
@@ -20957,7 +20957,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>2925741.78</v>
+        <v>270068.47</v>
       </c>
       <c r="L12" t="n">
         <v>9293400</v>
@@ -20998,7 +20998,7 @@
         <v>72834</v>
       </c>
       <c r="K13" t="n">
-        <v>1060390.21</v>
+        <v>46103.92</v>
       </c>
       <c r="L13" t="n">
         <v>4503600</v>
@@ -21039,7 +21039,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>377571.46</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>1377000</v>
@@ -21121,7 +21121,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>48556</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>172800</v>
@@ -21162,7 +21162,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>48556</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>21600</v>
@@ -21633,7 +21633,7 @@
         <v>14</v>
       </c>
       <c r="K4" t="n">
-        <v>388</v>
+        <v>97</v>
       </c>
       <c r="L4" t="n">
         <v>407010</v>
@@ -21674,7 +21674,7 @@
         <v>7</v>
       </c>
       <c r="K5" t="n">
-        <v>190</v>
+        <v>60</v>
       </c>
       <c r="L5" t="n">
         <v>260910</v>
@@ -21715,7 +21715,7 @@
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>108</v>
+        <v>27</v>
       </c>
       <c r="L6" t="n">
         <v>135300</v>
@@ -21756,7 +21756,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>74</v>
+        <v>12</v>
       </c>
       <c r="L7" t="n">
         <v>78960</v>
@@ -21797,7 +21797,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
         <v>21870</v>
@@ -22678,7 +22678,7 @@
         <v>2.1</v>
       </c>
       <c r="K5" t="n">
-        <v>62.89</v>
+        <v>19.86</v>
       </c>
       <c r="L5" t="n">
         <v>54791.1</v>
@@ -22719,7 +22719,7 @@
         <v>1.5</v>
       </c>
       <c r="K6" t="n">
-        <v>54.76</v>
+        <v>13.69</v>
       </c>
       <c r="L6" t="n">
         <v>50061</v>
@@ -22760,7 +22760,7 @@
         <v>2.1</v>
       </c>
       <c r="K7" t="n">
-        <v>47.21</v>
+        <v>7.66</v>
       </c>
       <c r="L7" t="n">
         <v>47376</v>
@@ -22801,7 +22801,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>6.62</v>
+        <v>0.74</v>
       </c>
       <c r="L8" t="n">
         <v>15527.7</v>
@@ -23682,7 +23682,7 @@
         <v>50983.8</v>
       </c>
       <c r="K5" t="n">
-        <v>3053686.84</v>
+        <v>964322.16</v>
       </c>
       <c r="L5" t="n">
         <v>9862398</v>
@@ -23723,7 +23723,7 @@
         <v>36417</v>
       </c>
       <c r="K6" t="n">
-        <v>2658732.34</v>
+        <v>664683.08</v>
       </c>
       <c r="L6" t="n">
         <v>9010980</v>
@@ -23764,7 +23764,7 @@
         <v>50983.8</v>
       </c>
       <c r="K7" t="n">
-        <v>2292425.87</v>
+        <v>371744.74</v>
       </c>
       <c r="L7" t="n">
         <v>8527680</v>
@@ -23805,7 +23805,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>321634.94</v>
+        <v>35737.22</v>
       </c>
       <c r="L8" t="n">
         <v>2794986</v>

--- a/risk/Risk_Analysis_T3_100yrs_Future_Perfect.xlsx
+++ b/risk/Risk_Analysis_T3_100yrs_Future_Perfect.xlsx
@@ -560,7 +560,7 @@
         <v>543390</v>
       </c>
       <c r="H4" t="n">
-        <v>59910</v>
+        <v>67230</v>
       </c>
       <c r="I4" t="n">
         <v>9</v>
@@ -572,22 +572,22 @@
         <v>436</v>
       </c>
       <c r="L4" t="n">
-        <v>1418850</v>
+        <v>1517130</v>
       </c>
       <c r="M4" t="n">
-        <v>71160</v>
+        <v>49980</v>
       </c>
       <c r="N4" t="n">
-        <v>81030</v>
+        <v>77430</v>
       </c>
       <c r="O4" t="n">
-        <v>222360</v>
+        <v>223740</v>
       </c>
       <c r="P4" t="n">
-        <v>41910</v>
+        <v>15360</v>
       </c>
       <c r="Q4" t="n">
-        <v>215945.11</v>
+        <v>2237818.25</v>
       </c>
     </row>
     <row r="5">
@@ -613,7 +613,7 @@
         <v>353430</v>
       </c>
       <c r="H5" t="n">
-        <v>54420</v>
+        <v>59070</v>
       </c>
       <c r="I5" t="n">
         <v>5</v>
@@ -625,22 +625,22 @@
         <v>256</v>
       </c>
       <c r="L5" t="n">
-        <v>890880</v>
+        <v>943050</v>
       </c>
       <c r="M5" t="n">
-        <v>51690</v>
+        <v>37500</v>
       </c>
       <c r="N5" t="n">
-        <v>75360</v>
+        <v>87450</v>
       </c>
       <c r="O5" t="n">
-        <v>182310</v>
+        <v>209010</v>
       </c>
       <c r="P5" t="n">
-        <v>53010</v>
+        <v>34110</v>
       </c>
       <c r="Q5" t="n">
-        <v>137593.43</v>
+        <v>1425867.35</v>
       </c>
     </row>
     <row r="6">
@@ -666,7 +666,7 @@
         <v>238500</v>
       </c>
       <c r="H6" t="n">
-        <v>45720</v>
+        <v>46440</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -678,22 +678,22 @@
         <v>165</v>
       </c>
       <c r="L6" t="n">
-        <v>584340</v>
+        <v>584010</v>
       </c>
       <c r="M6" t="n">
-        <v>34530</v>
+        <v>23190</v>
       </c>
       <c r="N6" t="n">
-        <v>25860</v>
+        <v>36300</v>
       </c>
       <c r="O6" t="n">
-        <v>114090</v>
+        <v>124080</v>
       </c>
       <c r="P6" t="n">
-        <v>51870</v>
+        <v>37320</v>
       </c>
       <c r="Q6" t="n">
-        <v>96245.50999999999</v>
+        <v>997382.95</v>
       </c>
     </row>
     <row r="7">
@@ -719,7 +719,7 @@
         <v>210210</v>
       </c>
       <c r="H7" t="n">
-        <v>43470</v>
+        <v>45390</v>
       </c>
       <c r="I7" t="n">
         <v>2</v>
@@ -731,22 +731,22 @@
         <v>155</v>
       </c>
       <c r="L7" t="n">
-        <v>539460</v>
+        <v>537270</v>
       </c>
       <c r="M7" t="n">
-        <v>24150</v>
+        <v>26640</v>
       </c>
       <c r="N7" t="n">
-        <v>9030</v>
+        <v>13890</v>
       </c>
       <c r="O7" t="n">
-        <v>84600</v>
+        <v>90930</v>
       </c>
       <c r="P7" t="n">
-        <v>61920</v>
+        <v>45330</v>
       </c>
       <c r="Q7" t="n">
-        <v>93835.28999999999</v>
+        <v>972406.02</v>
       </c>
     </row>
     <row r="8">
@@ -772,7 +772,7 @@
         <v>178680</v>
       </c>
       <c r="H8" t="n">
-        <v>26700</v>
+        <v>28110</v>
       </c>
       <c r="I8" t="n">
         <v>3</v>
@@ -784,22 +784,22 @@
         <v>101</v>
       </c>
       <c r="L8" t="n">
-        <v>443280</v>
+        <v>440220</v>
       </c>
       <c r="M8" t="n">
-        <v>19200</v>
+        <v>26250</v>
       </c>
       <c r="N8" t="n">
-        <v>1650</v>
+        <v>3960</v>
       </c>
       <c r="O8" t="n">
-        <v>61200</v>
+        <v>65430</v>
       </c>
       <c r="P8" t="n">
-        <v>68850</v>
+        <v>55140</v>
       </c>
       <c r="Q8" t="n">
-        <v>79021.06</v>
+        <v>818887.58</v>
       </c>
     </row>
     <row r="9">
@@ -825,7 +825,7 @@
         <v>162030</v>
       </c>
       <c r="H9" t="n">
-        <v>8040</v>
+        <v>11010</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
@@ -837,22 +837,22 @@
         <v>110</v>
       </c>
       <c r="L9" t="n">
-        <v>377430</v>
+        <v>395160</v>
       </c>
       <c r="M9" t="n">
-        <v>11640</v>
+        <v>34410</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="O9" t="n">
-        <v>55170</v>
+        <v>65070</v>
       </c>
       <c r="P9" t="n">
-        <v>68280</v>
+        <v>62760</v>
       </c>
       <c r="Q9" t="n">
-        <v>75444.28</v>
+        <v>781821.76</v>
       </c>
     </row>
     <row r="10">
@@ -878,7 +878,7 @@
         <v>133470</v>
       </c>
       <c r="H10" t="n">
-        <v>3840</v>
+        <v>3660</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -890,22 +890,22 @@
         <v>57</v>
       </c>
       <c r="L10" t="n">
-        <v>288360</v>
+        <v>319710</v>
       </c>
       <c r="M10" t="n">
-        <v>10230</v>
+        <v>24510</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>32070</v>
+        <v>45540</v>
       </c>
       <c r="P10" t="n">
-        <v>77340</v>
+        <v>76950</v>
       </c>
       <c r="Q10" t="n">
-        <v>61088.39</v>
+        <v>633053.0699999999</v>
       </c>
     </row>
     <row r="11">
@@ -931,7 +931,7 @@
         <v>75930</v>
       </c>
       <c r="H11" t="n">
-        <v>4800</v>
+        <v>4560</v>
       </c>
       <c r="I11" t="n">
         <v>3</v>
@@ -943,22 +943,22 @@
         <v>34</v>
       </c>
       <c r="L11" t="n">
-        <v>181020</v>
+        <v>217290</v>
       </c>
       <c r="M11" t="n">
-        <v>6210</v>
+        <v>26220</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>10890</v>
+        <v>21270</v>
       </c>
       <c r="P11" t="n">
-        <v>73020</v>
+        <v>91230</v>
       </c>
       <c r="Q11" t="n">
-        <v>38457.81</v>
+        <v>398534.53</v>
       </c>
     </row>
     <row r="12">
@@ -984,7 +984,7 @@
         <v>59790</v>
       </c>
       <c r="H12" t="n">
-        <v>4800</v>
+        <v>5700</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -996,22 +996,22 @@
         <v>12</v>
       </c>
       <c r="L12" t="n">
-        <v>149430</v>
+        <v>198960</v>
       </c>
       <c r="M12" t="n">
-        <v>3480</v>
+        <v>22830</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>4200</v>
+        <v>11760</v>
       </c>
       <c r="P12" t="n">
-        <v>59130</v>
+        <v>97950</v>
       </c>
       <c r="Q12" t="n">
-        <v>27193.91</v>
+        <v>281807.82</v>
       </c>
     </row>
     <row r="13">
@@ -1037,7 +1037,7 @@
         <v>48150</v>
       </c>
       <c r="H13" t="n">
-        <v>1320</v>
+        <v>1830</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1049,22 +1049,22 @@
         <v>6</v>
       </c>
       <c r="L13" t="n">
-        <v>95400</v>
+        <v>133200</v>
       </c>
       <c r="M13" t="n">
-        <v>2700</v>
+        <v>16440</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2400</v>
+        <v>3900</v>
       </c>
       <c r="P13" t="n">
-        <v>42270</v>
+        <v>70620</v>
       </c>
       <c r="Q13" t="n">
-        <v>18591.22</v>
+        <v>192659.02</v>
       </c>
     </row>
     <row r="14">
@@ -1090,7 +1090,7 @@
         <v>22020</v>
       </c>
       <c r="H14" t="n">
-        <v>810</v>
+        <v>780</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
@@ -1102,22 +1102,22 @@
         <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>41310</v>
+        <v>57450</v>
       </c>
       <c r="M14" t="n">
-        <v>1140</v>
+        <v>16890</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3510</v>
+        <v>3210</v>
       </c>
       <c r="P14" t="n">
-        <v>28080</v>
+        <v>36390</v>
       </c>
       <c r="Q14" t="n">
-        <v>8752.790000000001</v>
+        <v>90704.28999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1143,7 +1143,7 @@
         <v>5550</v>
       </c>
       <c r="H15" t="n">
-        <v>270</v>
+        <v>510</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1155,22 +1155,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>16170</v>
+        <v>30300</v>
       </c>
       <c r="M15" t="n">
-        <v>300</v>
+        <v>6000</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>750</v>
+        <v>1290</v>
       </c>
       <c r="P15" t="n">
-        <v>30270</v>
+        <v>33420</v>
       </c>
       <c r="Q15" t="n">
-        <v>3142.43</v>
+        <v>32564.73</v>
       </c>
     </row>
     <row r="16">
@@ -1196,7 +1196,7 @@
         <v>3750</v>
       </c>
       <c r="H16" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -1208,22 +1208,22 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>7050</v>
+        <v>23970</v>
       </c>
       <c r="M16" t="n">
+        <v>3150</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
         <v>150</v>
       </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>30</v>
-      </c>
       <c r="P16" t="n">
-        <v>38520</v>
+        <v>55560</v>
       </c>
       <c r="Q16" t="n">
-        <v>2199.97</v>
+        <v>22798.08</v>
       </c>
     </row>
     <row r="17">
@@ -1249,7 +1249,7 @@
         <v>1290</v>
       </c>
       <c r="H17" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1261,10 +1261,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>2280</v>
+        <v>9300</v>
       </c>
       <c r="M17" t="n">
-        <v>150</v>
+        <v>1590</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -1273,10 +1273,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>21210</v>
+        <v>32580</v>
       </c>
       <c r="Q17" t="n">
-        <v>1135.2</v>
+        <v>11763.92</v>
       </c>
     </row>
     <row r="18">
@@ -1302,7 +1302,7 @@
         <v>300</v>
       </c>
       <c r="H18" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -1314,10 +1314,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1560</v>
+        <v>6150</v>
       </c>
       <c r="M18" t="n">
-        <v>210</v>
+        <v>990</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -1326,10 +1326,10 @@
         <v>30</v>
       </c>
       <c r="P18" t="n">
-        <v>21450</v>
+        <v>30690</v>
       </c>
       <c r="Q18" t="n">
-        <v>536.6799999999999</v>
+        <v>5561.61</v>
       </c>
     </row>
     <row r="19">
@@ -1367,22 +1367,22 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1440</v>
+        <v>3900</v>
       </c>
       <c r="M19" t="n">
-        <v>90</v>
+        <v>1200</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="P19" t="n">
-        <v>17580</v>
+        <v>31080</v>
       </c>
       <c r="Q19" t="n">
-        <v>249.31</v>
+        <v>2583.62</v>
       </c>
     </row>
     <row r="20">
@@ -1408,7 +1408,7 @@
         <v>3690</v>
       </c>
       <c r="H20" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -1420,10 +1420,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>660</v>
+        <v>3150</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1680</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -1432,10 +1432,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1950</v>
+        <v>5190</v>
       </c>
       <c r="Q20" t="n">
-        <v>73.66</v>
+        <v>763.29</v>
       </c>
     </row>
     <row r="21">
@@ -1485,10 +1485,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="Q21" t="n">
-        <v>14.73</v>
+        <v>152.66</v>
       </c>
     </row>
     <row r="22">
@@ -1526,7 +1526,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.45</v>
+        <v>15.03</v>
       </c>
     </row>
     <row r="23">
@@ -1579,7 +1579,7 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -1852,7 +1852,7 @@
         <v>7950</v>
       </c>
       <c r="H4" t="n">
-        <v>3390</v>
+        <v>3600</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -1864,22 +1864,22 @@
         <v>8</v>
       </c>
       <c r="L4" t="n">
-        <v>17100</v>
+        <v>17550</v>
       </c>
       <c r="M4" t="n">
-        <v>3510</v>
+        <v>1590</v>
       </c>
       <c r="N4" t="n">
-        <v>1140</v>
+        <v>450</v>
       </c>
       <c r="O4" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>121.36</v>
+        <v>13754.7</v>
       </c>
     </row>
     <row r="5">
@@ -1905,7 +1905,7 @@
         <v>9390</v>
       </c>
       <c r="H5" t="n">
-        <v>4140</v>
+        <v>4830</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -1917,13 +1917,13 @@
         <v>3</v>
       </c>
       <c r="L5" t="n">
-        <v>21240</v>
+        <v>17760</v>
       </c>
       <c r="M5" t="n">
-        <v>8220</v>
+        <v>5010</v>
       </c>
       <c r="N5" t="n">
-        <v>150</v>
+        <v>780</v>
       </c>
       <c r="O5" t="n">
         <v>30</v>
@@ -1932,7 +1932,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>245.27</v>
+        <v>27797.04</v>
       </c>
     </row>
     <row r="6">
@@ -1958,7 +1958,7 @@
         <v>8190</v>
       </c>
       <c r="H6" t="n">
-        <v>2850</v>
+        <v>3540</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1970,22 +1970,22 @@
         <v>9</v>
       </c>
       <c r="L6" t="n">
-        <v>22740</v>
+        <v>18090</v>
       </c>
       <c r="M6" t="n">
-        <v>9960</v>
+        <v>5100</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="O6" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>589.33</v>
+        <v>66790.62</v>
       </c>
     </row>
     <row r="7">
@@ -2011,7 +2011,7 @@
         <v>8700</v>
       </c>
       <c r="H7" t="n">
-        <v>3600</v>
+        <v>3210</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -2023,22 +2023,22 @@
         <v>10</v>
       </c>
       <c r="L7" t="n">
-        <v>27960</v>
+        <v>21360</v>
       </c>
       <c r="M7" t="n">
-        <v>7680</v>
+        <v>3900</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>870</v>
+        <v>750</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>976.27</v>
+        <v>110643.48</v>
       </c>
     </row>
     <row r="8">
@@ -2064,7 +2064,7 @@
         <v>15630</v>
       </c>
       <c r="H8" t="n">
-        <v>3720</v>
+        <v>2940</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -2076,10 +2076,10 @@
         <v>12</v>
       </c>
       <c r="L8" t="n">
-        <v>37800</v>
+        <v>33270</v>
       </c>
       <c r="M8" t="n">
-        <v>6600</v>
+        <v>2430</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -2091,7 +2091,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1257.98</v>
+        <v>142571.52</v>
       </c>
     </row>
     <row r="9">
@@ -2117,7 +2117,7 @@
         <v>19860</v>
       </c>
       <c r="H9" t="n">
-        <v>3510</v>
+        <v>5040</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
@@ -2129,22 +2129,22 @@
         <v>9</v>
       </c>
       <c r="L9" t="n">
-        <v>47010</v>
+        <v>43740</v>
       </c>
       <c r="M9" t="n">
-        <v>3510</v>
+        <v>2460</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>180</v>
+        <v>300</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1286.2</v>
+        <v>145769.22</v>
       </c>
     </row>
     <row r="10">
@@ -2170,7 +2170,7 @@
         <v>17790</v>
       </c>
       <c r="H10" t="n">
-        <v>3300</v>
+        <v>2970</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -2182,22 +2182,22 @@
         <v>3</v>
       </c>
       <c r="L10" t="n">
-        <v>44070</v>
+        <v>45660</v>
       </c>
       <c r="M10" t="n">
-        <v>3000</v>
+        <v>1140</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1297.3</v>
+        <v>147026.88</v>
       </c>
     </row>
     <row r="11">
@@ -2223,7 +2223,7 @@
         <v>19530</v>
       </c>
       <c r="H11" t="n">
-        <v>4440</v>
+        <v>3930</v>
       </c>
       <c r="I11" t="n">
         <v>2</v>
@@ -2235,22 +2235,22 @@
         <v>4</v>
       </c>
       <c r="L11" t="n">
-        <v>57960</v>
+        <v>53820</v>
       </c>
       <c r="M11" t="n">
-        <v>1980</v>
+        <v>3630</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1225.37</v>
+        <v>138875.04</v>
       </c>
     </row>
     <row r="12">
@@ -2276,7 +2276,7 @@
         <v>32640</v>
       </c>
       <c r="H12" t="n">
-        <v>4740</v>
+        <v>5280</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -2288,22 +2288,22 @@
         <v>4</v>
       </c>
       <c r="L12" t="n">
-        <v>92610</v>
+        <v>95490</v>
       </c>
       <c r="M12" t="n">
-        <v>1020</v>
+        <v>4320</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>150</v>
+        <v>240</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1810.4</v>
+        <v>205179.12</v>
       </c>
     </row>
     <row r="13">
@@ -2329,7 +2329,7 @@
         <v>28260</v>
       </c>
       <c r="H13" t="n">
-        <v>1320</v>
+        <v>1770</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -2341,10 +2341,10 @@
         <v>5</v>
       </c>
       <c r="L13" t="n">
-        <v>67530</v>
+        <v>78360</v>
       </c>
       <c r="M13" t="n">
-        <v>300</v>
+        <v>3750</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -2356,7 +2356,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1792.45</v>
+        <v>203144.22</v>
       </c>
     </row>
     <row r="14">
@@ -2382,7 +2382,7 @@
         <v>15060</v>
       </c>
       <c r="H14" t="n">
-        <v>810</v>
+        <v>780</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
@@ -2394,10 +2394,10 @@
         <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>32340</v>
+        <v>38430</v>
       </c>
       <c r="M14" t="n">
-        <v>240</v>
+        <v>3750</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2409,7 +2409,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>993.41</v>
+        <v>112586.58</v>
       </c>
     </row>
     <row r="15">
@@ -2435,7 +2435,7 @@
         <v>4380</v>
       </c>
       <c r="H15" t="n">
-        <v>270</v>
+        <v>510</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -2447,10 +2447,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>13170</v>
+        <v>19290</v>
       </c>
       <c r="M15" t="n">
-        <v>150</v>
+        <v>3510</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2462,7 +2462,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>386.13</v>
+        <v>43761.06</v>
       </c>
     </row>
     <row r="16">
@@ -2488,7 +2488,7 @@
         <v>3030</v>
       </c>
       <c r="H16" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -2500,10 +2500,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>5820</v>
+        <v>11850</v>
       </c>
       <c r="M16" t="n">
-        <v>60</v>
+        <v>1950</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2515,7 +2515,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>288.25</v>
+        <v>32668.56</v>
       </c>
     </row>
     <row r="17">
@@ -2541,7 +2541,7 @@
         <v>570</v>
       </c>
       <c r="H17" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -2553,10 +2553,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1770</v>
+        <v>4080</v>
       </c>
       <c r="M17" t="n">
-        <v>90</v>
+        <v>750</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>112.56</v>
+        <v>12757.14</v>
       </c>
     </row>
     <row r="18">
@@ -2594,7 +2594,7 @@
         <v>90</v>
       </c>
       <c r="H18" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -2606,10 +2606,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>990</v>
+        <v>2100</v>
       </c>
       <c r="M18" t="n">
-        <v>150</v>
+        <v>900</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2621,7 +2621,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>53.76</v>
+        <v>6092.46</v>
       </c>
     </row>
     <row r="19">
@@ -2659,10 +2659,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>750</v>
+        <v>1500</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1110</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2674,7 +2674,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>19.3</v>
+        <v>2187.9</v>
       </c>
     </row>
     <row r="20">
@@ -2700,7 +2700,7 @@
         <v>60</v>
       </c>
       <c r="H20" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2712,10 +2712,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>660</v>
+        <v>2940</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1590</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -2727,7 +2727,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>8.18</v>
+        <v>927.1799999999999</v>
       </c>
     </row>
     <row r="21">
@@ -2780,7 +2780,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.65</v>
+        <v>186.66</v>
       </c>
     </row>
     <row r="22">
@@ -2818,7 +2818,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2833,7 +2833,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.32</v>
+        <v>36.72</v>
       </c>
     </row>
     <row r="23">
@@ -2871,7 +2871,7 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -3197,7 +3197,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1490.4</v>
+        <v>1738.8</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -3209,13 +3209,13 @@
         <v>0.99</v>
       </c>
       <c r="L5" t="n">
-        <v>4460.4</v>
+        <v>3729.6</v>
       </c>
       <c r="M5" t="n">
-        <v>164.4</v>
+        <v>100.2</v>
       </c>
       <c r="N5" t="n">
-        <v>1.5</v>
+        <v>7.8</v>
       </c>
       <c r="O5" t="n">
         <v>1.5</v>
@@ -3224,7 +3224,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>12.26</v>
+        <v>1389.85</v>
       </c>
     </row>
     <row r="6">
@@ -3250,7 +3250,7 @@
         <v>409.5</v>
       </c>
       <c r="H6" t="n">
-        <v>1624.5</v>
+        <v>2017.8</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -3262,22 +3262,22 @@
         <v>4.56</v>
       </c>
       <c r="L6" t="n">
-        <v>8413.799999999999</v>
+        <v>6693.3</v>
       </c>
       <c r="M6" t="n">
-        <v>796.8</v>
+        <v>408</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="O6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>442</v>
+        <v>50092.96</v>
       </c>
     </row>
     <row r="7">
@@ -3303,7 +3303,7 @@
         <v>1305</v>
       </c>
       <c r="H7" t="n">
-        <v>2628</v>
+        <v>2343.3</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -3315,22 +3315,22 @@
         <v>6.38</v>
       </c>
       <c r="L7" t="n">
-        <v>16776</v>
+        <v>12816</v>
       </c>
       <c r="M7" t="n">
-        <v>2688</v>
+        <v>1365</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>304.5</v>
+        <v>262.5</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>781.01</v>
+        <v>88514.78</v>
       </c>
     </row>
     <row r="8">
@@ -3356,7 +3356,7 @@
         <v>10159.5</v>
       </c>
       <c r="H8" t="n">
-        <v>3162</v>
+        <v>2499</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -3368,10 +3368,10 @@
         <v>8.83</v>
       </c>
       <c r="L8" t="n">
-        <v>26838</v>
+        <v>23621.7</v>
       </c>
       <c r="M8" t="n">
-        <v>3630</v>
+        <v>1336.5</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -3383,7 +3383,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1195.08</v>
+        <v>135442.94</v>
       </c>
     </row>
     <row r="9">
@@ -3409,7 +3409,7 @@
         <v>16881</v>
       </c>
       <c r="H9" t="n">
-        <v>3510</v>
+        <v>5040</v>
       </c>
       <c r="I9" t="n">
         <v>0.8</v>
@@ -3421,22 +3421,22 @@
         <v>7.23</v>
       </c>
       <c r="L9" t="n">
-        <v>38078.1</v>
+        <v>35429.4</v>
       </c>
       <c r="M9" t="n">
-        <v>2457</v>
+        <v>1722</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>99</v>
+        <v>165</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1247.61</v>
+        <v>141396.14</v>
       </c>
     </row>
     <row r="10">
@@ -3462,7 +3462,7 @@
         <v>17790</v>
       </c>
       <c r="H10" t="n">
-        <v>3300</v>
+        <v>2970</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -3474,22 +3474,22 @@
         <v>2.61</v>
       </c>
       <c r="L10" t="n">
-        <v>39222.3</v>
+        <v>40637.4</v>
       </c>
       <c r="M10" t="n">
-        <v>2550</v>
+        <v>969</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>84</v>
+        <v>126</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1297.3</v>
+        <v>147026.88</v>
       </c>
     </row>
     <row r="11">
@@ -3515,7 +3515,7 @@
         <v>19530</v>
       </c>
       <c r="H11" t="n">
-        <v>4440</v>
+        <v>3930</v>
       </c>
       <c r="I11" t="n">
         <v>1.8</v>
@@ -3527,22 +3527,22 @@
         <v>3.59</v>
       </c>
       <c r="L11" t="n">
-        <v>57960</v>
+        <v>53820</v>
       </c>
       <c r="M11" t="n">
-        <v>1782</v>
+        <v>3267</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>127.5</v>
+        <v>51</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1225.37</v>
+        <v>138875.04</v>
       </c>
     </row>
     <row r="12">
@@ -3568,7 +3568,7 @@
         <v>32640</v>
       </c>
       <c r="H12" t="n">
-        <v>4740</v>
+        <v>5280</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -3580,22 +3580,22 @@
         <v>3.71</v>
       </c>
       <c r="L12" t="n">
-        <v>92610</v>
+        <v>95490</v>
       </c>
       <c r="M12" t="n">
-        <v>969</v>
+        <v>4104</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>150</v>
+        <v>240</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1810.4</v>
+        <v>205179.12</v>
       </c>
     </row>
     <row r="13">
@@ -3621,7 +3621,7 @@
         <v>28260</v>
       </c>
       <c r="H13" t="n">
-        <v>1320</v>
+        <v>1770</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -3633,10 +3633,10 @@
         <v>4.75</v>
       </c>
       <c r="L13" t="n">
-        <v>67530</v>
+        <v>78360</v>
       </c>
       <c r="M13" t="n">
-        <v>300</v>
+        <v>3750</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -3648,7 +3648,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1792.45</v>
+        <v>203144.22</v>
       </c>
     </row>
     <row r="14">
@@ -3674,7 +3674,7 @@
         <v>15060</v>
       </c>
       <c r="H14" t="n">
-        <v>810</v>
+        <v>780</v>
       </c>
       <c r="I14" t="n">
         <v>0.97</v>
@@ -3686,10 +3686,10 @@
         <v>0.97</v>
       </c>
       <c r="L14" t="n">
-        <v>32340</v>
+        <v>38430</v>
       </c>
       <c r="M14" t="n">
-        <v>240</v>
+        <v>3750</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -3701,7 +3701,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>993.41</v>
+        <v>112586.58</v>
       </c>
     </row>
     <row r="15">
@@ -3727,7 +3727,7 @@
         <v>4380</v>
       </c>
       <c r="H15" t="n">
-        <v>270</v>
+        <v>510</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -3739,10 +3739,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>13170</v>
+        <v>19290</v>
       </c>
       <c r="M15" t="n">
-        <v>150</v>
+        <v>3510</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -3754,7 +3754,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>386.13</v>
+        <v>43761.06</v>
       </c>
     </row>
     <row r="16">
@@ -3780,7 +3780,7 @@
         <v>3030</v>
       </c>
       <c r="H16" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -3792,10 +3792,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>5820</v>
+        <v>11850</v>
       </c>
       <c r="M16" t="n">
-        <v>60</v>
+        <v>1950</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -3807,7 +3807,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>288.25</v>
+        <v>32668.56</v>
       </c>
     </row>
     <row r="17">
@@ -3833,7 +3833,7 @@
         <v>570</v>
       </c>
       <c r="H17" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -3845,10 +3845,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1770</v>
+        <v>4080</v>
       </c>
       <c r="M17" t="n">
-        <v>90</v>
+        <v>750</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -3860,7 +3860,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>112.56</v>
+        <v>12757.14</v>
       </c>
     </row>
     <row r="18">
@@ -3886,7 +3886,7 @@
         <v>90</v>
       </c>
       <c r="H18" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -3898,10 +3898,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>990</v>
+        <v>2100</v>
       </c>
       <c r="M18" t="n">
-        <v>150</v>
+        <v>900</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -3913,7 +3913,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>53.76</v>
+        <v>6092.46</v>
       </c>
     </row>
     <row r="19">
@@ -3951,10 +3951,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>750</v>
+        <v>1500</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1110</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -3966,7 +3966,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>19.3</v>
+        <v>2187.9</v>
       </c>
     </row>
     <row r="20">
@@ -3992,7 +3992,7 @@
         <v>60</v>
       </c>
       <c r="H20" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -4004,10 +4004,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>660</v>
+        <v>2940</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1590</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -4019,7 +4019,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>8.18</v>
+        <v>927.1799999999999</v>
       </c>
     </row>
     <row r="21">
@@ -4072,7 +4072,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.65</v>
+        <v>186.66</v>
       </c>
     </row>
     <row r="22">
@@ -4110,7 +4110,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -4125,7 +4125,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.32</v>
+        <v>36.72</v>
       </c>
     </row>
     <row r="23">
@@ -4163,7 +4163,7 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>8495280</v>
+        <v>9911160</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -4501,13 +4501,13 @@
         <v>48216.11</v>
       </c>
       <c r="L5" t="n">
-        <v>802872</v>
+        <v>671328</v>
       </c>
       <c r="M5" t="n">
-        <v>57540</v>
+        <v>35070</v>
       </c>
       <c r="N5" t="n">
-        <v>255</v>
+        <v>1326</v>
       </c>
       <c r="O5" t="n">
         <v>255</v>
@@ -4516,7 +4516,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>7358.04</v>
+        <v>833911.2</v>
       </c>
     </row>
     <row r="6">
@@ -4542,7 +4542,7 @@
         <v>22113</v>
       </c>
       <c r="H6" t="n">
-        <v>9259650</v>
+        <v>11501460</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -4554,22 +4554,22 @@
         <v>221561.03</v>
       </c>
       <c r="L6" t="n">
-        <v>1514484</v>
+        <v>1204794</v>
       </c>
       <c r="M6" t="n">
-        <v>278880</v>
+        <v>142800</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1275</v>
       </c>
       <c r="O6" t="n">
-        <v>2550</v>
+        <v>1275</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>265198.05</v>
+        <v>30055779</v>
       </c>
     </row>
     <row r="7">
@@ -4595,7 +4595,7 @@
         <v>70470</v>
       </c>
       <c r="H7" t="n">
-        <v>14979600</v>
+        <v>13356810</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -4607,22 +4607,22 @@
         <v>309787.28</v>
       </c>
       <c r="L7" t="n">
-        <v>3019680</v>
+        <v>2306880</v>
       </c>
       <c r="M7" t="n">
-        <v>940800</v>
+        <v>477750</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>51765</v>
+        <v>44625</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>468607.68</v>
+        <v>53108870.4</v>
       </c>
     </row>
     <row r="8">
@@ -4648,7 +4648,7 @@
         <v>548613</v>
       </c>
       <c r="H8" t="n">
-        <v>18023400</v>
+        <v>14244300</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -4660,10 +4660,10 @@
         <v>428846.59</v>
       </c>
       <c r="L8" t="n">
-        <v>4830840</v>
+        <v>4251906</v>
       </c>
       <c r="M8" t="n">
-        <v>1270500</v>
+        <v>467775</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -4675,7 +4675,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>717050.88</v>
+        <v>81265766.40000001</v>
       </c>
     </row>
     <row r="9">
@@ -4701,7 +4701,7 @@
         <v>911574</v>
       </c>
       <c r="H9" t="n">
-        <v>20007000</v>
+        <v>28728000</v>
       </c>
       <c r="I9" t="n">
         <v>155961.87</v>
@@ -4713,22 +4713,22 @@
         <v>350914.21</v>
       </c>
       <c r="L9" t="n">
-        <v>6854058</v>
+        <v>6377292</v>
       </c>
       <c r="M9" t="n">
-        <v>859950</v>
+        <v>602700</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>16830</v>
+        <v>28050</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>748567.8199999999</v>
+        <v>84837686.04000001</v>
       </c>
     </row>
     <row r="10">
@@ -4754,7 +4754,7 @@
         <v>960660</v>
       </c>
       <c r="H10" t="n">
-        <v>18810000</v>
+        <v>16929000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -4766,22 +4766,22 @@
         <v>126731.16</v>
       </c>
       <c r="L10" t="n">
-        <v>7060014</v>
+        <v>7314732</v>
       </c>
       <c r="M10" t="n">
-        <v>892500</v>
+        <v>339150</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>14280</v>
+        <v>21420</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>778377.6</v>
+        <v>88216128</v>
       </c>
     </row>
     <row r="11">
@@ -4807,7 +4807,7 @@
         <v>1054620</v>
       </c>
       <c r="H11" t="n">
-        <v>25308000</v>
+        <v>22401000</v>
       </c>
       <c r="I11" t="n">
         <v>349020.53</v>
@@ -4819,22 +4819,22 @@
         <v>174510.26</v>
       </c>
       <c r="L11" t="n">
-        <v>10432800</v>
+        <v>9687600</v>
       </c>
       <c r="M11" t="n">
-        <v>623700</v>
+        <v>1143450</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>21675</v>
+        <v>8670</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>735220.8</v>
+        <v>83325024</v>
       </c>
     </row>
     <row r="12">
@@ -4860,7 +4860,7 @@
         <v>1762560</v>
       </c>
       <c r="H12" t="n">
-        <v>27018000</v>
+        <v>30096000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -4872,22 +4872,22 @@
         <v>180045.65</v>
       </c>
       <c r="L12" t="n">
-        <v>16669800</v>
+        <v>17188200</v>
       </c>
       <c r="M12" t="n">
-        <v>339150</v>
+        <v>1436400</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>25500</v>
+        <v>40800</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1086242.4</v>
+        <v>123107472</v>
       </c>
     </row>
     <row r="13">
@@ -4913,7 +4913,7 @@
         <v>1526040</v>
       </c>
       <c r="H13" t="n">
-        <v>7524000</v>
+        <v>10089000</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -4925,10 +4925,10 @@
         <v>230519.61</v>
       </c>
       <c r="L13" t="n">
-        <v>12155400</v>
+        <v>14104800</v>
       </c>
       <c r="M13" t="n">
-        <v>105000</v>
+        <v>1312500</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -4940,7 +4940,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1075469.4</v>
+        <v>121886532</v>
       </c>
     </row>
     <row r="14">
@@ -4966,7 +4966,7 @@
         <v>813240</v>
       </c>
       <c r="H14" t="n">
-        <v>4617000</v>
+        <v>4446000</v>
       </c>
       <c r="I14" t="n">
         <v>188785.73</v>
@@ -4978,10 +4978,10 @@
         <v>47196.43</v>
       </c>
       <c r="L14" t="n">
-        <v>5821200</v>
+        <v>6917400</v>
       </c>
       <c r="M14" t="n">
-        <v>84000</v>
+        <v>1312500</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -4993,7 +4993,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>596046.6</v>
+        <v>67551948</v>
       </c>
     </row>
     <row r="15">
@@ -5019,7 +5019,7 @@
         <v>236520</v>
       </c>
       <c r="H15" t="n">
-        <v>1539000</v>
+        <v>2907000</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -5031,10 +5031,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>2370600</v>
+        <v>3472200</v>
       </c>
       <c r="M15" t="n">
-        <v>52500</v>
+        <v>1228500</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -5046,7 +5046,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>231676.2</v>
+        <v>26256636</v>
       </c>
     </row>
     <row r="16">
@@ -5072,7 +5072,7 @@
         <v>163620</v>
       </c>
       <c r="H16" t="n">
-        <v>684000</v>
+        <v>855000</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -5084,10 +5084,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1047600</v>
+        <v>2133000</v>
       </c>
       <c r="M16" t="n">
-        <v>21000</v>
+        <v>682500</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -5099,7 +5099,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>172951.2</v>
+        <v>19601136</v>
       </c>
     </row>
     <row r="17">
@@ -5125,7 +5125,7 @@
         <v>30780</v>
       </c>
       <c r="H17" t="n">
-        <v>342000</v>
+        <v>855000</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -5137,10 +5137,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>318600</v>
+        <v>734400</v>
       </c>
       <c r="M17" t="n">
-        <v>31500</v>
+        <v>262500</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -5152,7 +5152,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>67537.8</v>
+        <v>7654284</v>
       </c>
     </row>
     <row r="18">
@@ -5178,7 +5178,7 @@
         <v>4860</v>
       </c>
       <c r="H18" t="n">
-        <v>342000</v>
+        <v>684000</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -5190,10 +5190,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>178200</v>
+        <v>378000</v>
       </c>
       <c r="M18" t="n">
-        <v>52500</v>
+        <v>315000</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -5205,7 +5205,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>32254.2</v>
+        <v>3655476</v>
       </c>
     </row>
     <row r="19">
@@ -5243,10 +5243,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>135000</v>
+        <v>270000</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>388500</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -5258,7 +5258,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>11583</v>
+        <v>1312740</v>
       </c>
     </row>
     <row r="20">
@@ -5284,7 +5284,7 @@
         <v>3240</v>
       </c>
       <c r="H20" t="n">
-        <v>342000</v>
+        <v>684000</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -5296,10 +5296,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>118800</v>
+        <v>529200</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>556500</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -5311,7 +5311,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>4908.6</v>
+        <v>556308</v>
       </c>
     </row>
     <row r="21">
@@ -5364,7 +5364,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>988.2</v>
+        <v>111996</v>
       </c>
     </row>
     <row r="22">
@@ -5402,7 +5402,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>10800</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -5417,7 +5417,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>194.4</v>
+        <v>22032</v>
       </c>
     </row>
     <row r="23">
@@ -5455,7 +5455,7 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>5400</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -5728,7 +5728,7 @@
         <v>48120</v>
       </c>
       <c r="H4" t="n">
-        <v>6180</v>
+        <v>7860</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -5740,22 +5740,22 @@
         <v>39</v>
       </c>
       <c r="L4" t="n">
-        <v>144660</v>
+        <v>164160</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>8070</v>
+        <v>7110</v>
       </c>
       <c r="O4" t="n">
-        <v>20250</v>
+        <v>21180</v>
       </c>
       <c r="P4" t="n">
-        <v>11460</v>
+        <v>7950</v>
       </c>
       <c r="Q4" t="n">
-        <v>26704.52</v>
+        <v>140550.12</v>
       </c>
     </row>
     <row r="5">
@@ -5781,7 +5781,7 @@
         <v>17790</v>
       </c>
       <c r="H5" t="n">
-        <v>2190</v>
+        <v>3180</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
         <v>15</v>
       </c>
       <c r="L5" t="n">
-        <v>58500</v>
+        <v>76290</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>11490</v>
+        <v>12360</v>
       </c>
       <c r="O5" t="n">
-        <v>8910</v>
+        <v>13560</v>
       </c>
       <c r="P5" t="n">
-        <v>9150</v>
+        <v>11970</v>
       </c>
       <c r="Q5" t="n">
-        <v>11910.42</v>
+        <v>62686.44</v>
       </c>
     </row>
     <row r="6">
@@ -5834,7 +5834,7 @@
         <v>2250</v>
       </c>
       <c r="H6" t="n">
-        <v>330</v>
+        <v>600</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -5846,22 +5846,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>11220</v>
+        <v>17160</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1260</v>
+        <v>2610</v>
       </c>
       <c r="O6" t="n">
-        <v>420</v>
+        <v>1290</v>
       </c>
       <c r="P6" t="n">
-        <v>6000</v>
+        <v>8790</v>
       </c>
       <c r="Q6" t="n">
-        <v>1302.2</v>
+        <v>6853.68</v>
       </c>
     </row>
     <row r="7">
@@ -5887,7 +5887,7 @@
         <v>630</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -5899,7 +5899,7 @@
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>3090</v>
+        <v>4890</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -5911,10 +5911,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>5610</v>
+        <v>8730</v>
       </c>
       <c r="Q7" t="n">
-        <v>104.04</v>
+        <v>547.5599999999999</v>
       </c>
     </row>
     <row r="8">
@@ -5952,7 +5952,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>480</v>
+        <v>1920</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -5964,10 +5964,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>5190</v>
+        <v>9870</v>
       </c>
       <c r="Q8" t="n">
-        <v>47.81</v>
+        <v>251.64</v>
       </c>
     </row>
     <row r="9">
@@ -6005,7 +6005,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>180</v>
+        <v>1020</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -6017,10 +6017,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>4320</v>
+        <v>10170</v>
       </c>
       <c r="Q9" t="n">
-        <v>24.42</v>
+        <v>128.52</v>
       </c>
     </row>
     <row r="10">
@@ -6058,7 +6058,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -6070,10 +6070,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2010</v>
+        <v>5490</v>
       </c>
       <c r="Q10" t="n">
-        <v>12.52</v>
+        <v>65.88</v>
       </c>
     </row>
     <row r="11">
@@ -7073,7 +7073,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>788.4</v>
+        <v>1144.8</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -7085,22 +7085,22 @@
         <v>4.96</v>
       </c>
       <c r="L5" t="n">
-        <v>12285</v>
+        <v>16020.9</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>114.9</v>
+        <v>123.6</v>
       </c>
       <c r="O5" t="n">
-        <v>445.5</v>
+        <v>678</v>
       </c>
       <c r="P5" t="n">
-        <v>183</v>
+        <v>239.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>595.52</v>
+        <v>3134.32</v>
       </c>
     </row>
     <row r="6">
@@ -7126,7 +7126,7 @@
         <v>112.5</v>
       </c>
       <c r="H6" t="n">
-        <v>188.1</v>
+        <v>342</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -7138,22 +7138,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>4151.4</v>
+        <v>6349.2</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>63</v>
+        <v>130.5</v>
       </c>
       <c r="O6" t="n">
-        <v>105</v>
+        <v>322.5</v>
       </c>
       <c r="P6" t="n">
-        <v>900</v>
+        <v>1318.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>976.65</v>
+        <v>5140.26</v>
       </c>
     </row>
     <row r="7">
@@ -7179,7 +7179,7 @@
         <v>94.5</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>175.2</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -7191,7 +7191,7 @@
         <v>0.64</v>
       </c>
       <c r="L7" t="n">
-        <v>1854</v>
+        <v>2934</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -7203,10 +7203,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1402.5</v>
+        <v>2182.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>83.23</v>
+        <v>438.05</v>
       </c>
     </row>
     <row r="8">
@@ -7244,7 +7244,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>340.8</v>
+        <v>1363.2</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -7256,10 +7256,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1972.2</v>
+        <v>3750.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>45.42</v>
+        <v>239.06</v>
       </c>
     </row>
     <row r="9">
@@ -7297,7 +7297,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>145.8</v>
+        <v>826.2</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -7309,10 +7309,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2160</v>
+        <v>5085</v>
       </c>
       <c r="Q9" t="n">
-        <v>23.69</v>
+        <v>124.66</v>
       </c>
     </row>
     <row r="10">
@@ -7350,7 +7350,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>186.9</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -7362,10 +7362,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1708.5</v>
+        <v>4666.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>12.52</v>
+        <v>65.88</v>
       </c>
     </row>
     <row r="11">
@@ -8365,7 +8365,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>4493880</v>
+        <v>6525360</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -8377,22 +8377,22 @@
         <v>241080.54</v>
       </c>
       <c r="L5" t="n">
-        <v>2211300</v>
+        <v>2883762</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>19533</v>
+        <v>21012</v>
       </c>
       <c r="O5" t="n">
-        <v>75735</v>
+        <v>115260</v>
       </c>
       <c r="P5" t="n">
-        <v>11895</v>
+        <v>15561</v>
       </c>
       <c r="Q5" t="n">
-        <v>357312.71</v>
+        <v>1880593.2</v>
       </c>
     </row>
     <row r="6">
@@ -8418,7 +8418,7 @@
         <v>6075</v>
       </c>
       <c r="H6" t="n">
-        <v>1072170</v>
+        <v>1949400</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -8430,22 +8430,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>747252</v>
+        <v>1142856</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>10710</v>
+        <v>22185</v>
       </c>
       <c r="O6" t="n">
-        <v>17850</v>
+        <v>54825</v>
       </c>
       <c r="P6" t="n">
-        <v>58500</v>
+        <v>85702.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>585989.64</v>
+        <v>3084156</v>
       </c>
     </row>
     <row r="7">
@@ -8471,7 +8471,7 @@
         <v>5103</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>998640</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -8483,7 +8483,7 @@
         <v>30978.73</v>
       </c>
       <c r="L7" t="n">
-        <v>333720</v>
+        <v>528120</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -8495,10 +8495,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>91162.5</v>
+        <v>141862.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>49937.47</v>
+        <v>262828.8</v>
       </c>
     </row>
     <row r="8">
@@ -8536,7 +8536,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>61344</v>
+        <v>245376</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -8548,10 +8548,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>128193</v>
+        <v>243789</v>
       </c>
       <c r="Q8" t="n">
-        <v>27252.61</v>
+        <v>143434.8</v>
       </c>
     </row>
     <row r="9">
@@ -8589,7 +8589,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>26244</v>
+        <v>148716</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -8601,10 +8601,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>140400</v>
+        <v>330525</v>
       </c>
       <c r="Q9" t="n">
-        <v>14211.74</v>
+        <v>74798.64</v>
       </c>
     </row>
     <row r="10">
@@ -8642,7 +8642,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>33642</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -8654,10 +8654,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>111052.5</v>
+        <v>303322.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>7510.32</v>
+        <v>39528</v>
       </c>
     </row>
     <row r="11">
@@ -9604,7 +9604,7 @@
         <v>87060</v>
       </c>
       <c r="H4" t="n">
-        <v>5280</v>
+        <v>6210</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -9616,22 +9616,22 @@
         <v>37</v>
       </c>
       <c r="L4" t="n">
-        <v>138300</v>
+        <v>159330</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>22890</v>
+        <v>23520</v>
       </c>
       <c r="O4" t="n">
-        <v>32910</v>
+        <v>32940</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>33294.81</v>
+        <v>180669.51</v>
       </c>
     </row>
     <row r="5">
@@ -9657,7 +9657,7 @@
         <v>25710</v>
       </c>
       <c r="H5" t="n">
-        <v>3810</v>
+        <v>4290</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -9669,22 +9669,22 @@
         <v>11</v>
       </c>
       <c r="L5" t="n">
-        <v>48660</v>
+        <v>56400</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>8730</v>
+        <v>11580</v>
       </c>
       <c r="O5" t="n">
-        <v>28740</v>
+        <v>28020</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>9408.74</v>
+        <v>51055.2</v>
       </c>
     </row>
     <row r="6">
@@ -9710,7 +9710,7 @@
         <v>7980</v>
       </c>
       <c r="H6" t="n">
-        <v>1440</v>
+        <v>1890</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -9722,22 +9722,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>13890</v>
+        <v>21810</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>4080</v>
+        <v>4650</v>
       </c>
       <c r="O6" t="n">
-        <v>25410</v>
+        <v>26400</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1532.98</v>
+        <v>8318.52</v>
       </c>
     </row>
     <row r="7">
@@ -9763,7 +9763,7 @@
         <v>2910</v>
       </c>
       <c r="H7" t="n">
-        <v>240</v>
+        <v>570</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -9775,22 +9775,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>3780</v>
+        <v>7740</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1650</v>
+        <v>3270</v>
       </c>
       <c r="O7" t="n">
-        <v>11970</v>
+        <v>15960</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>320.2</v>
+        <v>1737.54</v>
       </c>
     </row>
     <row r="8">
@@ -9816,7 +9816,7 @@
         <v>780</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -9828,22 +9828,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2040</v>
+        <v>3510</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>270</v>
+        <v>870</v>
       </c>
       <c r="O8" t="n">
-        <v>2790</v>
+        <v>5250</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>118.54</v>
+        <v>643.23</v>
       </c>
     </row>
     <row r="9">
@@ -9881,22 +9881,22 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="O9" t="n">
-        <v>510</v>
+        <v>960</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.97</v>
+        <v>37.8</v>
       </c>
     </row>
     <row r="10">
@@ -10949,7 +10949,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1371.6</v>
+        <v>1544.4</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -10961,22 +10961,22 @@
         <v>3.64</v>
       </c>
       <c r="L5" t="n">
-        <v>10218.6</v>
+        <v>11844</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>87.3</v>
+        <v>115.8</v>
       </c>
       <c r="O5" t="n">
-        <v>1437</v>
+        <v>1401</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>470.44</v>
+        <v>2552.76</v>
       </c>
     </row>
     <row r="6">
@@ -11002,7 +11002,7 @@
         <v>399</v>
       </c>
       <c r="H6" t="n">
-        <v>820.8</v>
+        <v>1077.3</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -11014,22 +11014,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>5139.3</v>
+        <v>8069.7</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>204</v>
+        <v>232.5</v>
       </c>
       <c r="O6" t="n">
-        <v>6352.5</v>
+        <v>6600</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1149.74</v>
+        <v>6238.89</v>
       </c>
     </row>
     <row r="7">
@@ -11055,7 +11055,7 @@
         <v>436.5</v>
       </c>
       <c r="H7" t="n">
-        <v>175.2</v>
+        <v>416.1</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -11067,22 +11067,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>2268</v>
+        <v>4644</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>115.5</v>
+        <v>228.9</v>
       </c>
       <c r="O7" t="n">
-        <v>4189.5</v>
+        <v>5586</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>256.16</v>
+        <v>1390.03</v>
       </c>
     </row>
     <row r="8">
@@ -11108,7 +11108,7 @@
         <v>507</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -11120,22 +11120,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1448.4</v>
+        <v>2492.1</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>54</v>
+        <v>174</v>
       </c>
       <c r="O8" t="n">
-        <v>1255.5</v>
+        <v>2362.5</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>112.61</v>
+        <v>611.0700000000001</v>
       </c>
     </row>
     <row r="9">
@@ -11173,22 +11173,22 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>97.2</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O9" t="n">
-        <v>280.5</v>
+        <v>528</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.76</v>
+        <v>36.67</v>
       </c>
     </row>
     <row r="10">
@@ -12241,7 +12241,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>7818120</v>
+        <v>8803080</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -12253,22 +12253,22 @@
         <v>176792.4</v>
       </c>
       <c r="L5" t="n">
-        <v>1839348</v>
+        <v>2131920</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>14841</v>
+        <v>19686</v>
       </c>
       <c r="O5" t="n">
-        <v>244290</v>
+        <v>238170</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>282262.32</v>
+        <v>1531656</v>
       </c>
     </row>
     <row r="6">
@@ -12294,7 +12294,7 @@
         <v>21546</v>
       </c>
       <c r="H6" t="n">
-        <v>4678560</v>
+        <v>6140610</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -12306,22 +12306,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>925074</v>
+        <v>1452546</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>34680</v>
+        <v>39525</v>
       </c>
       <c r="O6" t="n">
-        <v>1079925</v>
+        <v>1122000</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>689842.98</v>
+        <v>3743334</v>
       </c>
     </row>
     <row r="7">
@@ -12347,7 +12347,7 @@
         <v>23571</v>
       </c>
       <c r="H7" t="n">
-        <v>998640</v>
+        <v>2371770</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -12359,22 +12359,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>408240</v>
+        <v>835920</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>19635</v>
+        <v>38913</v>
       </c>
       <c r="O7" t="n">
-        <v>712215</v>
+        <v>949620</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>153697.82</v>
+        <v>834019.2</v>
       </c>
     </row>
     <row r="8">
@@ -12400,7 +12400,7 @@
         <v>27378</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>290700</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -12412,22 +12412,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>260712</v>
+        <v>448578</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>9180</v>
+        <v>29580</v>
       </c>
       <c r="O8" t="n">
-        <v>213435</v>
+        <v>401625</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>67566.72</v>
+        <v>366641.1</v>
       </c>
     </row>
     <row r="9">
@@ -12465,22 +12465,22 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>17496</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3060</v>
       </c>
       <c r="O9" t="n">
-        <v>47685</v>
+        <v>89760</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>4054.21</v>
+        <v>21999.6</v>
       </c>
     </row>
     <row r="10">
@@ -13480,7 +13480,7 @@
         <v>83820</v>
       </c>
       <c r="H4" t="n">
-        <v>7080</v>
+        <v>8070</v>
       </c>
       <c r="I4" t="n">
         <v>5</v>
@@ -13492,19 +13492,19 @@
         <v>134</v>
       </c>
       <c r="L4" t="n">
-        <v>172500</v>
+        <v>176880</v>
       </c>
       <c r="M4" t="n">
-        <v>12750</v>
+        <v>150</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>34260</v>
+        <v>37710</v>
       </c>
       <c r="P4" t="n">
-        <v>17940</v>
+        <v>3390</v>
       </c>
       <c r="Q4" t="n">
         <v>35605.65</v>
@@ -13533,7 +13533,7 @@
         <v>68280</v>
       </c>
       <c r="H5" t="n">
-        <v>6270</v>
+        <v>6450</v>
       </c>
       <c r="I5" t="n">
         <v>4</v>
@@ -13545,19 +13545,19 @@
         <v>84</v>
       </c>
       <c r="L5" t="n">
-        <v>164760</v>
+        <v>154260</v>
       </c>
       <c r="M5" t="n">
-        <v>18510</v>
+        <v>1170</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>31260</v>
+        <v>37650</v>
       </c>
       <c r="P5" t="n">
-        <v>29310</v>
+        <v>11250</v>
       </c>
       <c r="Q5" t="n">
         <v>29907.57</v>
@@ -13586,7 +13586,7 @@
         <v>70440</v>
       </c>
       <c r="H6" t="n">
-        <v>7710</v>
+        <v>7350</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -13598,19 +13598,19 @@
         <v>75</v>
       </c>
       <c r="L6" t="n">
-        <v>158820</v>
+        <v>139440</v>
       </c>
       <c r="M6" t="n">
-        <v>14490</v>
+        <v>2160</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>21150</v>
+        <v>21930</v>
       </c>
       <c r="P6" t="n">
-        <v>30690</v>
+        <v>17040</v>
       </c>
       <c r="Q6" t="n">
         <v>31025.36</v>
@@ -13639,7 +13639,7 @@
         <v>86310</v>
       </c>
       <c r="H7" t="n">
-        <v>11760</v>
+        <v>12420</v>
       </c>
       <c r="I7" t="n">
         <v>2</v>
@@ -13651,19 +13651,19 @@
         <v>73</v>
       </c>
       <c r="L7" t="n">
-        <v>202890</v>
+        <v>187770</v>
       </c>
       <c r="M7" t="n">
-        <v>9330</v>
+        <v>4500</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>20370</v>
+        <v>19800</v>
       </c>
       <c r="P7" t="n">
-        <v>33780</v>
+        <v>24210</v>
       </c>
       <c r="Q7" t="n">
         <v>41540.53</v>
@@ -13692,7 +13692,7 @@
         <v>58830</v>
       </c>
       <c r="H8" t="n">
-        <v>2580</v>
+        <v>3270</v>
       </c>
       <c r="I8" t="n">
         <v>2</v>
@@ -13704,19 +13704,19 @@
         <v>40</v>
       </c>
       <c r="L8" t="n">
-        <v>124800</v>
+        <v>120930</v>
       </c>
       <c r="M8" t="n">
-        <v>5760</v>
+        <v>6270</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>18720</v>
+        <v>18600</v>
       </c>
       <c r="P8" t="n">
-        <v>34770</v>
+        <v>30330</v>
       </c>
       <c r="Q8" t="n">
         <v>34400.7</v>
@@ -13745,7 +13745,7 @@
         <v>36330</v>
       </c>
       <c r="H9" t="n">
-        <v>270</v>
+        <v>450</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -13757,19 +13757,19 @@
         <v>34</v>
       </c>
       <c r="L9" t="n">
-        <v>72930</v>
+        <v>82590</v>
       </c>
       <c r="M9" t="n">
-        <v>3600</v>
+        <v>14220</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>27270</v>
+        <v>26580</v>
       </c>
       <c r="P9" t="n">
-        <v>32850</v>
+        <v>31980</v>
       </c>
       <c r="Q9" t="n">
         <v>29025.26</v>
@@ -13810,19 +13810,19 @@
         <v>5</v>
       </c>
       <c r="L10" t="n">
-        <v>38340</v>
+        <v>45720</v>
       </c>
       <c r="M10" t="n">
-        <v>1770</v>
+        <v>9090</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>9720</v>
+        <v>14940</v>
       </c>
       <c r="P10" t="n">
-        <v>37140</v>
+        <v>40290</v>
       </c>
       <c r="Q10" t="n">
         <v>15497.22</v>
@@ -13863,19 +13863,19 @@
         <v>2</v>
       </c>
       <c r="L11" t="n">
-        <v>9390</v>
+        <v>23910</v>
       </c>
       <c r="M11" t="n">
-        <v>630</v>
+        <v>10800</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>810</v>
+        <v>1860</v>
       </c>
       <c r="P11" t="n">
-        <v>32610</v>
+        <v>36630</v>
       </c>
       <c r="Q11" t="n">
         <v>1688.62</v>
@@ -13904,7 +13904,7 @@
         <v>960</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -13916,19 +13916,19 @@
         <v>2</v>
       </c>
       <c r="L12" t="n">
-        <v>4500</v>
+        <v>34410</v>
       </c>
       <c r="M12" t="n">
-        <v>390</v>
+        <v>9660</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P12" t="n">
-        <v>30510</v>
+        <v>49500</v>
       </c>
       <c r="Q12" t="n">
         <v>351.21</v>
@@ -13969,10 +13969,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>2850</v>
+        <v>19710</v>
       </c>
       <c r="M13" t="n">
-        <v>120</v>
+        <v>5370</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -13981,7 +13981,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>23820</v>
+        <v>42270</v>
       </c>
       <c r="Q13" t="n">
         <v>222.75</v>
@@ -14022,10 +14022,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>840</v>
+        <v>5820</v>
       </c>
       <c r="M14" t="n">
-        <v>150</v>
+        <v>8610</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -14034,7 +14034,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>13230</v>
+        <v>22260</v>
       </c>
       <c r="Q14" t="n">
         <v>118.74</v>
@@ -14075,10 +14075,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>480</v>
+        <v>3480</v>
       </c>
       <c r="M15" t="n">
-        <v>60</v>
+        <v>960</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -14087,7 +14087,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>10980</v>
+        <v>11880</v>
       </c>
       <c r="Q15" t="n">
         <v>15.07</v>
@@ -14128,10 +14128,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>270</v>
+        <v>5730</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>390</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -14140,7 +14140,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>12600</v>
+        <v>21270</v>
       </c>
       <c r="Q16" t="n">
         <v>21.76</v>
@@ -14181,10 +14181,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>390</v>
+        <v>2910</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -14193,7 +14193,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>10020</v>
+        <v>23370</v>
       </c>
       <c r="Q17" t="n">
         <v>12.83</v>
@@ -14234,7 +14234,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>360</v>
+        <v>2520</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -14246,7 +14246,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>3480</v>
+        <v>7920</v>
       </c>
       <c r="Q18" t="n">
         <v>5.8</v>
@@ -14287,7 +14287,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>570</v>
+        <v>1290</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -14299,7 +14299,7 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>690</v>
+        <v>1230</v>
       </c>
       <c r="Q19" t="n">
         <v>1.79</v>
@@ -14340,7 +14340,7 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -14825,7 +14825,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>19591.2</v>
+        <v>21265.2</v>
       </c>
       <c r="I5" t="n">
         <v>1.66</v>
@@ -14837,22 +14837,22 @@
         <v>84.73999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>187084.8</v>
+        <v>198040.5</v>
       </c>
       <c r="M5" t="n">
-        <v>1033.8</v>
+        <v>750</v>
       </c>
       <c r="N5" t="n">
-        <v>753.6</v>
+        <v>874.5</v>
       </c>
       <c r="O5" t="n">
-        <v>9115.5</v>
+        <v>10450.5</v>
       </c>
       <c r="P5" t="n">
-        <v>1060.2</v>
+        <v>682.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>6879.67</v>
+        <v>71293.37</v>
       </c>
     </row>
     <row r="6">
@@ -14878,7 +14878,7 @@
         <v>11925</v>
       </c>
       <c r="H6" t="n">
-        <v>26060.4</v>
+        <v>26470.8</v>
       </c>
       <c r="I6" t="n">
         <v>0.51</v>
@@ -14890,22 +14890,22 @@
         <v>83.66</v>
       </c>
       <c r="L6" t="n">
-        <v>216205.8</v>
+        <v>216083.7</v>
       </c>
       <c r="M6" t="n">
-        <v>2762.4</v>
+        <v>1855.2</v>
       </c>
       <c r="N6" t="n">
-        <v>1293</v>
+        <v>1815</v>
       </c>
       <c r="O6" t="n">
-        <v>28522.5</v>
+        <v>31020</v>
       </c>
       <c r="P6" t="n">
-        <v>7780.5</v>
+        <v>5598</v>
       </c>
       <c r="Q6" t="n">
-        <v>72184.14</v>
+        <v>748037.21</v>
       </c>
     </row>
     <row r="7">
@@ -14931,7 +14931,7 @@
         <v>31531.5</v>
       </c>
       <c r="H7" t="n">
-        <v>31733.1</v>
+        <v>33134.7</v>
       </c>
       <c r="I7" t="n">
         <v>1.28</v>
@@ -14943,22 +14943,22 @@
         <v>98.89</v>
       </c>
       <c r="L7" t="n">
-        <v>323676</v>
+        <v>322362</v>
       </c>
       <c r="M7" t="n">
-        <v>8452.5</v>
+        <v>9324</v>
       </c>
       <c r="N7" t="n">
-        <v>632.1</v>
+        <v>972.3</v>
       </c>
       <c r="O7" t="n">
-        <v>29610</v>
+        <v>31825.5</v>
       </c>
       <c r="P7" t="n">
-        <v>15480</v>
+        <v>11332.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>75068.23</v>
+        <v>777924.8100000001</v>
       </c>
     </row>
     <row r="8">
@@ -14984,7 +14984,7 @@
         <v>116142</v>
       </c>
       <c r="H8" t="n">
-        <v>22695</v>
+        <v>23893.5</v>
       </c>
       <c r="I8" t="n">
         <v>2.21</v>
@@ -14996,22 +14996,22 @@
         <v>74.34</v>
       </c>
       <c r="L8" t="n">
-        <v>314728.8</v>
+        <v>312556.2</v>
       </c>
       <c r="M8" t="n">
-        <v>10560</v>
+        <v>14437.5</v>
       </c>
       <c r="N8" t="n">
-        <v>330</v>
+        <v>792</v>
       </c>
       <c r="O8" t="n">
-        <v>27540</v>
+        <v>29443.5</v>
       </c>
       <c r="P8" t="n">
-        <v>26163</v>
+        <v>20953.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>75070.00999999999</v>
+        <v>777943.2</v>
       </c>
     </row>
     <row r="9">
@@ -15037,7 +15037,7 @@
         <v>137725.5</v>
       </c>
       <c r="H9" t="n">
-        <v>8040</v>
+        <v>11010</v>
       </c>
       <c r="I9" t="n">
         <v>0.8</v>
@@ -15049,22 +15049,22 @@
         <v>88.33</v>
       </c>
       <c r="L9" t="n">
-        <v>305718.3</v>
+        <v>320079.6</v>
       </c>
       <c r="M9" t="n">
-        <v>8148</v>
+        <v>24087</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O9" t="n">
-        <v>30343.5</v>
+        <v>35788.5</v>
       </c>
       <c r="P9" t="n">
-        <v>34140</v>
+        <v>31380</v>
       </c>
       <c r="Q9" t="n">
-        <v>73180.95</v>
+        <v>758367.1</v>
       </c>
     </row>
     <row r="10">
@@ -15090,7 +15090,7 @@
         <v>133470</v>
       </c>
       <c r="H10" t="n">
-        <v>3840</v>
+        <v>3660</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -15102,22 +15102,22 @@
         <v>49.59</v>
       </c>
       <c r="L10" t="n">
-        <v>256640.4</v>
+        <v>284541.9</v>
       </c>
       <c r="M10" t="n">
-        <v>8695.5</v>
+        <v>20833.5</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>22449</v>
+        <v>31878</v>
       </c>
       <c r="P10" t="n">
-        <v>65739</v>
+        <v>65407.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>61088.39</v>
+        <v>633053.0699999999</v>
       </c>
     </row>
     <row r="11">
@@ -15143,7 +15143,7 @@
         <v>75930</v>
       </c>
       <c r="H11" t="n">
-        <v>4800</v>
+        <v>4560</v>
       </c>
       <c r="I11" t="n">
         <v>2.7</v>
@@ -15155,22 +15155,22 @@
         <v>30.55</v>
       </c>
       <c r="L11" t="n">
-        <v>181020</v>
+        <v>217290</v>
       </c>
       <c r="M11" t="n">
-        <v>5589</v>
+        <v>23598</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>9256.5</v>
+        <v>18079.5</v>
       </c>
       <c r="P11" t="n">
-        <v>65718</v>
+        <v>82107</v>
       </c>
       <c r="Q11" t="n">
-        <v>38457.81</v>
+        <v>398534.53</v>
       </c>
     </row>
     <row r="12">
@@ -15196,7 +15196,7 @@
         <v>59790</v>
       </c>
       <c r="H12" t="n">
-        <v>4800</v>
+        <v>5700</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -15208,22 +15208,22 @@
         <v>11.12</v>
       </c>
       <c r="L12" t="n">
-        <v>149430</v>
+        <v>198960</v>
       </c>
       <c r="M12" t="n">
-        <v>3306</v>
+        <v>21688.5</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>4200</v>
+        <v>11760</v>
       </c>
       <c r="P12" t="n">
-        <v>59130</v>
+        <v>97950</v>
       </c>
       <c r="Q12" t="n">
-        <v>27193.91</v>
+        <v>281807.82</v>
       </c>
     </row>
     <row r="13">
@@ -15249,7 +15249,7 @@
         <v>48150</v>
       </c>
       <c r="H13" t="n">
-        <v>1320</v>
+        <v>1830</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -15261,22 +15261,22 @@
         <v>5.7</v>
       </c>
       <c r="L13" t="n">
-        <v>95400</v>
+        <v>133200</v>
       </c>
       <c r="M13" t="n">
-        <v>2700</v>
+        <v>16440</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2400</v>
+        <v>3900</v>
       </c>
       <c r="P13" t="n">
-        <v>42270</v>
+        <v>70620</v>
       </c>
       <c r="Q13" t="n">
-        <v>18591.22</v>
+        <v>192659.02</v>
       </c>
     </row>
     <row r="14">
@@ -15302,7 +15302,7 @@
         <v>22020</v>
       </c>
       <c r="H14" t="n">
-        <v>810</v>
+        <v>780</v>
       </c>
       <c r="I14" t="n">
         <v>0.97</v>
@@ -15314,22 +15314,22 @@
         <v>0.97</v>
       </c>
       <c r="L14" t="n">
-        <v>41310</v>
+        <v>57450</v>
       </c>
       <c r="M14" t="n">
-        <v>1140</v>
+        <v>16890</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3510</v>
+        <v>3210</v>
       </c>
       <c r="P14" t="n">
-        <v>28080</v>
+        <v>36390</v>
       </c>
       <c r="Q14" t="n">
-        <v>8752.790000000001</v>
+        <v>90704.3</v>
       </c>
     </row>
     <row r="15">
@@ -15355,7 +15355,7 @@
         <v>5550</v>
       </c>
       <c r="H15" t="n">
-        <v>270</v>
+        <v>510</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -15367,22 +15367,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>16170</v>
+        <v>30300</v>
       </c>
       <c r="M15" t="n">
-        <v>300</v>
+        <v>6000</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>750</v>
+        <v>1290</v>
       </c>
       <c r="P15" t="n">
-        <v>30270</v>
+        <v>33420</v>
       </c>
       <c r="Q15" t="n">
-        <v>3142.43</v>
+        <v>32564.73</v>
       </c>
     </row>
     <row r="16">
@@ -15408,7 +15408,7 @@
         <v>3750</v>
       </c>
       <c r="H16" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -15420,22 +15420,22 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>7050</v>
+        <v>23970</v>
       </c>
       <c r="M16" t="n">
+        <v>3150</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
         <v>150</v>
       </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>30</v>
-      </c>
       <c r="P16" t="n">
-        <v>38520</v>
+        <v>55560</v>
       </c>
       <c r="Q16" t="n">
-        <v>2199.97</v>
+        <v>22798.08</v>
       </c>
     </row>
     <row r="17">
@@ -15461,7 +15461,7 @@
         <v>1290</v>
       </c>
       <c r="H17" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -15473,10 +15473,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>2280</v>
+        <v>9300</v>
       </c>
       <c r="M17" t="n">
-        <v>150</v>
+        <v>1590</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -15485,10 +15485,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>21210</v>
+        <v>32580</v>
       </c>
       <c r="Q17" t="n">
-        <v>1135.2</v>
+        <v>11763.92</v>
       </c>
     </row>
     <row r="18">
@@ -15514,7 +15514,7 @@
         <v>300</v>
       </c>
       <c r="H18" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -15526,10 +15526,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1560</v>
+        <v>6150</v>
       </c>
       <c r="M18" t="n">
-        <v>210</v>
+        <v>990</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -15538,10 +15538,10 @@
         <v>30</v>
       </c>
       <c r="P18" t="n">
-        <v>21450</v>
+        <v>30690</v>
       </c>
       <c r="Q18" t="n">
-        <v>536.6799999999999</v>
+        <v>5561.61</v>
       </c>
     </row>
     <row r="19">
@@ -15579,22 +15579,22 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1440</v>
+        <v>3900</v>
       </c>
       <c r="M19" t="n">
-        <v>90</v>
+        <v>1200</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="P19" t="n">
-        <v>17580</v>
+        <v>31080</v>
       </c>
       <c r="Q19" t="n">
-        <v>249.31</v>
+        <v>2583.62</v>
       </c>
     </row>
     <row r="20">
@@ -15620,7 +15620,7 @@
         <v>3690</v>
       </c>
       <c r="H20" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -15632,10 +15632,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>660</v>
+        <v>3150</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1680</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -15644,10 +15644,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1950</v>
+        <v>5190</v>
       </c>
       <c r="Q20" t="n">
-        <v>73.66</v>
+        <v>763.29</v>
       </c>
     </row>
     <row r="21">
@@ -15697,10 +15697,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="Q21" t="n">
-        <v>14.73</v>
+        <v>152.66</v>
       </c>
     </row>
     <row r="22">
@@ -15738,7 +15738,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -15753,7 +15753,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.45</v>
+        <v>15.03</v>
       </c>
     </row>
     <row r="23">
@@ -15791,7 +15791,7 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -16117,7 +16117,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2257.2</v>
+        <v>2322</v>
       </c>
       <c r="I5" t="n">
         <v>1.32</v>
@@ -16129,19 +16129,19 @@
         <v>27.8</v>
       </c>
       <c r="L5" t="n">
-        <v>34599.6</v>
+        <v>32394.6</v>
       </c>
       <c r="M5" t="n">
-        <v>370.2</v>
+        <v>23.4</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>1563</v>
+        <v>1882.5</v>
       </c>
       <c r="P5" t="n">
-        <v>586.2</v>
+        <v>225</v>
       </c>
       <c r="Q5" t="n">
         <v>1495.38</v>
@@ -16170,7 +16170,7 @@
         <v>3522</v>
       </c>
       <c r="H6" t="n">
-        <v>4394.7</v>
+        <v>4189.5</v>
       </c>
       <c r="I6" t="n">
         <v>0.51</v>
@@ -16182,19 +16182,19 @@
         <v>38.02</v>
       </c>
       <c r="L6" t="n">
-        <v>58763.4</v>
+        <v>51592.8</v>
       </c>
       <c r="M6" t="n">
-        <v>1159.2</v>
+        <v>172.8</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>5287.5</v>
+        <v>5482.5</v>
       </c>
       <c r="P6" t="n">
-        <v>4603.5</v>
+        <v>2556</v>
       </c>
       <c r="Q6" t="n">
         <v>23269.02</v>
@@ -16223,7 +16223,7 @@
         <v>12946.5</v>
       </c>
       <c r="H7" t="n">
-        <v>8584.799999999999</v>
+        <v>9066.6</v>
       </c>
       <c r="I7" t="n">
         <v>1.28</v>
@@ -16235,19 +16235,19 @@
         <v>46.57</v>
       </c>
       <c r="L7" t="n">
-        <v>121734</v>
+        <v>112662</v>
       </c>
       <c r="M7" t="n">
-        <v>3265.5</v>
+        <v>1575</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>7129.5</v>
+        <v>6930</v>
       </c>
       <c r="P7" t="n">
-        <v>8445</v>
+        <v>6052.5</v>
       </c>
       <c r="Q7" t="n">
         <v>33232.43</v>
@@ -16276,7 +16276,7 @@
         <v>38239.5</v>
       </c>
       <c r="H8" t="n">
-        <v>2193</v>
+        <v>2779.5</v>
       </c>
       <c r="I8" t="n">
         <v>1.47</v>
@@ -16288,19 +16288,19 @@
         <v>29.44</v>
       </c>
       <c r="L8" t="n">
-        <v>88608</v>
+        <v>85860.3</v>
       </c>
       <c r="M8" t="n">
-        <v>3168</v>
+        <v>3448.5</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>8424</v>
+        <v>8370</v>
       </c>
       <c r="P8" t="n">
-        <v>13212.6</v>
+        <v>11525.4</v>
       </c>
       <c r="Q8" t="n">
         <v>32680.66</v>
@@ -16329,7 +16329,7 @@
         <v>30880.5</v>
       </c>
       <c r="H9" t="n">
-        <v>270</v>
+        <v>450</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -16341,19 +16341,19 @@
         <v>27.3</v>
       </c>
       <c r="L9" t="n">
-        <v>59073.3</v>
+        <v>66897.89999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>2520</v>
+        <v>9954</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>14998.5</v>
+        <v>14619</v>
       </c>
       <c r="P9" t="n">
-        <v>16425</v>
+        <v>15990</v>
       </c>
       <c r="Q9" t="n">
         <v>28154.5</v>
@@ -16394,19 +16394,19 @@
         <v>4.35</v>
       </c>
       <c r="L10" t="n">
-        <v>34122.6</v>
+        <v>40690.8</v>
       </c>
       <c r="M10" t="n">
-        <v>1504.5</v>
+        <v>7726.5</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>6804</v>
+        <v>10458</v>
       </c>
       <c r="P10" t="n">
-        <v>31569</v>
+        <v>34246.5</v>
       </c>
       <c r="Q10" t="n">
         <v>15497.22</v>
@@ -16447,19 +16447,19 @@
         <v>1.8</v>
       </c>
       <c r="L11" t="n">
-        <v>9390</v>
+        <v>23910</v>
       </c>
       <c r="M11" t="n">
-        <v>567</v>
+        <v>9720</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>688.5</v>
+        <v>1581</v>
       </c>
       <c r="P11" t="n">
-        <v>29349</v>
+        <v>32967</v>
       </c>
       <c r="Q11" t="n">
         <v>1688.62</v>
@@ -16488,7 +16488,7 @@
         <v>960</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -16500,19 +16500,19 @@
         <v>1.85</v>
       </c>
       <c r="L12" t="n">
-        <v>4500</v>
+        <v>34410</v>
       </c>
       <c r="M12" t="n">
-        <v>370.5</v>
+        <v>9177</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P12" t="n">
-        <v>30510</v>
+        <v>49500</v>
       </c>
       <c r="Q12" t="n">
         <v>351.21</v>
@@ -16553,10 +16553,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>2850</v>
+        <v>19710</v>
       </c>
       <c r="M13" t="n">
-        <v>120</v>
+        <v>5370</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -16565,7 +16565,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>23820</v>
+        <v>42270</v>
       </c>
       <c r="Q13" t="n">
         <v>222.75</v>
@@ -16606,10 +16606,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>840</v>
+        <v>5820</v>
       </c>
       <c r="M14" t="n">
-        <v>150</v>
+        <v>8610</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -16618,7 +16618,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>13230</v>
+        <v>22260</v>
       </c>
       <c r="Q14" t="n">
         <v>118.74</v>
@@ -16659,10 +16659,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>480</v>
+        <v>3480</v>
       </c>
       <c r="M15" t="n">
-        <v>60</v>
+        <v>960</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -16671,7 +16671,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>10980</v>
+        <v>11880</v>
       </c>
       <c r="Q15" t="n">
         <v>15.07</v>
@@ -16712,10 +16712,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>270</v>
+        <v>5730</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>390</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -16724,7 +16724,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>12600</v>
+        <v>21270</v>
       </c>
       <c r="Q16" t="n">
         <v>21.76</v>
@@ -16765,10 +16765,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>390</v>
+        <v>2910</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -16777,7 +16777,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>10020</v>
+        <v>23370</v>
       </c>
       <c r="Q17" t="n">
         <v>12.83</v>
@@ -16818,7 +16818,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>360</v>
+        <v>2520</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -16830,7 +16830,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>3480</v>
+        <v>7920</v>
       </c>
       <c r="Q18" t="n">
         <v>5.8</v>
@@ -16871,7 +16871,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>570</v>
+        <v>1290</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -16883,7 +16883,7 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>690</v>
+        <v>1230</v>
       </c>
       <c r="Q19" t="n">
         <v>1.79</v>
@@ -16924,7 +16924,7 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -17409,7 +17409,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>12866040</v>
+        <v>13235400</v>
       </c>
       <c r="I5" t="n">
         <v>257152.58</v>
@@ -17421,19 +17421,19 @@
         <v>1350051.02</v>
       </c>
       <c r="L5" t="n">
-        <v>6227928</v>
+        <v>5831028</v>
       </c>
       <c r="M5" t="n">
-        <v>129570</v>
+        <v>8190</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>265710</v>
+        <v>320025</v>
       </c>
       <c r="P5" t="n">
-        <v>38103</v>
+        <v>14625</v>
       </c>
       <c r="Q5" t="n">
         <v>897227.17</v>
@@ -17462,7 +17462,7 @@
         <v>190188</v>
       </c>
       <c r="H6" t="n">
-        <v>25049790</v>
+        <v>23880150</v>
       </c>
       <c r="I6" t="n">
         <v>98471.57000000001</v>
@@ -17474,19 +17474,19 @@
         <v>1846341.9</v>
       </c>
       <c r="L6" t="n">
-        <v>10577412</v>
+        <v>9286704</v>
       </c>
       <c r="M6" t="n">
-        <v>405720</v>
+        <v>60480</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>898875</v>
+        <v>932025</v>
       </c>
       <c r="P6" t="n">
-        <v>299227.5</v>
+        <v>166140</v>
       </c>
       <c r="Q6" t="n">
         <v>13961411.1</v>
@@ -17515,7 +17515,7 @@
         <v>699111</v>
       </c>
       <c r="H7" t="n">
-        <v>48933360</v>
+        <v>51679620</v>
       </c>
       <c r="I7" t="n">
         <v>247829.82</v>
@@ -17527,19 +17527,19 @@
         <v>2261447.14</v>
       </c>
       <c r="L7" t="n">
-        <v>21912120</v>
+        <v>20279160</v>
       </c>
       <c r="M7" t="n">
-        <v>1142925</v>
+        <v>551250</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1212015</v>
+        <v>1178100</v>
       </c>
       <c r="P7" t="n">
-        <v>548925</v>
+        <v>393412.5</v>
       </c>
       <c r="Q7" t="n">
         <v>19939455.94</v>
@@ -17568,7 +17568,7 @@
         <v>2064933</v>
       </c>
       <c r="H8" t="n">
-        <v>12500100</v>
+        <v>15843150</v>
       </c>
       <c r="I8" t="n">
         <v>285897.73</v>
@@ -17580,19 +17580,19 @@
         <v>1429488.64</v>
       </c>
       <c r="L8" t="n">
-        <v>15949440</v>
+        <v>15454854</v>
       </c>
       <c r="M8" t="n">
-        <v>1108800</v>
+        <v>1206975</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1432080</v>
+        <v>1422900</v>
       </c>
       <c r="P8" t="n">
-        <v>858819</v>
+        <v>749151</v>
       </c>
       <c r="Q8" t="n">
         <v>19608399</v>
@@ -17621,7 +17621,7 @@
         <v>1667547</v>
       </c>
       <c r="H9" t="n">
-        <v>1539000</v>
+        <v>2565000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -17633,19 +17633,19 @@
         <v>1325675.91</v>
       </c>
       <c r="L9" t="n">
-        <v>10633194</v>
+        <v>12041622</v>
       </c>
       <c r="M9" t="n">
-        <v>882000</v>
+        <v>3483900</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2549745</v>
+        <v>2485230</v>
       </c>
       <c r="P9" t="n">
-        <v>1067625</v>
+        <v>1039350</v>
       </c>
       <c r="Q9" t="n">
         <v>16892702.95</v>
@@ -17686,19 +17686,19 @@
         <v>211218.6</v>
       </c>
       <c r="L10" t="n">
-        <v>6142068</v>
+        <v>7324344</v>
       </c>
       <c r="M10" t="n">
-        <v>526575</v>
+        <v>2704275</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1156680</v>
+        <v>1777860</v>
       </c>
       <c r="P10" t="n">
-        <v>2051985</v>
+        <v>2226022.5</v>
       </c>
       <c r="Q10" t="n">
         <v>9298333.439999999</v>
@@ -17739,19 +17739,19 @@
         <v>87255.13</v>
       </c>
       <c r="L11" t="n">
-        <v>1690200</v>
+        <v>4303800</v>
       </c>
       <c r="M11" t="n">
-        <v>198450</v>
+        <v>3402000</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>117045</v>
+        <v>268770</v>
       </c>
       <c r="P11" t="n">
-        <v>1907685</v>
+        <v>2142855</v>
       </c>
       <c r="Q11" t="n">
         <v>1013171.76</v>
@@ -17780,7 +17780,7 @@
         <v>51840</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>513000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -17792,19 +17792,19 @@
         <v>90022.82000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>810000</v>
+        <v>6193800</v>
       </c>
       <c r="M12" t="n">
-        <v>129675</v>
+        <v>3211950</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>5100</v>
       </c>
       <c r="P12" t="n">
-        <v>1983150</v>
+        <v>3217500</v>
       </c>
       <c r="Q12" t="n">
         <v>210723.12</v>
@@ -17845,10 +17845,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>513000</v>
+        <v>3547800</v>
       </c>
       <c r="M13" t="n">
-        <v>42000</v>
+        <v>1879500</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -17857,7 +17857,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1548300</v>
+        <v>2747550</v>
       </c>
       <c r="Q13" t="n">
         <v>133652.16</v>
@@ -17898,10 +17898,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>151200</v>
+        <v>1047600</v>
       </c>
       <c r="M14" t="n">
-        <v>52500</v>
+        <v>3013500</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -17910,7 +17910,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>859950</v>
+        <v>1446900</v>
       </c>
       <c r="Q14" t="n">
         <v>71245.44</v>
@@ -17951,10 +17951,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>86400</v>
+        <v>626400</v>
       </c>
       <c r="M15" t="n">
-        <v>21000</v>
+        <v>336000</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -17963,7 +17963,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>713700</v>
+        <v>772200</v>
       </c>
       <c r="Q15" t="n">
         <v>9039.6</v>
@@ -18004,10 +18004,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>48600</v>
+        <v>1031400</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>136500</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -18016,7 +18016,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>819000</v>
+        <v>1382550</v>
       </c>
       <c r="Q16" t="n">
         <v>13057.2</v>
@@ -18057,10 +18057,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>70200</v>
+        <v>523800</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>31500</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -18069,7 +18069,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>651300</v>
+        <v>1519050</v>
       </c>
       <c r="Q17" t="n">
         <v>7700.4</v>
@@ -18110,7 +18110,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>64800</v>
+        <v>453600</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -18122,7 +18122,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>226200</v>
+        <v>514800</v>
       </c>
       <c r="Q18" t="n">
         <v>3481.92</v>
@@ -18163,7 +18163,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>102600</v>
+        <v>232200</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -18175,7 +18175,7 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>44850</v>
+        <v>79950</v>
       </c>
       <c r="Q19" t="n">
         <v>1071.36</v>
@@ -18216,7 +18216,7 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>37800</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -18648,7 +18648,7 @@
         <v>107220</v>
       </c>
       <c r="H4" t="n">
-        <v>13650</v>
+        <v>16080</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -18660,22 +18660,22 @@
         <v>48</v>
       </c>
       <c r="L4" t="n">
-        <v>345540</v>
+        <v>388710</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>17670</v>
+        <v>14280</v>
       </c>
       <c r="O4" t="n">
-        <v>55260</v>
+        <v>54930</v>
       </c>
       <c r="P4" t="n">
-        <v>7650</v>
+        <v>2970</v>
       </c>
       <c r="Q4" t="n">
-        <v>34208.52</v>
+        <v>391972.68</v>
       </c>
     </row>
     <row r="5">
@@ -18701,7 +18701,7 @@
         <v>30540</v>
       </c>
       <c r="H5" t="n">
-        <v>2910</v>
+        <v>4830</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -18713,22 +18713,22 @@
         <v>15</v>
       </c>
       <c r="L5" t="n">
-        <v>111990</v>
+        <v>141450</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>25440</v>
+        <v>30000</v>
       </c>
       <c r="O5" t="n">
-        <v>34680</v>
+        <v>47790</v>
       </c>
       <c r="P5" t="n">
-        <v>6540</v>
+        <v>8340</v>
       </c>
       <c r="Q5" t="n">
-        <v>11143.01</v>
+        <v>127680.3</v>
       </c>
     </row>
     <row r="6">
@@ -18754,7 +18754,7 @@
         <v>4110</v>
       </c>
       <c r="H6" t="n">
-        <v>330</v>
+        <v>450</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -18766,22 +18766,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>18780</v>
+        <v>30060</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>5580</v>
+        <v>10080</v>
       </c>
       <c r="O6" t="n">
-        <v>7560</v>
+        <v>9930</v>
       </c>
       <c r="P6" t="n">
-        <v>3840</v>
+        <v>7950</v>
       </c>
       <c r="Q6" t="n">
-        <v>1096.85</v>
+        <v>12568.05</v>
       </c>
     </row>
     <row r="7">
@@ -18819,22 +18819,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
+        <v>7800</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>420</v>
+      </c>
+      <c r="O7" t="n">
         <v>3090</v>
       </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>150</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1800</v>
-      </c>
       <c r="P7" t="n">
-        <v>3630</v>
+        <v>8790</v>
       </c>
       <c r="Q7" t="n">
-        <v>144.12</v>
+        <v>1651.32</v>
       </c>
     </row>
     <row r="8">
@@ -18872,7 +18872,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>480</v>
+        <v>1140</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -18881,13 +18881,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>390</v>
+        <v>840</v>
       </c>
       <c r="P8" t="n">
-        <v>1710</v>
+        <v>6000</v>
       </c>
       <c r="Q8" t="n">
-        <v>11.84</v>
+        <v>135.63</v>
       </c>
     </row>
     <row r="9">
@@ -18925,7 +18925,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -18937,10 +18937,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.09</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="10">
@@ -18978,7 +18978,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -19031,7 +19031,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -19993,7 +19993,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1047.6</v>
+        <v>1738.8</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -20005,22 +20005,22 @@
         <v>4.96</v>
       </c>
       <c r="L5" t="n">
-        <v>23517.9</v>
+        <v>29704.5</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>254.4</v>
+        <v>300</v>
       </c>
       <c r="O5" t="n">
-        <v>1734</v>
+        <v>2389.5</v>
       </c>
       <c r="P5" t="n">
-        <v>130.8</v>
+        <v>166.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>557.15</v>
+        <v>6384.02</v>
       </c>
     </row>
     <row r="6">
@@ -20046,7 +20046,7 @@
         <v>205.5</v>
       </c>
       <c r="H6" t="n">
-        <v>188.1</v>
+        <v>256.5</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -20058,22 +20058,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>6948.6</v>
+        <v>11122.2</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>279</v>
+        <v>504</v>
       </c>
       <c r="O6" t="n">
-        <v>1890</v>
+        <v>2482.5</v>
       </c>
       <c r="P6" t="n">
-        <v>576</v>
+        <v>1192.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>822.64</v>
+        <v>9426.040000000001</v>
       </c>
     </row>
     <row r="7">
@@ -20111,22 +20111,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1854</v>
+        <v>4680</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>10.5</v>
+        <v>29.4</v>
       </c>
       <c r="O7" t="n">
-        <v>630</v>
+        <v>1081.5</v>
       </c>
       <c r="P7" t="n">
-        <v>907.5</v>
+        <v>2197.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>115.29</v>
+        <v>1321.06</v>
       </c>
     </row>
     <row r="8">
@@ -20164,7 +20164,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>340.8</v>
+        <v>809.4</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -20173,13 +20173,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>175.5</v>
+        <v>378</v>
       </c>
       <c r="P8" t="n">
-        <v>649.8</v>
+        <v>2280</v>
       </c>
       <c r="Q8" t="n">
-        <v>11.24</v>
+        <v>128.85</v>
       </c>
     </row>
     <row r="9">
@@ -20217,7 +20217,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>48.6</v>
+        <v>121.5</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -20229,10 +20229,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.08</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="10">
@@ -20270,7 +20270,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>160.2</v>
+        <v>133.5</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -20323,7 +20323,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -21285,7 +21285,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>5971320</v>
+        <v>9911160</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -21297,22 +21297,22 @@
         <v>241080.54</v>
       </c>
       <c r="L5" t="n">
-        <v>4233222</v>
+        <v>5346810</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>43248</v>
+        <v>51000</v>
       </c>
       <c r="O5" t="n">
-        <v>294780</v>
+        <v>406215</v>
       </c>
       <c r="P5" t="n">
-        <v>8502</v>
+        <v>10842</v>
       </c>
       <c r="Q5" t="n">
-        <v>334290.24</v>
+        <v>3830409</v>
       </c>
     </row>
     <row r="6">
@@ -21338,7 +21338,7 @@
         <v>11097</v>
       </c>
       <c r="H6" t="n">
-        <v>1072170</v>
+        <v>1462050</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -21350,22 +21350,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1250748</v>
+        <v>2001996</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>47430</v>
+        <v>85680</v>
       </c>
       <c r="O6" t="n">
-        <v>321300</v>
+        <v>422025</v>
       </c>
       <c r="P6" t="n">
-        <v>37440</v>
+        <v>77512.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>493581.6</v>
+        <v>5655622.5</v>
       </c>
     </row>
     <row r="7">
@@ -21403,22 +21403,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>333720</v>
+        <v>842400</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1785</v>
+        <v>4998</v>
       </c>
       <c r="O7" t="n">
-        <v>107100</v>
+        <v>183855</v>
       </c>
       <c r="P7" t="n">
-        <v>58987.5</v>
+        <v>142837.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>69175.3</v>
+        <v>792633.6</v>
       </c>
     </row>
     <row r="8">
@@ -21456,7 +21456,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>61344</v>
+        <v>145692</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -21465,13 +21465,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>29835</v>
+        <v>64260</v>
       </c>
       <c r="P8" t="n">
-        <v>42237</v>
+        <v>148200</v>
       </c>
       <c r="Q8" t="n">
-        <v>6746.98</v>
+        <v>77309.10000000001</v>
       </c>
     </row>
     <row r="9">
@@ -21509,7 +21509,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>8748</v>
+        <v>21870</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -21521,10 +21521,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>975</v>
+        <v>2925</v>
       </c>
       <c r="Q9" t="n">
-        <v>50.28</v>
+        <v>576.1799999999999</v>
       </c>
     </row>
     <row r="10">
@@ -21562,7 +21562,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>28836</v>
+        <v>24030</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -21615,7 +21615,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>16200</v>
+        <v>32400</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -22577,7 +22577,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>111669840</v>
+        <v>121211640</v>
       </c>
       <c r="I5" t="n">
         <v>321440.72</v>
@@ -22589,22 +22589,22 @@
         <v>4114441.22</v>
       </c>
       <c r="L5" t="n">
-        <v>33675264</v>
+        <v>35647290</v>
       </c>
       <c r="M5" t="n">
-        <v>361830</v>
+        <v>262500</v>
       </c>
       <c r="N5" t="n">
-        <v>128112</v>
+        <v>148665</v>
       </c>
       <c r="O5" t="n">
-        <v>1549635</v>
+        <v>1776585</v>
       </c>
       <c r="P5" t="n">
-        <v>68913</v>
+        <v>44343</v>
       </c>
       <c r="Q5" t="n">
-        <v>4127802.77</v>
+        <v>42776020.62</v>
       </c>
     </row>
     <row r="6">
@@ -22630,7 +22630,7 @@
         <v>643950</v>
       </c>
       <c r="H6" t="n">
-        <v>148544280</v>
+        <v>150883560</v>
       </c>
       <c r="I6" t="n">
         <v>98471.57000000001</v>
@@ -22642,22 +22642,22 @@
         <v>4061952.18</v>
       </c>
       <c r="L6" t="n">
-        <v>38917044</v>
+        <v>38895066</v>
       </c>
       <c r="M6" t="n">
-        <v>966840</v>
+        <v>649320</v>
       </c>
       <c r="N6" t="n">
-        <v>219810</v>
+        <v>308550</v>
       </c>
       <c r="O6" t="n">
-        <v>4848825</v>
+        <v>5273400</v>
       </c>
       <c r="P6" t="n">
-        <v>505732.5</v>
+        <v>363870</v>
       </c>
       <c r="Q6" t="n">
-        <v>43310481.3</v>
+        <v>448822326.38</v>
       </c>
     </row>
     <row r="7">
@@ -22683,7 +22683,7 @@
         <v>1702701</v>
       </c>
       <c r="H7" t="n">
-        <v>180878670</v>
+        <v>188867790</v>
       </c>
       <c r="I7" t="n">
         <v>247829.82</v>
@@ -22695,22 +22695,22 @@
         <v>4801702.84</v>
       </c>
       <c r="L7" t="n">
-        <v>58261680</v>
+        <v>58025160</v>
       </c>
       <c r="M7" t="n">
-        <v>2958375</v>
+        <v>3263400</v>
       </c>
       <c r="N7" t="n">
-        <v>107457</v>
+        <v>165291</v>
       </c>
       <c r="O7" t="n">
-        <v>5033700</v>
+        <v>5410335</v>
       </c>
       <c r="P7" t="n">
-        <v>1006200</v>
+        <v>736612.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>45040938.62</v>
+        <v>466754888.16</v>
       </c>
     </row>
     <row r="8">
@@ -22736,7 +22736,7 @@
         <v>6271668</v>
       </c>
       <c r="H8" t="n">
-        <v>129361500</v>
+        <v>136192950</v>
       </c>
       <c r="I8" t="n">
         <v>428846.59</v>
@@ -22748,22 +22748,22 @@
         <v>3609458.82</v>
       </c>
       <c r="L8" t="n">
-        <v>56651184</v>
+        <v>56260116</v>
       </c>
       <c r="M8" t="n">
-        <v>3696000</v>
+        <v>5053125</v>
       </c>
       <c r="N8" t="n">
-        <v>56100</v>
+        <v>134640</v>
       </c>
       <c r="O8" t="n">
-        <v>4681800</v>
+        <v>5005395</v>
       </c>
       <c r="P8" t="n">
-        <v>1700595</v>
+        <v>1361958</v>
       </c>
       <c r="Q8" t="n">
-        <v>45042003.29</v>
+        <v>466765921.17</v>
       </c>
     </row>
     <row r="9">
@@ -22789,7 +22789,7 @@
         <v>7437177</v>
       </c>
       <c r="H9" t="n">
-        <v>45828000</v>
+        <v>62757000</v>
       </c>
       <c r="I9" t="n">
         <v>155961.87</v>
@@ -22801,22 +22801,22 @@
         <v>4288951.48</v>
       </c>
       <c r="L9" t="n">
-        <v>55029294</v>
+        <v>57614328</v>
       </c>
       <c r="M9" t="n">
-        <v>2851800</v>
+        <v>8430450</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3060</v>
       </c>
       <c r="O9" t="n">
-        <v>5158395</v>
+        <v>6084045</v>
       </c>
       <c r="P9" t="n">
-        <v>2219100</v>
+        <v>2039700</v>
       </c>
       <c r="Q9" t="n">
-        <v>43908570.03</v>
+        <v>455020261.99</v>
       </c>
     </row>
     <row r="10">
@@ -22842,7 +22842,7 @@
         <v>7207380</v>
       </c>
       <c r="H10" t="n">
-        <v>21888000</v>
+        <v>20862000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -22854,22 +22854,22 @@
         <v>2407892.04</v>
       </c>
       <c r="L10" t="n">
-        <v>46195272</v>
+        <v>51217542</v>
       </c>
       <c r="M10" t="n">
-        <v>3043425</v>
+        <v>7291725</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3816330</v>
+        <v>5419260</v>
       </c>
       <c r="P10" t="n">
-        <v>4273035</v>
+        <v>4251487.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>36653033.52</v>
+        <v>379831839.3</v>
       </c>
     </row>
     <row r="11">
@@ -22895,7 +22895,7 @@
         <v>4100220</v>
       </c>
       <c r="H11" t="n">
-        <v>27360000</v>
+        <v>25992000</v>
       </c>
       <c r="I11" t="n">
         <v>523530.79</v>
@@ -22907,22 +22907,22 @@
         <v>1483337.24</v>
       </c>
       <c r="L11" t="n">
-        <v>32583600</v>
+        <v>39112200</v>
       </c>
       <c r="M11" t="n">
-        <v>1956150</v>
+        <v>8259300</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>1573605</v>
+        <v>3073515</v>
       </c>
       <c r="P11" t="n">
-        <v>4271670</v>
+        <v>5336955</v>
       </c>
       <c r="Q11" t="n">
-        <v>23074683.84</v>
+        <v>239120715.6</v>
       </c>
     </row>
     <row r="12">
@@ -22948,7 +22948,7 @@
         <v>3228660</v>
       </c>
       <c r="H12" t="n">
-        <v>27360000</v>
+        <v>32490000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -22960,22 +22960,22 @@
         <v>540136.9399999999</v>
       </c>
       <c r="L12" t="n">
-        <v>26897400</v>
+        <v>35812800</v>
       </c>
       <c r="M12" t="n">
-        <v>1157100</v>
+        <v>7590975</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>714000</v>
+        <v>1999200</v>
       </c>
       <c r="P12" t="n">
-        <v>3843450</v>
+        <v>6366750</v>
       </c>
       <c r="Q12" t="n">
-        <v>16316344.08</v>
+        <v>169084694.7</v>
       </c>
     </row>
     <row r="13">
@@ -23001,7 +23001,7 @@
         <v>2600100</v>
       </c>
       <c r="H13" t="n">
-        <v>7524000</v>
+        <v>10431000</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -23013,22 +23013,22 @@
         <v>276623.53</v>
       </c>
       <c r="L13" t="n">
-        <v>17172000</v>
+        <v>23976000</v>
       </c>
       <c r="M13" t="n">
-        <v>945000</v>
+        <v>5754000</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>408000</v>
+        <v>663000</v>
       </c>
       <c r="P13" t="n">
-        <v>2747550</v>
+        <v>4590300</v>
       </c>
       <c r="Q13" t="n">
-        <v>11154732.48</v>
+        <v>115595413.2</v>
       </c>
     </row>
     <row r="14">
@@ -23054,7 +23054,7 @@
         <v>1189080</v>
       </c>
       <c r="H14" t="n">
-        <v>4617000</v>
+        <v>4446000</v>
       </c>
       <c r="I14" t="n">
         <v>188785.73</v>
@@ -23066,22 +23066,22 @@
         <v>47196.43</v>
       </c>
       <c r="L14" t="n">
-        <v>7435800</v>
+        <v>10341000</v>
       </c>
       <c r="M14" t="n">
-        <v>399000</v>
+        <v>5911500</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>596700</v>
+        <v>545700</v>
       </c>
       <c r="P14" t="n">
-        <v>1825200</v>
+        <v>2365350</v>
       </c>
       <c r="Q14" t="n">
-        <v>5251672.8</v>
+        <v>54422577</v>
       </c>
     </row>
     <row r="15">
@@ -23107,7 +23107,7 @@
         <v>299700</v>
       </c>
       <c r="H15" t="n">
-        <v>1539000</v>
+        <v>2907000</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -23119,22 +23119,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>2910600</v>
+        <v>5454000</v>
       </c>
       <c r="M15" t="n">
-        <v>105000</v>
+        <v>2100000</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>127500</v>
+        <v>219300</v>
       </c>
       <c r="P15" t="n">
-        <v>1967550</v>
+        <v>2172300</v>
       </c>
       <c r="Q15" t="n">
-        <v>1885459.68</v>
+        <v>19538836.2</v>
       </c>
     </row>
     <row r="16">
@@ -23160,7 +23160,7 @@
         <v>202500</v>
       </c>
       <c r="H16" t="n">
-        <v>684000</v>
+        <v>855000</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -23172,22 +23172,22 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1269000</v>
+        <v>4314600</v>
       </c>
       <c r="M16" t="n">
-        <v>52500</v>
+        <v>1102500</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>5100</v>
+        <v>25500</v>
       </c>
       <c r="P16" t="n">
-        <v>2503800</v>
+        <v>3611400</v>
       </c>
       <c r="Q16" t="n">
-        <v>1319982.48</v>
+        <v>13678850.7</v>
       </c>
     </row>
     <row r="17">
@@ -23213,7 +23213,7 @@
         <v>69660</v>
       </c>
       <c r="H17" t="n">
-        <v>342000</v>
+        <v>855000</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -23225,10 +23225,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>410400</v>
+        <v>1674000</v>
       </c>
       <c r="M17" t="n">
-        <v>52500</v>
+        <v>556500</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -23237,10 +23237,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1378650</v>
+        <v>2117700</v>
       </c>
       <c r="Q17" t="n">
-        <v>681117.12</v>
+        <v>7058350.8</v>
       </c>
     </row>
     <row r="18">
@@ -23266,7 +23266,7 @@
         <v>16200</v>
       </c>
       <c r="H18" t="n">
-        <v>342000</v>
+        <v>684000</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -23278,10 +23278,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>280800</v>
+        <v>1107000</v>
       </c>
       <c r="M18" t="n">
-        <v>73500</v>
+        <v>346500</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -23290,10 +23290,10 @@
         <v>5100</v>
       </c>
       <c r="P18" t="n">
-        <v>1394250</v>
+        <v>1994850</v>
       </c>
       <c r="Q18" t="n">
-        <v>322010.64</v>
+        <v>3336965.1</v>
       </c>
     </row>
     <row r="19">
@@ -23331,22 +23331,22 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>259200</v>
+        <v>702000</v>
       </c>
       <c r="M19" t="n">
-        <v>31500</v>
+        <v>420000</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>5100</v>
+        <v>20400</v>
       </c>
       <c r="P19" t="n">
-        <v>1142700</v>
+        <v>2020200</v>
       </c>
       <c r="Q19" t="n">
-        <v>149588.64</v>
+        <v>1550172.6</v>
       </c>
     </row>
     <row r="20">
@@ -23372,7 +23372,7 @@
         <v>199260</v>
       </c>
       <c r="H20" t="n">
-        <v>342000</v>
+        <v>684000</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -23384,10 +23384,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>118800</v>
+        <v>567000</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>588000</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -23396,10 +23396,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>126750</v>
+        <v>337350</v>
       </c>
       <c r="Q20" t="n">
-        <v>44193.6</v>
+        <v>457974</v>
       </c>
     </row>
     <row r="21">
@@ -23449,10 +23449,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>7800</v>
       </c>
       <c r="Q21" t="n">
-        <v>8838.719999999999</v>
+        <v>91594.8</v>
       </c>
     </row>
     <row r="22">
@@ -23490,7 +23490,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>10800</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -23505,7 +23505,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>870.48</v>
+        <v>9020.700000000001</v>
       </c>
     </row>
     <row r="23">
@@ -23543,7 +23543,7 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>5400</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -23816,7 +23816,7 @@
         <v>50310</v>
       </c>
       <c r="H4" t="n">
-        <v>3090</v>
+        <v>2760</v>
       </c>
       <c r="I4" t="n">
         <v>2</v>
@@ -23828,22 +23828,22 @@
         <v>73</v>
       </c>
       <c r="L4" t="n">
-        <v>137190</v>
+        <v>119850</v>
       </c>
       <c r="M4" t="n">
-        <v>44130</v>
+        <v>45900</v>
       </c>
       <c r="N4" t="n">
-        <v>15630</v>
+        <v>13380</v>
       </c>
       <c r="O4" t="n">
-        <v>17250</v>
+        <v>19230</v>
       </c>
       <c r="P4" t="n">
-        <v>1950</v>
+        <v>720</v>
       </c>
       <c r="Q4" t="n">
-        <v>10689.38</v>
+        <v>104797.8</v>
       </c>
     </row>
     <row r="5">
@@ -23869,7 +23869,7 @@
         <v>58860</v>
       </c>
       <c r="H5" t="n">
-        <v>9480</v>
+        <v>8340</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -23881,22 +23881,22 @@
         <v>68</v>
       </c>
       <c r="L5" t="n">
-        <v>165390</v>
+        <v>153030</v>
       </c>
       <c r="M5" t="n">
-        <v>17970</v>
+        <v>27540</v>
       </c>
       <c r="N5" t="n">
-        <v>21150</v>
+        <v>21780</v>
       </c>
       <c r="O5" t="n">
-        <v>20460</v>
+        <v>20340</v>
       </c>
       <c r="P5" t="n">
-        <v>2970</v>
+        <v>1020</v>
       </c>
       <c r="Q5" t="n">
-        <v>18451.8</v>
+        <v>180900</v>
       </c>
     </row>
     <row r="6">
@@ -23922,7 +23922,7 @@
         <v>64560</v>
       </c>
       <c r="H6" t="n">
-        <v>12900</v>
+        <v>13170</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -23934,22 +23934,22 @@
         <v>54</v>
       </c>
       <c r="L6" t="n">
-        <v>173100</v>
+        <v>162390</v>
       </c>
       <c r="M6" t="n">
-        <v>6690</v>
+        <v>13350</v>
       </c>
       <c r="N6" t="n">
-        <v>12540</v>
+        <v>14550</v>
       </c>
       <c r="O6" t="n">
-        <v>18540</v>
+        <v>21510</v>
       </c>
       <c r="P6" t="n">
-        <v>3390</v>
+        <v>1200</v>
       </c>
       <c r="Q6" t="n">
-        <v>22223.86</v>
+        <v>217881</v>
       </c>
     </row>
     <row r="7">
@@ -23975,7 +23975,7 @@
         <v>64230</v>
       </c>
       <c r="H7" t="n">
-        <v>13230</v>
+        <v>13110</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -23987,22 +23987,22 @@
         <v>59</v>
       </c>
       <c r="L7" t="n">
-        <v>184590</v>
+        <v>186840</v>
       </c>
       <c r="M7" t="n">
-        <v>4950</v>
+        <v>14100</v>
       </c>
       <c r="N7" t="n">
-        <v>6000</v>
+        <v>8130</v>
       </c>
       <c r="O7" t="n">
-        <v>21240</v>
+        <v>20430</v>
       </c>
       <c r="P7" t="n">
-        <v>3930</v>
+        <v>1890</v>
       </c>
       <c r="Q7" t="n">
-        <v>23249.54</v>
+        <v>227936.7</v>
       </c>
     </row>
     <row r="8">
@@ -24028,7 +24028,7 @@
         <v>86130</v>
       </c>
       <c r="H8" t="n">
-        <v>19320</v>
+        <v>20070</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
@@ -24040,22 +24040,22 @@
         <v>48</v>
       </c>
       <c r="L8" t="n">
-        <v>239370</v>
+        <v>235530</v>
       </c>
       <c r="M8" t="n">
-        <v>5100</v>
+        <v>12180</v>
       </c>
       <c r="N8" t="n">
-        <v>1290</v>
+        <v>2340</v>
       </c>
       <c r="O8" t="n">
-        <v>23160</v>
+        <v>24060</v>
       </c>
       <c r="P8" t="n">
-        <v>6120</v>
+        <v>4200</v>
       </c>
       <c r="Q8" t="n">
-        <v>24300.47</v>
+        <v>238239.9</v>
       </c>
     </row>
     <row r="9">
@@ -24081,7 +24081,7 @@
         <v>99450</v>
       </c>
       <c r="H9" t="n">
-        <v>3930</v>
+        <v>5160</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -24093,22 +24093,22 @@
         <v>66</v>
       </c>
       <c r="L9" t="n">
-        <v>240120</v>
+        <v>247230</v>
       </c>
       <c r="M9" t="n">
-        <v>4200</v>
+        <v>10680</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>19560</v>
+        <v>22110</v>
       </c>
       <c r="P9" t="n">
-        <v>9270</v>
+        <v>6120</v>
       </c>
       <c r="Q9" t="n">
-        <v>28696.4</v>
+        <v>281337.3</v>
       </c>
     </row>
     <row r="10">
@@ -24134,7 +24134,7 @@
         <v>92520</v>
       </c>
       <c r="H10" t="n">
-        <v>480</v>
+        <v>600</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -24146,22 +24146,22 @@
         <v>49</v>
       </c>
       <c r="L10" t="n">
-        <v>198120</v>
+        <v>216480</v>
       </c>
       <c r="M10" t="n">
-        <v>5280</v>
+        <v>9300</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>20520</v>
+        <v>24510</v>
       </c>
       <c r="P10" t="n">
-        <v>12630</v>
+        <v>6360</v>
       </c>
       <c r="Q10" t="n">
-        <v>29813.43</v>
+        <v>292288.5</v>
       </c>
     </row>
     <row r="11">
@@ -24187,7 +24187,7 @@
         <v>53370</v>
       </c>
       <c r="H11" t="n">
-        <v>300</v>
+        <v>390</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -24199,22 +24199,22 @@
         <v>28</v>
       </c>
       <c r="L11" t="n">
-        <v>111750</v>
+        <v>132090</v>
       </c>
       <c r="M11" t="n">
-        <v>3420</v>
+        <v>6540</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>9900</v>
+        <v>18030</v>
       </c>
       <c r="P11" t="n">
-        <v>15900</v>
+        <v>9810</v>
       </c>
       <c r="Q11" t="n">
-        <v>23802.73</v>
+        <v>233360.1</v>
       </c>
     </row>
     <row r="12">
@@ -24240,7 +24240,7 @@
         <v>25740</v>
       </c>
       <c r="H12" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -24252,22 +24252,22 @@
         <v>6</v>
       </c>
       <c r="L12" t="n">
-        <v>51630</v>
+        <v>65040</v>
       </c>
       <c r="M12" t="n">
-        <v>2040</v>
+        <v>5340</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>4140</v>
+        <v>11610</v>
       </c>
       <c r="P12" t="n">
-        <v>14370</v>
+        <v>15270</v>
       </c>
       <c r="Q12" t="n">
-        <v>14667.62</v>
+        <v>143800.2</v>
       </c>
     </row>
     <row r="13">
@@ -24305,22 +24305,22 @@
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>25020</v>
+        <v>34050</v>
       </c>
       <c r="M13" t="n">
-        <v>2220</v>
+        <v>4740</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2400</v>
+        <v>3900</v>
       </c>
       <c r="P13" t="n">
-        <v>12360</v>
+        <v>12810</v>
       </c>
       <c r="Q13" t="n">
-        <v>8217.200000000001</v>
+        <v>80560.8</v>
       </c>
     </row>
     <row r="14">
@@ -24358,22 +24358,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>7650</v>
+        <v>12420</v>
       </c>
       <c r="M14" t="n">
-        <v>750</v>
+        <v>4140</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3510</v>
+        <v>3210</v>
       </c>
       <c r="P14" t="n">
-        <v>12570</v>
+        <v>10380</v>
       </c>
       <c r="Q14" t="n">
-        <v>3140.2</v>
+        <v>30786.3</v>
       </c>
     </row>
     <row r="15">
@@ -24411,22 +24411,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>2550</v>
+        <v>7590</v>
       </c>
       <c r="M15" t="n">
-        <v>90</v>
+        <v>1470</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>750</v>
+        <v>1290</v>
       </c>
       <c r="P15" t="n">
-        <v>18690</v>
+        <v>20460</v>
       </c>
       <c r="Q15" t="n">
-        <v>951.51</v>
+        <v>9328.5</v>
       </c>
     </row>
     <row r="16">
@@ -24464,22 +24464,22 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>960</v>
+        <v>6390</v>
       </c>
       <c r="M16" t="n">
-        <v>90</v>
+        <v>810</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="P16" t="n">
-        <v>25920</v>
+        <v>34290</v>
       </c>
       <c r="Q16" t="n">
-        <v>455.51</v>
+        <v>4465.8</v>
       </c>
     </row>
     <row r="17">
@@ -24517,10 +24517,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>120</v>
+        <v>2310</v>
       </c>
       <c r="M17" t="n">
-        <v>60</v>
+        <v>750</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -24529,10 +24529,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>11190</v>
+        <v>9210</v>
       </c>
       <c r="Q17" t="n">
-        <v>176.35</v>
+        <v>1728.9</v>
       </c>
     </row>
     <row r="18">
@@ -24570,10 +24570,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>210</v>
+        <v>1530</v>
       </c>
       <c r="M18" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -24582,10 +24582,10 @@
         <v>30</v>
       </c>
       <c r="P18" t="n">
-        <v>18000</v>
+        <v>22800</v>
       </c>
       <c r="Q18" t="n">
-        <v>118.15</v>
+        <v>1158.3</v>
       </c>
     </row>
     <row r="19">
@@ -24623,7 +24623,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>120</v>
+        <v>1110</v>
       </c>
       <c r="M19" t="n">
         <v>90</v>
@@ -24632,13 +24632,13 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="P19" t="n">
-        <v>16890</v>
+        <v>29850</v>
       </c>
       <c r="Q19" t="n">
-        <v>100.34</v>
+        <v>983.7</v>
       </c>
     </row>
     <row r="20">
@@ -24679,7 +24679,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -24688,10 +24688,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1950</v>
+        <v>5190</v>
       </c>
       <c r="Q20" t="n">
-        <v>19</v>
+        <v>186.3</v>
       </c>
     </row>
     <row r="21">
@@ -24741,10 +24741,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="Q21" t="n">
-        <v>6.52</v>
+        <v>63.9</v>
       </c>
     </row>
     <row r="22">
@@ -24797,7 +24797,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.09</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="23">
@@ -25161,7 +25161,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>3412.8</v>
+        <v>3002.4</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -25173,22 +25173,22 @@
         <v>22.51</v>
       </c>
       <c r="L5" t="n">
-        <v>34731.9</v>
+        <v>32136.3</v>
       </c>
       <c r="M5" t="n">
-        <v>359.4</v>
+        <v>550.8</v>
       </c>
       <c r="N5" t="n">
-        <v>211.5</v>
+        <v>217.8</v>
       </c>
       <c r="O5" t="n">
-        <v>1023</v>
+        <v>1017</v>
       </c>
       <c r="P5" t="n">
-        <v>59.4</v>
+        <v>20.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>922.59</v>
+        <v>9045</v>
       </c>
     </row>
     <row r="6">
@@ -25214,7 +25214,7 @@
         <v>3228</v>
       </c>
       <c r="H6" t="n">
-        <v>7353</v>
+        <v>7506.9</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -25226,22 +25226,22 @@
         <v>27.38</v>
       </c>
       <c r="L6" t="n">
-        <v>64047</v>
+        <v>60084.3</v>
       </c>
       <c r="M6" t="n">
-        <v>535.2</v>
+        <v>1068</v>
       </c>
       <c r="N6" t="n">
-        <v>627</v>
+        <v>727.5</v>
       </c>
       <c r="O6" t="n">
-        <v>4635</v>
+        <v>5377.5</v>
       </c>
       <c r="P6" t="n">
-        <v>508.5</v>
+        <v>180</v>
       </c>
       <c r="Q6" t="n">
-        <v>16667.9</v>
+        <v>163410.75</v>
       </c>
     </row>
     <row r="7">
@@ -25267,7 +25267,7 @@
         <v>9634.5</v>
       </c>
       <c r="H7" t="n">
-        <v>9657.9</v>
+        <v>9570.299999999999</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -25279,22 +25279,22 @@
         <v>37.64</v>
       </c>
       <c r="L7" t="n">
-        <v>110754</v>
+        <v>112104</v>
       </c>
       <c r="M7" t="n">
-        <v>1732.5</v>
+        <v>4935</v>
       </c>
       <c r="N7" t="n">
-        <v>420</v>
+        <v>569.1</v>
       </c>
       <c r="O7" t="n">
-        <v>7434</v>
+        <v>7150.5</v>
       </c>
       <c r="P7" t="n">
-        <v>982.5</v>
+        <v>472.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>18599.63</v>
+        <v>182349.36</v>
       </c>
     </row>
     <row r="8">
@@ -25320,7 +25320,7 @@
         <v>55984.5</v>
       </c>
       <c r="H8" t="n">
-        <v>16422</v>
+        <v>17059.5</v>
       </c>
       <c r="I8" t="n">
         <v>0.74</v>
@@ -25332,22 +25332,22 @@
         <v>35.33</v>
       </c>
       <c r="L8" t="n">
-        <v>169952.7</v>
+        <v>167226.3</v>
       </c>
       <c r="M8" t="n">
-        <v>2805</v>
+        <v>6699</v>
       </c>
       <c r="N8" t="n">
-        <v>258</v>
+        <v>468</v>
       </c>
       <c r="O8" t="n">
-        <v>10422</v>
+        <v>10827</v>
       </c>
       <c r="P8" t="n">
-        <v>2325.6</v>
+        <v>1596</v>
       </c>
       <c r="Q8" t="n">
-        <v>23085.45</v>
+        <v>226327.9</v>
       </c>
     </row>
     <row r="9">
@@ -25373,7 +25373,7 @@
         <v>84532.5</v>
       </c>
       <c r="H9" t="n">
-        <v>3930</v>
+        <v>5160</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -25385,22 +25385,22 @@
         <v>53</v>
       </c>
       <c r="L9" t="n">
-        <v>194497.2</v>
+        <v>200256.3</v>
       </c>
       <c r="M9" t="n">
-        <v>2940</v>
+        <v>7476</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>10758</v>
+        <v>12160.5</v>
       </c>
       <c r="P9" t="n">
-        <v>4635</v>
+        <v>3060</v>
       </c>
       <c r="Q9" t="n">
-        <v>27835.51</v>
+        <v>272897.18</v>
       </c>
     </row>
     <row r="10">
@@ -25426,7 +25426,7 @@
         <v>92520</v>
       </c>
       <c r="H10" t="n">
-        <v>480</v>
+        <v>600</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -25438,22 +25438,22 @@
         <v>42.63</v>
       </c>
       <c r="L10" t="n">
-        <v>176326.8</v>
+        <v>192667.2</v>
       </c>
       <c r="M10" t="n">
-        <v>4488</v>
+        <v>7905</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>14364</v>
+        <v>17157</v>
       </c>
       <c r="P10" t="n">
-        <v>10735.5</v>
+        <v>5406</v>
       </c>
       <c r="Q10" t="n">
-        <v>29813.43</v>
+        <v>292288.5</v>
       </c>
     </row>
     <row r="11">
@@ -25479,7 +25479,7 @@
         <v>53370</v>
       </c>
       <c r="H11" t="n">
-        <v>300</v>
+        <v>390</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -25491,22 +25491,22 @@
         <v>25.16</v>
       </c>
       <c r="L11" t="n">
-        <v>111750</v>
+        <v>132090</v>
       </c>
       <c r="M11" t="n">
-        <v>3078</v>
+        <v>5886</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>8415</v>
+        <v>15325.5</v>
       </c>
       <c r="P11" t="n">
-        <v>14310</v>
+        <v>8829</v>
       </c>
       <c r="Q11" t="n">
-        <v>23802.73</v>
+        <v>233360.1</v>
       </c>
     </row>
     <row r="12">
@@ -25532,7 +25532,7 @@
         <v>25740</v>
       </c>
       <c r="H12" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -25544,22 +25544,22 @@
         <v>5.56</v>
       </c>
       <c r="L12" t="n">
-        <v>51630</v>
+        <v>65040</v>
       </c>
       <c r="M12" t="n">
-        <v>1938</v>
+        <v>5073</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>4140</v>
+        <v>11610</v>
       </c>
       <c r="P12" t="n">
-        <v>14370</v>
+        <v>15270</v>
       </c>
       <c r="Q12" t="n">
-        <v>14667.62</v>
+        <v>143800.2</v>
       </c>
     </row>
     <row r="13">
@@ -25597,22 +25597,22 @@
         <v>0.95</v>
       </c>
       <c r="L13" t="n">
-        <v>25020</v>
+        <v>34050</v>
       </c>
       <c r="M13" t="n">
-        <v>2220</v>
+        <v>4740</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2400</v>
+        <v>3900</v>
       </c>
       <c r="P13" t="n">
-        <v>12360</v>
+        <v>12810</v>
       </c>
       <c r="Q13" t="n">
-        <v>8217.200000000001</v>
+        <v>80560.8</v>
       </c>
     </row>
     <row r="14">
@@ -25650,22 +25650,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>7650</v>
+        <v>12420</v>
       </c>
       <c r="M14" t="n">
-        <v>750</v>
+        <v>4140</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3510</v>
+        <v>3210</v>
       </c>
       <c r="P14" t="n">
-        <v>12570</v>
+        <v>10380</v>
       </c>
       <c r="Q14" t="n">
-        <v>3140.2</v>
+        <v>30786.3</v>
       </c>
     </row>
     <row r="15">
@@ -25703,22 +25703,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>2550</v>
+        <v>7590</v>
       </c>
       <c r="M15" t="n">
-        <v>90</v>
+        <v>1470</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>750</v>
+        <v>1290</v>
       </c>
       <c r="P15" t="n">
-        <v>18690</v>
+        <v>20460</v>
       </c>
       <c r="Q15" t="n">
-        <v>951.51</v>
+        <v>9328.5</v>
       </c>
     </row>
     <row r="16">
@@ -25756,22 +25756,22 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>960</v>
+        <v>6390</v>
       </c>
       <c r="M16" t="n">
-        <v>90</v>
+        <v>810</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="P16" t="n">
-        <v>25920</v>
+        <v>34290</v>
       </c>
       <c r="Q16" t="n">
-        <v>455.51</v>
+        <v>4465.8</v>
       </c>
     </row>
     <row r="17">
@@ -25809,10 +25809,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>120</v>
+        <v>2310</v>
       </c>
       <c r="M17" t="n">
-        <v>60</v>
+        <v>750</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -25821,10 +25821,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>11190</v>
+        <v>9210</v>
       </c>
       <c r="Q17" t="n">
-        <v>176.35</v>
+        <v>1728.9</v>
       </c>
     </row>
     <row r="18">
@@ -25862,10 +25862,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>210</v>
+        <v>1530</v>
       </c>
       <c r="M18" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -25874,10 +25874,10 @@
         <v>30</v>
       </c>
       <c r="P18" t="n">
-        <v>18000</v>
+        <v>22800</v>
       </c>
       <c r="Q18" t="n">
-        <v>118.15</v>
+        <v>1158.3</v>
       </c>
     </row>
     <row r="19">
@@ -25915,7 +25915,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>120</v>
+        <v>1110</v>
       </c>
       <c r="M19" t="n">
         <v>90</v>
@@ -25924,13 +25924,13 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="P19" t="n">
-        <v>16890</v>
+        <v>29850</v>
       </c>
       <c r="Q19" t="n">
-        <v>100.34</v>
+        <v>983.7</v>
       </c>
     </row>
     <row r="20">
@@ -25971,7 +25971,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -25980,10 +25980,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1950</v>
+        <v>5190</v>
       </c>
       <c r="Q20" t="n">
-        <v>19</v>
+        <v>186.3</v>
       </c>
     </row>
     <row r="21">
@@ -26033,10 +26033,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="Q21" t="n">
-        <v>6.52</v>
+        <v>63.9</v>
       </c>
     </row>
     <row r="22">
@@ -26089,7 +26089,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.09</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="23">
@@ -26453,7 +26453,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>19452960</v>
+        <v>17113680</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -26465,22 +26465,22 @@
         <v>1092898.45</v>
       </c>
       <c r="L5" t="n">
-        <v>6251742</v>
+        <v>5784534</v>
       </c>
       <c r="M5" t="n">
-        <v>125790</v>
+        <v>192780</v>
       </c>
       <c r="N5" t="n">
-        <v>35955</v>
+        <v>37026</v>
       </c>
       <c r="O5" t="n">
-        <v>173910</v>
+        <v>172890</v>
       </c>
       <c r="P5" t="n">
-        <v>3861</v>
+        <v>1326</v>
       </c>
       <c r="Q5" t="n">
-        <v>553554</v>
+        <v>5427000</v>
       </c>
     </row>
     <row r="6">
@@ -26506,7 +26506,7 @@
         <v>174312</v>
       </c>
       <c r="H6" t="n">
-        <v>41912100</v>
+        <v>42789330</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -26518,22 +26518,22 @@
         <v>1329366.17</v>
       </c>
       <c r="L6" t="n">
-        <v>11528460</v>
+        <v>10815174</v>
       </c>
       <c r="M6" t="n">
-        <v>187320</v>
+        <v>373800</v>
       </c>
       <c r="N6" t="n">
-        <v>106590</v>
+        <v>123675</v>
       </c>
       <c r="O6" t="n">
-        <v>787950</v>
+        <v>914175</v>
       </c>
       <c r="P6" t="n">
-        <v>33052.5</v>
+        <v>11700</v>
       </c>
       <c r="Q6" t="n">
-        <v>10000737.9</v>
+        <v>98046450</v>
       </c>
     </row>
     <row r="7">
@@ -26559,7 +26559,7 @@
         <v>520263</v>
       </c>
       <c r="H7" t="n">
-        <v>55050030</v>
+        <v>54550710</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -26571,22 +26571,22 @@
         <v>1827744.95</v>
       </c>
       <c r="L7" t="n">
-        <v>19935720</v>
+        <v>20178720</v>
       </c>
       <c r="M7" t="n">
-        <v>606375</v>
+        <v>1727250</v>
       </c>
       <c r="N7" t="n">
-        <v>71400</v>
+        <v>96747</v>
       </c>
       <c r="O7" t="n">
-        <v>1263780</v>
+        <v>1215585</v>
       </c>
       <c r="P7" t="n">
-        <v>63862.5</v>
+        <v>30712.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>11159780.83</v>
+        <v>109409616</v>
       </c>
     </row>
     <row r="8">
@@ -26612,7 +26612,7 @@
         <v>3023163</v>
       </c>
       <c r="H8" t="n">
-        <v>93605400</v>
+        <v>97239150</v>
       </c>
       <c r="I8" t="n">
         <v>142948.86</v>
@@ -26624,22 +26624,22 @@
         <v>1715386.37</v>
       </c>
       <c r="L8" t="n">
-        <v>30591486</v>
+        <v>30100734</v>
       </c>
       <c r="M8" t="n">
-        <v>981750</v>
+        <v>2344650</v>
       </c>
       <c r="N8" t="n">
-        <v>43860</v>
+        <v>79560</v>
       </c>
       <c r="O8" t="n">
-        <v>1771740</v>
+        <v>1840590</v>
       </c>
       <c r="P8" t="n">
-        <v>151164</v>
+        <v>103740</v>
       </c>
       <c r="Q8" t="n">
-        <v>13851267.79</v>
+        <v>135796743</v>
       </c>
     </row>
     <row r="9">
@@ -26665,7 +26665,7 @@
         <v>4564755</v>
       </c>
       <c r="H9" t="n">
-        <v>22401000</v>
+        <v>29412000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -26677,22 +26677,22 @@
         <v>2573370.89</v>
       </c>
       <c r="L9" t="n">
-        <v>35009496</v>
+        <v>36046134</v>
       </c>
       <c r="M9" t="n">
-        <v>1029000</v>
+        <v>2616600</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>1828860</v>
+        <v>2067285</v>
       </c>
       <c r="P9" t="n">
-        <v>301275</v>
+        <v>198900</v>
       </c>
       <c r="Q9" t="n">
-        <v>16701307.48</v>
+        <v>163738308.6</v>
       </c>
     </row>
     <row r="10">
@@ -26718,7 +26718,7 @@
         <v>4996080</v>
       </c>
       <c r="H10" t="n">
-        <v>2736000</v>
+        <v>3420000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -26730,22 +26730,22 @@
         <v>2069942.28</v>
       </c>
       <c r="L10" t="n">
-        <v>31738824</v>
+        <v>34680096</v>
       </c>
       <c r="M10" t="n">
-        <v>1570800</v>
+        <v>2766750</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2441880</v>
+        <v>2916690</v>
       </c>
       <c r="P10" t="n">
-        <v>697807.5</v>
+        <v>351390</v>
       </c>
       <c r="Q10" t="n">
-        <v>17888056.2</v>
+        <v>175373100</v>
       </c>
     </row>
     <row r="11">
@@ -26771,7 +26771,7 @@
         <v>2881980</v>
       </c>
       <c r="H11" t="n">
-        <v>1710000</v>
+        <v>2223000</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -26783,22 +26783,22 @@
         <v>1221571.85</v>
       </c>
       <c r="L11" t="n">
-        <v>20115000</v>
+        <v>23776200</v>
       </c>
       <c r="M11" t="n">
-        <v>1077300</v>
+        <v>2060100</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>1430550</v>
+        <v>2605335</v>
       </c>
       <c r="P11" t="n">
-        <v>930150</v>
+        <v>573885</v>
       </c>
       <c r="Q11" t="n">
-        <v>14281638.12</v>
+        <v>140016060</v>
       </c>
     </row>
     <row r="12">
@@ -26824,7 +26824,7 @@
         <v>1389960</v>
       </c>
       <c r="H12" t="n">
-        <v>171000</v>
+        <v>513000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -26836,22 +26836,22 @@
         <v>270068.47</v>
       </c>
       <c r="L12" t="n">
-        <v>9293400</v>
+        <v>11707200</v>
       </c>
       <c r="M12" t="n">
-        <v>678300</v>
+        <v>1775550</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>703800</v>
+        <v>1973700</v>
       </c>
       <c r="P12" t="n">
-        <v>934050</v>
+        <v>992550</v>
       </c>
       <c r="Q12" t="n">
-        <v>8800572.24</v>
+        <v>86280120</v>
       </c>
     </row>
     <row r="13">
@@ -26889,22 +26889,22 @@
         <v>46103.92</v>
       </c>
       <c r="L13" t="n">
-        <v>4503600</v>
+        <v>6129000</v>
       </c>
       <c r="M13" t="n">
-        <v>777000</v>
+        <v>1659000</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>408000</v>
+        <v>663000</v>
       </c>
       <c r="P13" t="n">
-        <v>803400</v>
+        <v>832650</v>
       </c>
       <c r="Q13" t="n">
-        <v>4930320.96</v>
+        <v>48336480</v>
       </c>
     </row>
     <row r="14">
@@ -26942,22 +26942,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1377000</v>
+        <v>2235600</v>
       </c>
       <c r="M14" t="n">
-        <v>262500</v>
+        <v>1449000</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>596700</v>
+        <v>545700</v>
       </c>
       <c r="P14" t="n">
-        <v>817050</v>
+        <v>674700</v>
       </c>
       <c r="Q14" t="n">
-        <v>1884121.56</v>
+        <v>18471780</v>
       </c>
     </row>
     <row r="15">
@@ -26995,22 +26995,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>459000</v>
+        <v>1366200</v>
       </c>
       <c r="M15" t="n">
-        <v>31500</v>
+        <v>514500</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>127500</v>
+        <v>219300</v>
       </c>
       <c r="P15" t="n">
-        <v>1214850</v>
+        <v>1329900</v>
       </c>
       <c r="Q15" t="n">
-        <v>570904.2</v>
+        <v>5597100</v>
       </c>
     </row>
     <row r="16">
@@ -27048,22 +27048,22 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>172800</v>
+        <v>1150200</v>
       </c>
       <c r="M16" t="n">
-        <v>31500</v>
+        <v>283500</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>5100</v>
+        <v>25500</v>
       </c>
       <c r="P16" t="n">
-        <v>1684800</v>
+        <v>2228850</v>
       </c>
       <c r="Q16" t="n">
-        <v>273306.96</v>
+        <v>2679480</v>
       </c>
     </row>
     <row r="17">
@@ -27101,10 +27101,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>21600</v>
+        <v>415800</v>
       </c>
       <c r="M17" t="n">
-        <v>21000</v>
+        <v>262500</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -27113,10 +27113,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>727350</v>
+        <v>598650</v>
       </c>
       <c r="Q17" t="n">
-        <v>105808.68</v>
+        <v>1037340</v>
       </c>
     </row>
     <row r="18">
@@ -27154,10 +27154,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>37800</v>
+        <v>275400</v>
       </c>
       <c r="M18" t="n">
-        <v>21000</v>
+        <v>31500</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -27166,10 +27166,10 @@
         <v>5100</v>
       </c>
       <c r="P18" t="n">
-        <v>1170000</v>
+        <v>1482000</v>
       </c>
       <c r="Q18" t="n">
-        <v>70887.96000000001</v>
+        <v>694980</v>
       </c>
     </row>
     <row r="19">
@@ -27207,7 +27207,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>21600</v>
+        <v>199800</v>
       </c>
       <c r="M19" t="n">
         <v>31500</v>
@@ -27216,13 +27216,13 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>5100</v>
+        <v>20400</v>
       </c>
       <c r="P19" t="n">
-        <v>1097850</v>
+        <v>1940250</v>
       </c>
       <c r="Q19" t="n">
-        <v>60202.44</v>
+        <v>590220</v>
       </c>
     </row>
     <row r="20">
@@ -27263,7 +27263,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>31500</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -27272,10 +27272,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>126750</v>
+        <v>337350</v>
       </c>
       <c r="Q20" t="n">
-        <v>11401.56</v>
+        <v>111780</v>
       </c>
     </row>
     <row r="21">
@@ -27325,10 +27325,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>7800</v>
       </c>
       <c r="Q21" t="n">
-        <v>3910.68</v>
+        <v>38340</v>
       </c>
     </row>
     <row r="22">
@@ -27381,7 +27381,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>55.08</v>
+        <v>540</v>
       </c>
     </row>
     <row r="23">
@@ -27692,7 +27692,7 @@
         <v>133530</v>
       </c>
       <c r="H4" t="n">
-        <v>17580</v>
+        <v>18060</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -27704,7 +27704,7 @@
         <v>97</v>
       </c>
       <c r="L4" t="n">
-        <v>407010</v>
+        <v>434310</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -27713,13 +27713,13 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>61110</v>
+        <v>57090</v>
       </c>
       <c r="P4" t="n">
-        <v>630</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>43928.14</v>
+        <v>611657.64</v>
       </c>
     </row>
     <row r="5">
@@ -27745,7 +27745,7 @@
         <v>110610</v>
       </c>
       <c r="H5" t="n">
-        <v>22560</v>
+        <v>23790</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -27757,7 +27757,7 @@
         <v>60</v>
       </c>
       <c r="L5" t="n">
-        <v>260910</v>
+        <v>283500</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -27766,13 +27766,13 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>54390</v>
+        <v>58590</v>
       </c>
       <c r="P5" t="n">
-        <v>540</v>
+        <v>30</v>
       </c>
       <c r="Q5" t="n">
-        <v>27915.99</v>
+        <v>388703.7</v>
       </c>
     </row>
     <row r="6">
@@ -27798,7 +27798,7 @@
         <v>56370</v>
       </c>
       <c r="H6" t="n">
-        <v>18240</v>
+        <v>17520</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -27810,7 +27810,7 @@
         <v>27</v>
       </c>
       <c r="L6" t="n">
-        <v>135300</v>
+        <v>141930</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -27819,13 +27819,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>34890</v>
+        <v>35730</v>
       </c>
       <c r="P6" t="n">
-        <v>1710</v>
+        <v>30</v>
       </c>
       <c r="Q6" t="n">
-        <v>13892.94</v>
+        <v>193446</v>
       </c>
     </row>
     <row r="7">
@@ -27851,7 +27851,7 @@
         <v>31350</v>
       </c>
       <c r="H7" t="n">
-        <v>13350</v>
+        <v>14190</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -27863,7 +27863,7 @@
         <v>12</v>
       </c>
       <c r="L7" t="n">
-        <v>78960</v>
+        <v>83070</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -27872,13 +27872,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>25380</v>
+        <v>28200</v>
       </c>
       <c r="P7" t="n">
-        <v>2610</v>
+        <v>60</v>
       </c>
       <c r="Q7" t="n">
-        <v>6882.98</v>
+        <v>95838.92999999999</v>
       </c>
     </row>
     <row r="8">
@@ -27904,7 +27904,7 @@
         <v>10860</v>
       </c>
       <c r="H8" t="n">
-        <v>1080</v>
+        <v>1830</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -27916,7 +27916,7 @@
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>21870</v>
+        <v>25140</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -27925,13 +27925,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>9990</v>
+        <v>11310</v>
       </c>
       <c r="P8" t="n">
-        <v>4320</v>
+        <v>600</v>
       </c>
       <c r="Q8" t="n">
-        <v>1569.25</v>
+        <v>21850.29</v>
       </c>
     </row>
     <row r="9">
@@ -27957,7 +27957,7 @@
         <v>330</v>
       </c>
       <c r="H9" t="n">
-        <v>330</v>
+        <v>360</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -27969,7 +27969,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>4050</v>
+        <v>5640</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -27978,13 +27978,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>4470</v>
+        <v>10290</v>
       </c>
       <c r="P9" t="n">
-        <v>4410</v>
+        <v>1860</v>
       </c>
       <c r="Q9" t="n">
-        <v>100.89</v>
+        <v>1404.81</v>
       </c>
     </row>
     <row r="10">
@@ -28022,7 +28022,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>690</v>
+        <v>1980</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -28031,13 +28031,13 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1320</v>
+        <v>5430</v>
       </c>
       <c r="P10" t="n">
-        <v>5820</v>
+        <v>6480</v>
       </c>
       <c r="Q10" t="n">
-        <v>26.73</v>
+        <v>372.24</v>
       </c>
     </row>
     <row r="11">
@@ -28063,7 +28063,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -28075,7 +28075,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>420</v>
+        <v>2430</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -28084,13 +28084,13 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>90</v>
+        <v>1380</v>
       </c>
       <c r="P11" t="n">
-        <v>4200</v>
+        <v>8160</v>
       </c>
       <c r="Q11" t="n">
-        <v>11.23</v>
+        <v>156.42</v>
       </c>
     </row>
     <row r="12">
@@ -28116,7 +28116,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>30</v>
+        <v>240</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -28128,7 +28128,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>30</v>
+        <v>1140</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -28140,10 +28140,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2370</v>
+        <v>6240</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.2</v>
+        <v>30.69</v>
       </c>
     </row>
     <row r="13">
@@ -28169,7 +28169,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -28181,7 +28181,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>840</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -28193,10 +28193,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1050</v>
+        <v>3870</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.36</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="14">
@@ -28234,7 +28234,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -28246,10 +28246,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>150</v>
+        <v>840</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="15">
@@ -29037,7 +29037,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>8121.6</v>
+        <v>8564.4</v>
       </c>
       <c r="I5" t="n">
         <v>0.33</v>
@@ -29049,7 +29049,7 @@
         <v>19.86</v>
       </c>
       <c r="L5" t="n">
-        <v>54791.1</v>
+        <v>59535</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -29058,13 +29058,13 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>2719.5</v>
+        <v>2929.5</v>
       </c>
       <c r="P5" t="n">
-        <v>10.8</v>
+        <v>0.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>1395.8</v>
+        <v>19435.18</v>
       </c>
     </row>
     <row r="6">
@@ -29090,7 +29090,7 @@
         <v>2818.5</v>
       </c>
       <c r="H6" t="n">
-        <v>10396.8</v>
+        <v>9986.4</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -29102,7 +29102,7 @@
         <v>13.69</v>
       </c>
       <c r="L6" t="n">
-        <v>50061</v>
+        <v>52514.1</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -29111,13 +29111,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>8722.5</v>
+        <v>8932.5</v>
       </c>
       <c r="P6" t="n">
-        <v>256.5</v>
+        <v>4.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>10419.7</v>
+        <v>145084.5</v>
       </c>
     </row>
     <row r="7">
@@ -29143,7 +29143,7 @@
         <v>4702.5</v>
       </c>
       <c r="H7" t="n">
-        <v>9745.5</v>
+        <v>10358.7</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -29155,7 +29155,7 @@
         <v>7.66</v>
       </c>
       <c r="L7" t="n">
-        <v>47376</v>
+        <v>49842</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -29164,13 +29164,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>8883</v>
+        <v>9870</v>
       </c>
       <c r="P7" t="n">
-        <v>652.5</v>
+        <v>15</v>
       </c>
       <c r="Q7" t="n">
-        <v>5506.38</v>
+        <v>76671.14</v>
       </c>
     </row>
     <row r="8">
@@ -29196,7 +29196,7 @@
         <v>7059</v>
       </c>
       <c r="H8" t="n">
-        <v>918</v>
+        <v>1555.5</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -29208,7 +29208,7 @@
         <v>0.74</v>
       </c>
       <c r="L8" t="n">
-        <v>15527.7</v>
+        <v>17849.4</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -29217,13 +29217,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>4495.5</v>
+        <v>5089.5</v>
       </c>
       <c r="P8" t="n">
-        <v>1641.6</v>
+        <v>228</v>
       </c>
       <c r="Q8" t="n">
-        <v>1490.79</v>
+        <v>20757.78</v>
       </c>
     </row>
     <row r="9">
@@ -29249,7 +29249,7 @@
         <v>280.5</v>
       </c>
       <c r="H9" t="n">
-        <v>330</v>
+        <v>360</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -29261,7 +29261,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>3280.5</v>
+        <v>4568.4</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -29270,13 +29270,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2458.5</v>
+        <v>5659.5</v>
       </c>
       <c r="P9" t="n">
-        <v>2205</v>
+        <v>930</v>
       </c>
       <c r="Q9" t="n">
-        <v>97.86</v>
+        <v>1362.67</v>
       </c>
     </row>
     <row r="10">
@@ -29314,7 +29314,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>614.1</v>
+        <v>1762.2</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -29323,13 +29323,13 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>924</v>
+        <v>3801</v>
       </c>
       <c r="P10" t="n">
-        <v>4947</v>
+        <v>5508</v>
       </c>
       <c r="Q10" t="n">
-        <v>26.73</v>
+        <v>372.24</v>
       </c>
     </row>
     <row r="11">
@@ -29355,7 +29355,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -29367,7 +29367,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>420</v>
+        <v>2430</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -29376,13 +29376,13 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>76.5</v>
+        <v>1173</v>
       </c>
       <c r="P11" t="n">
-        <v>3780</v>
+        <v>7344</v>
       </c>
       <c r="Q11" t="n">
-        <v>11.23</v>
+        <v>156.42</v>
       </c>
     </row>
     <row r="12">
@@ -29408,7 +29408,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>30</v>
+        <v>240</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -29420,7 +29420,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>30</v>
+        <v>1140</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -29432,10 +29432,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2370</v>
+        <v>6240</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.2</v>
+        <v>30.69</v>
       </c>
     </row>
     <row r="13">
@@ -29461,7 +29461,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -29473,7 +29473,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>840</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -29485,10 +29485,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1050</v>
+        <v>3870</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.36</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="14">
@@ -29526,7 +29526,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -29538,10 +29538,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>150</v>
+        <v>840</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="15">
@@ -30329,7 +30329,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>46293120</v>
+        <v>48817080</v>
       </c>
       <c r="I5" t="n">
         <v>64288.14</v>
@@ -30341,7 +30341,7 @@
         <v>964322.16</v>
       </c>
       <c r="L5" t="n">
-        <v>9862398</v>
+        <v>10716300</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -30350,13 +30350,13 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>462315</v>
+        <v>498015</v>
       </c>
       <c r="P5" t="n">
-        <v>702</v>
+        <v>39</v>
       </c>
       <c r="Q5" t="n">
-        <v>837479.79</v>
+        <v>11661111</v>
       </c>
     </row>
     <row r="6">
@@ -30382,7 +30382,7 @@
         <v>152199</v>
       </c>
       <c r="H6" t="n">
-        <v>59261760</v>
+        <v>56922480</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -30394,7 +30394,7 @@
         <v>664683.08</v>
       </c>
       <c r="L6" t="n">
-        <v>9010980</v>
+        <v>9452538</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -30403,13 +30403,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1482825</v>
+        <v>1518525</v>
       </c>
       <c r="P6" t="n">
-        <v>16672.5</v>
+        <v>292.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>6251823</v>
+        <v>87050700</v>
       </c>
     </row>
     <row r="7">
@@ -30435,7 +30435,7 @@
         <v>253935</v>
       </c>
       <c r="H7" t="n">
-        <v>55549350</v>
+        <v>59044590</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -30447,7 +30447,7 @@
         <v>371744.74</v>
       </c>
       <c r="L7" t="n">
-        <v>8527680</v>
+        <v>8971560</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -30456,13 +30456,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1510110</v>
+        <v>1677900</v>
       </c>
       <c r="P7" t="n">
-        <v>42412.5</v>
+        <v>975</v>
       </c>
       <c r="Q7" t="n">
-        <v>3303829.3</v>
+        <v>46002686.4</v>
       </c>
     </row>
     <row r="8">
@@ -30488,7 +30488,7 @@
         <v>381186</v>
       </c>
       <c r="H8" t="n">
-        <v>5232600</v>
+        <v>8866350</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -30500,7 +30500,7 @@
         <v>35737.22</v>
       </c>
       <c r="L8" t="n">
-        <v>2794986</v>
+        <v>3212892</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -30509,13 +30509,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>764235</v>
+        <v>865215</v>
       </c>
       <c r="P8" t="n">
-        <v>106704</v>
+        <v>14820</v>
       </c>
       <c r="Q8" t="n">
-        <v>894471.42</v>
+        <v>12454665.3</v>
       </c>
     </row>
     <row r="9">
@@ -30541,7 +30541,7 @@
         <v>15147</v>
       </c>
       <c r="H9" t="n">
-        <v>1881000</v>
+        <v>2052000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -30553,7 +30553,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>590490</v>
+        <v>822312</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -30562,13 +30562,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>417945</v>
+        <v>962115</v>
       </c>
       <c r="P9" t="n">
-        <v>143325</v>
+        <v>60450</v>
       </c>
       <c r="Q9" t="n">
-        <v>58718.5</v>
+        <v>817599.42</v>
       </c>
     </row>
     <row r="10">
@@ -30606,7 +30606,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>110538</v>
+        <v>317196</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -30615,13 +30615,13 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>157080</v>
+        <v>646170</v>
       </c>
       <c r="P10" t="n">
-        <v>321555</v>
+        <v>358020</v>
       </c>
       <c r="Q10" t="n">
-        <v>16040.16</v>
+        <v>223344</v>
       </c>
     </row>
     <row r="11">
@@ -30647,7 +30647,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>171000</v>
+        <v>855000</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -30659,7 +30659,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>75600</v>
+        <v>437400</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -30668,13 +30668,13 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>13005</v>
+        <v>199410</v>
       </c>
       <c r="P11" t="n">
-        <v>245700</v>
+        <v>477360</v>
       </c>
       <c r="Q11" t="n">
-        <v>6740.28</v>
+        <v>93852</v>
       </c>
     </row>
     <row r="12">
@@ -30700,7 +30700,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>171000</v>
+        <v>1368000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -30712,7 +30712,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>5400</v>
+        <v>205200</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -30724,10 +30724,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>154050</v>
+        <v>405600</v>
       </c>
       <c r="Q12" t="n">
-        <v>1322.46</v>
+        <v>18414</v>
       </c>
     </row>
     <row r="13">
@@ -30753,7 +30753,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>342000</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -30765,7 +30765,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>151200</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -30777,10 +30777,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>68250</v>
+        <v>251550</v>
       </c>
       <c r="Q13" t="n">
-        <v>213.3</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="14">
@@ -30818,7 +30818,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>37800</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -30830,10 +30830,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>9750</v>
+        <v>54600</v>
       </c>
       <c r="Q14" t="n">
-        <v>42.66</v>
+        <v>594</v>
       </c>
     </row>
     <row r="15">
